--- a/public/Invoicing.xlsx
+++ b/public/Invoicing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="132">
   <si>
     <t>Scheduled for Build</t>
   </si>
@@ -139,6 +139,12 @@
     <t>Bev Marchion</t>
   </si>
   <si>
+    <t xml:space="preserve">James Carlucci Roof </t>
+  </si>
+  <si>
+    <t>7/10 ready;. no folder</t>
+  </si>
+  <si>
     <t>Brett Schumacher</t>
   </si>
   <si>
@@ -163,7 +169,7 @@
     <t>7/9 Called and sent a text</t>
   </si>
   <si>
-    <t xml:space="preserve">James Carlucci Roof </t>
+    <t>Matthew Cox Roof</t>
   </si>
   <si>
     <t>Meghan Lewis</t>
@@ -172,16 +178,16 @@
     <t>7/9 Chelsea calling on 7/14</t>
   </si>
   <si>
-    <t>Matthew Cox Roof</t>
+    <t>Marc Johnson</t>
   </si>
   <si>
     <t>Amber Schrader</t>
   </si>
   <si>
-    <t xml:space="preserve">7/8 she should be good to pay now! </t>
+    <t xml:space="preserve">7/10 Chelesea - please call today :) </t>
   </si>
   <si>
-    <t>Marc Johnson</t>
+    <t xml:space="preserve">Eric Wagner Roof </t>
   </si>
   <si>
     <t>Anavelez Rodriguez Roof</t>
@@ -193,7 +199,7 @@
     <t>7/2 closing out with the siding</t>
   </si>
   <si>
-    <t xml:space="preserve">Eric Wagner Roof </t>
+    <t>Matthew Davis</t>
   </si>
   <si>
     <t>John Stavros</t>
@@ -202,7 +208,7 @@
     <t>7/8 message sent for an update on repairs</t>
   </si>
   <si>
-    <t>Matthew Davis</t>
+    <t>Donald Mills</t>
   </si>
   <si>
     <t>Ken Gilchrist</t>
@@ -211,7 +217,7 @@
     <t>7/9 COC is still in review</t>
   </si>
   <si>
-    <t>Donald Mills</t>
+    <t xml:space="preserve">April Deditch Roof </t>
   </si>
   <si>
     <t>James Harris Roof</t>
@@ -220,7 +226,7 @@
     <t xml:space="preserve">7/8 Chelsea calling tomorrow </t>
   </si>
   <si>
-    <t xml:space="preserve">April Deditch Roof </t>
+    <t>John Allen</t>
   </si>
   <si>
     <t>Barb Battaglia</t>
@@ -229,16 +235,13 @@
     <t>7/9 Chelsea calling to follow up about check</t>
   </si>
   <si>
-    <t>John Allen</t>
+    <t>Tracey Koszalka</t>
   </si>
   <si>
     <t>7/9 waiting on A &amp; J invoice to close</t>
   </si>
   <si>
-    <t>Rich Tran</t>
-  </si>
-  <si>
-    <t>Mike</t>
+    <t>Denise Kaluba Roof</t>
   </si>
   <si>
     <t>Jane Russo Siding</t>
@@ -250,16 +253,10 @@
     <t>7/8 Check has not been recevied. Chelsea calling Friday</t>
   </si>
   <si>
-    <t>Tracey Koszalka</t>
+    <t>Christina Simmons Siding</t>
   </si>
   <si>
     <t xml:space="preserve">Roy Kennedy </t>
-  </si>
-  <si>
-    <t>7/9 Sarah sent an updated invoice</t>
-  </si>
-  <si>
-    <t>Denise Kaluba Roof</t>
   </si>
   <si>
     <t>James Harris Siding</t>
@@ -268,7 +265,7 @@
     <t>7/9 Chelsea calling 7/14 to see if check was received</t>
   </si>
   <si>
-    <t>Christina Simmons Siding</t>
+    <t>Mohammad Barrak</t>
   </si>
   <si>
     <t>Maria Prescila</t>
@@ -277,28 +274,31 @@
     <t>7/9 Sarah resent invoice</t>
   </si>
   <si>
+    <t>Randy Evans</t>
+  </si>
+  <si>
     <t>Mohamed Hamid</t>
   </si>
   <si>
-    <t>Mohammad Barrak</t>
+    <t>Rachel Byrnes</t>
   </si>
   <si>
     <t>Thomas Holmes</t>
   </si>
   <si>
-    <t>Randy Evans</t>
+    <t>Kathie Parke</t>
   </si>
   <si>
     <t>Jennifer Morgan</t>
   </si>
   <si>
-    <t>Rachel Byrnes</t>
+    <t>Joe Schutt</t>
   </si>
   <si>
     <t>Shawn Simon, Roof</t>
   </si>
   <si>
-    <t>Kathie Parke</t>
+    <t>Nathan Molitor</t>
   </si>
   <si>
     <t>Brenda Omiecinski</t>
@@ -307,19 +307,19 @@
     <t>7/9 Repairs being done tomorrow 7/10 in the morning</t>
   </si>
   <si>
-    <t>Joe Schutt</t>
-  </si>
-  <si>
     <t>Andi Lamphier</t>
   </si>
   <si>
     <t>7/8 Issue with fascia. Holding off on follow up</t>
   </si>
   <si>
-    <t>Nathan Molitor</t>
+    <t>David Phillips</t>
   </si>
   <si>
-    <t>David Phillips</t>
+    <t>Jim Conner</t>
+  </si>
+  <si>
+    <t>Mike</t>
   </si>
   <si>
     <t>Howard Jackson</t>
@@ -328,13 +328,13 @@
     <t>Shannon Dorvinen</t>
   </si>
   <si>
-    <t>Jim Conner</t>
-  </si>
-  <si>
     <t>Mary Mundy</t>
   </si>
   <si>
     <t>7/9 Left her a voicemail</t>
+  </si>
+  <si>
+    <t>Mark Fleming</t>
   </si>
   <si>
     <t>Alan Rickenrode</t>
@@ -349,10 +349,10 @@
     <t>7/9 Jamie going out 7/15 at 10am to pick up check</t>
   </si>
   <si>
-    <t>Mark Fleming</t>
+    <t>Christopher Kray</t>
   </si>
   <si>
-    <t>Christopher Kray</t>
+    <t>Mitchell Ayers Roof</t>
   </si>
   <si>
     <t>Brian Bemiller</t>
@@ -364,7 +364,7 @@
     <t>7/9 Invoiced</t>
   </si>
   <si>
-    <t>Mitchell Ayers Roof</t>
+    <t>Coury Richards</t>
   </si>
   <si>
     <t>Tina Ward</t>
@@ -377,9 +377,6 @@
   </si>
   <si>
     <t>Meg</t>
-  </si>
-  <si>
-    <t>Coury Richards</t>
   </si>
   <si>
     <t>pg 11</t>
@@ -1507,9 +1504,6 @@
     <xf borderId="19" fillId="2" fontId="41" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="21" fillId="0" fontId="26" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -1519,8 +1513,8 @@
     <xf borderId="22" fillId="0" fontId="26" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="19" fillId="5" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="2" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="26" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -1533,6 +1527,9 @@
     </xf>
     <xf borderId="28" fillId="0" fontId="26" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="19" fillId="5" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="5" fontId="21" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1570,6 +1567,18 @@
     <xf borderId="19" fillId="5" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="32" fillId="0" fontId="26" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="33" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="34" fillId="0" fontId="26" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="21" fillId="2" fontId="21" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -1584,18 +1593,6 @@
     </xf>
     <xf borderId="19" fillId="5" fontId="41" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="26" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="26" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="26" fillId="2" fontId="21" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1675,12 +1672,6 @@
     <xf borderId="34" fillId="0" fontId="26" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="19" fillId="5" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="5" fontId="31" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="19" fillId="0" fontId="35" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1690,8 +1681,11 @@
     <xf borderId="22" fillId="0" fontId="26" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="19" fillId="2" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="19" fillId="5" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="5" fontId="31" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="29" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -1702,14 +1696,20 @@
     <xf borderId="30" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf borderId="19" fillId="2" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="21" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="35" fillId="0" fontId="50" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="26" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -1722,9 +1722,6 @@
     </xf>
     <xf borderId="0" fillId="5" fontId="32" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="26" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -2137,7 +2134,7 @@
       </c>
       <c r="C2" s="15">
         <f>D7</f>
-        <v>521246.77</v>
+        <v>499598.01</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="4"/>
@@ -2178,7 +2175,7 @@
       </c>
       <c r="C3" s="18">
         <f>L7</f>
-        <v>66165.67</v>
+        <v>73951.2</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="4"/>
@@ -2219,7 +2216,7 @@
       </c>
       <c r="C4" s="21">
         <f>T7</f>
-        <v>469584.445</v>
+        <v>449306.115</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="4"/>
@@ -2260,7 +2257,7 @@
       </c>
       <c r="C5" s="24">
         <f>C2+C3+C4</f>
-        <v>1056996.885</v>
+        <v>1022855.325</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="4"/>
@@ -2337,8 +2334,8 @@
       <c r="B7" s="28"/>
       <c r="C7" s="28"/>
       <c r="D7" s="29">
-        <f>E11+E14+E28+E35+E38+E41+E44+E47</f>
-        <v>521246.77</v>
+        <f>E11+E14+E26+E33+E36+E39+E42+E45</f>
+        <v>499598.01</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="5"/>
@@ -2351,7 +2348,7 @@
       <c r="K7" s="32"/>
       <c r="L7" s="33">
         <f>SUM(K9:K22)</f>
-        <v>66165.67</v>
+        <v>73951.2</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="34" t="s">
@@ -2366,7 +2363,7 @@
       </c>
       <c r="T7" s="38">
         <f>SUM(U9:U60)</f>
-        <v>469584.445</v>
+        <v>449306.115</v>
       </c>
       <c r="U7" s="35"/>
       <c r="V7" s="36"/>
@@ -2760,13 +2757,30 @@
         <v>8903.57</v>
       </c>
       <c r="F13" s="56"/>
-      <c r="L13" s="95"/>
+      <c r="G13" s="91">
+        <v>46211.0</v>
+      </c>
+      <c r="H13" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="94">
+        <v>7785.53</v>
+      </c>
+      <c r="L13" s="95" t="s">
+        <v>42</v>
+      </c>
       <c r="M13" s="58"/>
       <c r="N13" s="59">
         <v>46174.0</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P13" s="61" t="s">
         <v>23</v>
@@ -2788,7 +2802,7 @@
         <v>2175</v>
       </c>
       <c r="V13" s="65" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="W13" s="66"/>
       <c r="X13" s="67"/>
@@ -2824,7 +2838,7 @@
         <v>46175.0</v>
       </c>
       <c r="O14" s="72" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P14" s="97" t="s">
         <v>36</v>
@@ -2847,7 +2861,7 @@
         <v>14821.48</v>
       </c>
       <c r="V14" s="105" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W14" s="78"/>
       <c r="X14" s="67"/>
@@ -2867,7 +2881,7 @@
         <v>46209.0</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="54" t="s">
         <v>32</v>
@@ -2890,10 +2904,10 @@
         <v>46176.0</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P15" s="89" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q15" s="89" t="s">
         <v>17</v>
@@ -2910,7 +2924,7 @@
         <v>7202.92</v>
       </c>
       <c r="V15" s="65" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="W15" s="66"/>
       <c r="X15" s="106"/>
@@ -2930,16 +2944,16 @@
         <v>46211.0</v>
       </c>
       <c r="B16" s="92" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D16" s="93" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="94">
-        <v>7785.53</v>
+        <v>9441.65</v>
       </c>
       <c r="F16" s="56"/>
       <c r="G16" s="103"/>
@@ -2953,7 +2967,7 @@
         <v>46178.0</v>
       </c>
       <c r="O16" s="72" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P16" s="97" t="s">
         <v>19</v>
@@ -2976,7 +2990,7 @@
         <v>15846.07</v>
       </c>
       <c r="V16" s="77" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="W16" s="78"/>
       <c r="X16" s="106"/>
@@ -2992,20 +3006,20 @@
       <c r="AH16" s="67"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="91">
+      <c r="A17" s="107">
         <v>46211.0</v>
       </c>
-      <c r="B17" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="93" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="93" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="94">
-        <v>9441.65</v>
+      <c r="B17" s="108" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="109" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="110" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="111">
+        <v>24807.5</v>
       </c>
       <c r="F17" s="56"/>
       <c r="G17" s="103"/>
@@ -3019,7 +3033,7 @@
         <v>46181.0</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P17" s="89" t="s">
         <v>36</v>
@@ -3039,7 +3053,7 @@
         <v>21554.45</v>
       </c>
       <c r="V17" s="65" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="W17" s="66"/>
       <c r="X17" s="67"/>
@@ -3059,16 +3073,14 @@
         <v>46211.0</v>
       </c>
       <c r="B18" s="108" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" s="109" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="110" t="s">
-        <v>20</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D18" s="110"/>
       <c r="E18" s="111">
-        <v>24807.5</v>
+        <v>20256.52</v>
       </c>
       <c r="F18" s="56"/>
       <c r="G18" s="103"/>
@@ -3082,13 +3094,13 @@
         <v>46182.0</v>
       </c>
       <c r="O18" s="114" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P18" s="115" t="s">
         <v>32</v>
       </c>
       <c r="Q18" s="115" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R18" s="116">
         <v>19052.93</v>
@@ -3105,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="120" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="W18" s="78"/>
       <c r="X18" s="67"/>
@@ -3122,17 +3134,19 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="107">
-        <v>46211.0</v>
+        <v>46212.0</v>
       </c>
       <c r="B19" s="108" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" s="109" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="110"/>
+        <v>16</v>
+      </c>
+      <c r="D19" s="110" t="s">
+        <v>17</v>
+      </c>
       <c r="E19" s="111">
-        <v>20256.52</v>
+        <v>44727.0</v>
       </c>
       <c r="F19" s="56"/>
       <c r="G19" s="103"/>
@@ -3146,7 +3160,7 @@
         <v>46182.0</v>
       </c>
       <c r="O19" s="60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P19" s="61" t="s">
         <v>16</v>
@@ -3166,7 +3180,7 @@
         <v>18336.09</v>
       </c>
       <c r="V19" s="65" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="W19" s="66"/>
       <c r="X19" s="67"/>
@@ -3182,20 +3196,20 @@
       <c r="AH19" s="67"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="107">
+      <c r="A20" s="121">
         <v>46212.0</v>
       </c>
-      <c r="B20" s="108" t="s">
-        <v>62</v>
+      <c r="B20" s="122" t="s">
+        <v>64</v>
       </c>
       <c r="C20" s="109" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="110" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="111">
-        <v>44727.0</v>
+      <c r="E20" s="123">
+        <v>11961.02</v>
       </c>
       <c r="F20" s="56"/>
       <c r="G20" s="103"/>
@@ -3209,13 +3223,13 @@
         <v>46183.0</v>
       </c>
       <c r="O20" s="72" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P20" s="97" t="s">
         <v>16</v>
       </c>
       <c r="Q20" s="97" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R20" s="75">
         <v>11145.57</v>
@@ -3229,9 +3243,9 @@
         <v>15108.93</v>
       </c>
       <c r="V20" s="77" t="s">
-        <v>64</v>
-      </c>
-      <c r="W20" s="121"/>
+        <v>66</v>
+      </c>
+      <c r="W20" s="124"/>
       <c r="X20" s="67"/>
       <c r="Y20" s="67"/>
       <c r="Z20" s="67"/>
@@ -3245,20 +3259,20 @@
       <c r="AH20" s="67"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="122">
+      <c r="A21" s="125">
         <v>46212.0</v>
       </c>
-      <c r="B21" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="109" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="109" t="s">
+      <c r="B21" s="126" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="127" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="124">
-        <v>11961.02</v>
+      <c r="E21" s="128">
+        <v>8614.76</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="103"/>
@@ -3271,8 +3285,8 @@
       <c r="N21" s="59">
         <v>46184.0</v>
       </c>
-      <c r="O21" s="125" t="s">
-        <v>66</v>
+      <c r="O21" s="129" t="s">
+        <v>68</v>
       </c>
       <c r="P21" s="61" t="s">
         <v>19</v>
@@ -3292,7 +3306,7 @@
         <v>22119.23</v>
       </c>
       <c r="V21" s="65" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="W21" s="66"/>
       <c r="X21" s="67"/>
@@ -3308,20 +3322,20 @@
       <c r="AH21" s="67"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="126">
-        <v>46212.0</v>
-      </c>
-      <c r="B22" s="127" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="128" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="128" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="129">
-        <v>8614.76</v>
+      <c r="A22" s="125">
+        <v>46213.0</v>
+      </c>
+      <c r="B22" s="126" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="127" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="127" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="128">
+        <v>9778.84</v>
       </c>
       <c r="F22" s="56"/>
       <c r="G22" s="103"/>
@@ -3335,7 +3349,7 @@
         <v>46185.0</v>
       </c>
       <c r="O22" s="72" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P22" s="73" t="s">
         <v>23</v>
@@ -3356,7 +3370,7 @@
         <v>8447.04</v>
       </c>
       <c r="V22" s="77" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="W22" s="78"/>
       <c r="X22" s="67"/>
@@ -3372,20 +3386,20 @@
       <c r="AH22" s="67"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="126">
-        <v>46213.0</v>
-      </c>
-      <c r="B23" s="127" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="128" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="128" t="s">
+      <c r="A23" s="125">
+        <v>46214.0</v>
+      </c>
+      <c r="B23" s="126" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="129">
-        <v>9778.84</v>
+      <c r="E23" s="128">
+        <v>15506.8</v>
       </c>
       <c r="F23" s="56"/>
       <c r="G23" s="103"/>
@@ -3399,7 +3413,7 @@
         <v>46188.0</v>
       </c>
       <c r="O23" s="131" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P23" s="132" t="s">
         <v>16</v>
@@ -3423,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="65" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="W23" s="66"/>
       <c r="X23" s="67"/>
@@ -3439,20 +3453,20 @@
       <c r="AH23" s="67"/>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="126">
+      <c r="A24" s="125">
         <v>46213.0</v>
       </c>
-      <c r="B24" s="127" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="128" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" s="128" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="129">
-        <v>13863.23</v>
+      <c r="B24" s="126" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="127" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="127" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="128">
+        <v>9250.54</v>
       </c>
       <c r="F24" s="56"/>
       <c r="G24" s="103"/>
@@ -3466,10 +3480,10 @@
         <v>46191.0</v>
       </c>
       <c r="O24" s="72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P24" s="73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q24" s="73" t="s">
         <v>20</v>
@@ -3486,7 +3500,7 @@
         <v>37619.36</v>
       </c>
       <c r="V24" s="105" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W24" s="78"/>
       <c r="X24" s="67"/>
@@ -3502,20 +3516,21 @@
       <c r="AH24" s="67"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="126">
-        <v>46213.0</v>
-      </c>
-      <c r="B25" s="127" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="128" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="128" t="s">
+      <c r="A25" s="91">
+        <v>46214.0</v>
+      </c>
+      <c r="B25" s="92" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="93" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="129">
-        <v>15506.8</v>
+      <c r="E25" s="94">
+        <f>30542.52-9442.65</f>
+        <v>21099.87</v>
       </c>
       <c r="F25" s="56"/>
       <c r="G25" s="103"/>
@@ -3529,7 +3544,7 @@
         <v>46197.0</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P25" s="61" t="s">
         <v>16</v>
@@ -3544,15 +3559,14 @@
         <v>39184.31</v>
       </c>
       <c r="T25" s="63">
-        <v>18905.98</v>
+        <f>S25</f>
+        <v>39184.31</v>
       </c>
       <c r="U25" s="64">
         <f t="shared" si="1"/>
-        <v>20278.33</v>
-      </c>
-      <c r="V25" s="65" t="s">
-        <v>80</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V25" s="65"/>
       <c r="W25" s="66"/>
       <c r="X25" s="67"/>
       <c r="Y25" s="67"/>
@@ -3567,20 +3581,13 @@
       <c r="AH25" s="67"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="126">
-        <v>46213.0</v>
-      </c>
-      <c r="B26" s="127" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="128" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="129">
-        <v>9250.54</v>
+      <c r="A26" s="136"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="139">
+        <f>SUM(E16:E25)</f>
+        <v>175444.5</v>
       </c>
       <c r="F26" s="56"/>
       <c r="G26" s="103"/>
@@ -3594,7 +3601,7 @@
         <v>46197.0</v>
       </c>
       <c r="O26" s="72" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P26" s="73" t="s">
         <v>19</v>
@@ -3615,7 +3622,7 @@
         <v>23672.62</v>
       </c>
       <c r="V26" s="77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="W26" s="78"/>
       <c r="X26" s="67"/>
@@ -3631,21 +3638,20 @@
       <c r="AH26" s="67"/>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="91">
-        <v>46214.0</v>
-      </c>
-      <c r="B27" s="92" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="93" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="93" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="94">
-        <f>30542.52-9442.65</f>
-        <v>21099.87</v>
+      <c r="A27" s="107">
+        <v>46216.0</v>
+      </c>
+      <c r="B27" s="108" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="111">
+        <v>2043.11</v>
       </c>
       <c r="F27" s="56"/>
       <c r="G27" s="103"/>
@@ -3659,7 +3665,7 @@
         <v>46199.0</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P27" s="61" t="s">
         <v>23</v>
@@ -3680,7 +3686,7 @@
         <v>6856.23</v>
       </c>
       <c r="V27" s="65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="W27" s="66"/>
       <c r="X27" s="67"/>
@@ -3696,13 +3702,20 @@
       <c r="AH27" s="67"/>
     </row>
     <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="136"/>
-      <c r="B28" s="137"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="139">
-        <f>SUM(E16:E27)</f>
-        <v>197093.26</v>
+      <c r="A28" s="107">
+        <v>46216.0</v>
+      </c>
+      <c r="B28" s="108" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="110" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="111">
+        <v>9458.63</v>
       </c>
       <c r="F28" s="140"/>
       <c r="G28" s="103"/>
@@ -3754,19 +3767,19 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="107">
-        <v>46216.0</v>
+        <v>46217.0</v>
       </c>
       <c r="B29" s="108" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="109" t="s">
-        <v>36</v>
+      <c r="C29" s="110" t="s">
+        <v>23</v>
       </c>
       <c r="D29" s="110" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E29" s="111">
-        <v>2043.11</v>
+        <v>11945.81</v>
       </c>
       <c r="F29" s="140"/>
       <c r="G29" s="103"/>
@@ -3818,19 +3831,19 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="107">
-        <v>46216.0</v>
+        <v>46218.0</v>
       </c>
       <c r="B30" s="108" t="s">
         <v>90</v>
       </c>
       <c r="C30" s="110" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D30" s="110" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="111">
-        <v>9458.63</v>
+        <v>24772.6</v>
       </c>
       <c r="F30" s="83"/>
       <c r="G30" s="103"/>
@@ -3883,7 +3896,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="107">
-        <v>46217.0</v>
+        <v>46219.0</v>
       </c>
       <c r="B31" s="108" t="s">
         <v>92</v>
@@ -3895,7 +3908,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="111">
-        <v>11945.81</v>
+        <v>15683.1</v>
       </c>
       <c r="F31" s="83"/>
       <c r="G31" s="103"/>
@@ -3946,20 +3959,20 @@
       <c r="AH31" s="67"/>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="107">
-        <v>46218.0</v>
-      </c>
-      <c r="B32" s="108" t="s">
+      <c r="A32" s="121">
+        <v>46220.0</v>
+      </c>
+      <c r="B32" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="110" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="110" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="111">
-        <v>24772.6</v>
+      <c r="C32" s="109" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="123">
+        <v>19734.11</v>
       </c>
       <c r="F32" s="83"/>
       <c r="G32" s="103"/>
@@ -4010,20 +4023,13 @@
       <c r="AH32" s="67"/>
     </row>
     <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="107">
-        <v>46219.0</v>
-      </c>
-      <c r="B33" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="D33" s="110" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="111">
-        <v>15683.1</v>
+      <c r="A33" s="136"/>
+      <c r="B33" s="137"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="139">
+        <f>SUM(E27:E32)</f>
+        <v>83637.36</v>
       </c>
       <c r="F33" s="83"/>
       <c r="G33" s="103"/>
@@ -4037,10 +4043,10 @@
         <v>46205.0</v>
       </c>
       <c r="O33" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P33" s="61" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q33" s="61" t="s">
         <v>17</v>
@@ -4058,7 +4064,7 @@
         <v>9729.9</v>
       </c>
       <c r="V33" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W33" s="66"/>
       <c r="X33" s="67"/>
@@ -4074,21 +4080,13 @@
       <c r="AH33" s="67"/>
     </row>
     <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="122">
-        <v>46220.0</v>
-      </c>
-      <c r="B34" s="123" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="124">
-        <v>19734.11</v>
-      </c>
+      <c r="A34" s="142">
+        <v>46223.0</v>
+      </c>
+      <c r="B34" s="143"/>
+      <c r="C34" s="144"/>
+      <c r="D34" s="144"/>
+      <c r="E34" s="145"/>
       <c r="F34" s="83"/>
       <c r="G34" s="103"/>
       <c r="H34" s="103"/>
@@ -4097,11 +4095,11 @@
       <c r="K34" s="103"/>
       <c r="L34" s="104"/>
       <c r="M34" s="58"/>
-      <c r="N34" s="142">
+      <c r="N34" s="146">
         <v>46203.0</v>
       </c>
       <c r="O34" s="114" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P34" s="115" t="s">
         <v>16</v>
@@ -4109,7 +4107,7 @@
       <c r="Q34" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="R34" s="143">
+      <c r="R34" s="147">
         <v>13273.56</v>
       </c>
       <c r="S34" s="118">
@@ -4139,13 +4137,20 @@
       <c r="AH34" s="67"/>
     </row>
     <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="136"/>
-      <c r="B35" s="137"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="139">
-        <f>SUM(E29:E34)</f>
-        <v>83637.36</v>
+      <c r="A35" s="121">
+        <v>46224.0</v>
+      </c>
+      <c r="B35" s="122" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="109" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="109" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="123">
+        <v>50480.77</v>
       </c>
       <c r="F35" s="83"/>
       <c r="G35" s="103"/>
@@ -4155,7 +4160,7 @@
       <c r="K35" s="103"/>
       <c r="L35" s="104"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="144">
+      <c r="N35" s="148">
         <v>46202.0</v>
       </c>
       <c r="O35" s="131" t="s">
@@ -4167,7 +4172,7 @@
       <c r="Q35" s="132" t="s">
         <v>20</v>
       </c>
-      <c r="R35" s="145">
+      <c r="R35" s="149">
         <v>19583.29</v>
       </c>
       <c r="S35" s="134">
@@ -4182,7 +4187,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V35" s="146"/>
+      <c r="V35" s="150"/>
       <c r="W35" s="66"/>
       <c r="X35" s="67"/>
       <c r="Y35" s="67"/>
@@ -4197,13 +4202,14 @@
       <c r="AH35" s="67"/>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="147">
-        <v>46223.0</v>
-      </c>
-      <c r="B36" s="148"/>
-      <c r="C36" s="149"/>
-      <c r="D36" s="149"/>
-      <c r="E36" s="150"/>
+      <c r="A36" s="136"/>
+      <c r="B36" s="137"/>
+      <c r="C36" s="138"/>
+      <c r="D36" s="138"/>
+      <c r="E36" s="139">
+        <f>E34+E35</f>
+        <v>50480.77</v>
+      </c>
       <c r="F36" s="83"/>
       <c r="G36" s="103"/>
       <c r="H36" s="103"/>
@@ -4253,21 +4259,13 @@
       <c r="AH36" s="67"/>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="122">
-        <v>46224.0</v>
-      </c>
-      <c r="B37" s="123" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="109" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="124">
-        <v>50480.77</v>
-      </c>
+      <c r="A37" s="142">
+        <v>46230.0</v>
+      </c>
+      <c r="B37" s="143"/>
+      <c r="C37" s="144"/>
+      <c r="D37" s="144"/>
+      <c r="E37" s="145"/>
       <c r="F37" s="83"/>
       <c r="G37" s="103"/>
       <c r="H37" s="103"/>
@@ -4280,7 +4278,7 @@
         <v>46204.0</v>
       </c>
       <c r="O37" s="60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P37" s="61" t="s">
         <v>16</v>
@@ -4303,7 +4301,7 @@
         <v>11398.99</v>
       </c>
       <c r="V37" s="65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="W37" s="66"/>
       <c r="X37" s="67"/>
@@ -4319,13 +4317,20 @@
       <c r="AH37" s="67"/>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="136"/>
-      <c r="B38" s="137"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="139">
-        <f>E36+E37</f>
-        <v>50480.77</v>
+      <c r="A38" s="121">
+        <v>46232.0</v>
+      </c>
+      <c r="B38" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="109" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="109" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="123">
+        <v>38024.73</v>
       </c>
       <c r="F38" s="83"/>
       <c r="G38" s="103"/>
@@ -4375,13 +4380,14 @@
       <c r="AH38" s="67"/>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="147">
-        <v>46230.0</v>
-      </c>
-      <c r="B39" s="148"/>
-      <c r="C39" s="149"/>
-      <c r="D39" s="149"/>
-      <c r="E39" s="150"/>
+      <c r="A39" s="136"/>
+      <c r="B39" s="137"/>
+      <c r="C39" s="138"/>
+      <c r="D39" s="138"/>
+      <c r="E39" s="139">
+        <f>E37+E38</f>
+        <v>38024.73</v>
+      </c>
       <c r="F39" s="83"/>
       <c r="G39" s="103"/>
       <c r="H39" s="103"/>
@@ -4431,21 +4437,13 @@
       <c r="AH39" s="67"/>
     </row>
     <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="122">
-        <v>46232.0</v>
-      </c>
-      <c r="B40" s="123" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" s="109" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="124">
-        <v>38024.73</v>
-      </c>
+      <c r="A40" s="142">
+        <v>46237.0</v>
+      </c>
+      <c r="B40" s="143"/>
+      <c r="C40" s="144"/>
+      <c r="D40" s="144"/>
+      <c r="E40" s="145"/>
       <c r="F40" s="83"/>
       <c r="G40" s="103"/>
       <c r="H40" s="103"/>
@@ -4458,7 +4456,7 @@
         <v>46205.0</v>
       </c>
       <c r="O40" s="160" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P40" s="161" t="s">
         <v>32</v>
@@ -4493,13 +4491,20 @@
       <c r="AH40" s="67"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="136"/>
-      <c r="B41" s="137"/>
-      <c r="C41" s="138"/>
-      <c r="D41" s="138"/>
-      <c r="E41" s="139">
-        <f>E39+E40</f>
-        <v>38024.73</v>
+      <c r="A41" s="121">
+        <v>46239.0</v>
+      </c>
+      <c r="B41" s="122" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="109" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="109" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="123">
+        <v>18059.08</v>
       </c>
       <c r="F41" s="83"/>
       <c r="G41" s="103"/>
@@ -4516,7 +4521,7 @@
         <v>113</v>
       </c>
       <c r="P41" s="166" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q41" s="167" t="s">
         <v>17</v>
@@ -4550,13 +4555,14 @@
       <c r="AH41" s="67"/>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="147">
-        <v>46237.0</v>
-      </c>
-      <c r="B42" s="148"/>
-      <c r="C42" s="149"/>
-      <c r="D42" s="149"/>
-      <c r="E42" s="150"/>
+      <c r="A42" s="136"/>
+      <c r="B42" s="137"/>
+      <c r="C42" s="138"/>
+      <c r="D42" s="138"/>
+      <c r="E42" s="139">
+        <f>E40+E41</f>
+        <v>18059.08</v>
+      </c>
       <c r="F42" s="83"/>
       <c r="G42" s="103"/>
       <c r="H42" s="103"/>
@@ -4572,7 +4578,7 @@
         <v>114</v>
       </c>
       <c r="P42" s="171" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q42" s="172" t="s">
         <v>17</v>
@@ -4605,20 +4611,20 @@
       <c r="AH42" s="67"/>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="122">
-        <v>46239.0</v>
-      </c>
-      <c r="B43" s="123" t="s">
+      <c r="A43" s="142">
+        <v>46244.0</v>
+      </c>
+      <c r="B43" s="174" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="109" t="s">
+      <c r="C43" s="175" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="124">
-        <v>18059.08</v>
+      <c r="D43" s="175" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="176">
+        <v>26195.16</v>
       </c>
       <c r="F43" s="83"/>
       <c r="G43" s="103"/>
@@ -4668,14 +4674,13 @@
       <c r="AH43" s="67"/>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="136"/>
-      <c r="B44" s="137"/>
-      <c r="C44" s="138"/>
-      <c r="D44" s="138"/>
-      <c r="E44" s="139">
-        <f>E42+E43</f>
-        <v>18059.08</v>
-      </c>
+      <c r="A44" s="121">
+        <v>46248.0</v>
+      </c>
+      <c r="B44" s="177"/>
+      <c r="C44" s="178"/>
+      <c r="D44" s="178"/>
+      <c r="E44" s="179"/>
       <c r="F44" s="83"/>
       <c r="G44" s="103"/>
       <c r="H44" s="103"/>
@@ -4720,19 +4725,12 @@
       <c r="AH44" s="67"/>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="147">
-        <v>46244.0</v>
-      </c>
-      <c r="B45" s="174" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="175" t="s">
-        <v>23</v>
-      </c>
-      <c r="D45" s="175" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="176">
+      <c r="A45" s="136"/>
+      <c r="B45" s="137"/>
+      <c r="C45" s="138"/>
+      <c r="D45" s="138"/>
+      <c r="E45" s="139">
+        <f>E43+E44</f>
         <v>26195.16</v>
       </c>
       <c r="F45" s="83"/>
@@ -4743,10 +4741,10 @@
       <c r="K45" s="103"/>
       <c r="L45" s="104"/>
       <c r="M45" s="58"/>
-      <c r="N45" s="177"/>
-      <c r="O45" s="177"/>
-      <c r="P45" s="177"/>
-      <c r="Q45" s="177"/>
+      <c r="N45" s="180"/>
+      <c r="O45" s="180"/>
+      <c r="P45" s="180"/>
+      <c r="Q45" s="180"/>
       <c r="R45" s="90"/>
       <c r="S45" s="90"/>
       <c r="T45" s="90"/>
@@ -4754,7 +4752,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V45" s="178"/>
+      <c r="V45" s="181"/>
       <c r="W45" s="66"/>
       <c r="X45" s="67"/>
       <c r="Y45" s="67"/>
@@ -4769,13 +4767,11 @@
       <c r="AH45" s="67"/>
     </row>
     <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="122">
-        <v>46248.0</v>
-      </c>
-      <c r="B46" s="179"/>
-      <c r="C46" s="180"/>
-      <c r="D46" s="180"/>
-      <c r="E46" s="181"/>
+      <c r="A46" s="182"/>
+      <c r="B46" s="183"/>
+      <c r="C46" s="184"/>
+      <c r="D46" s="184"/>
+      <c r="E46" s="184"/>
       <c r="F46" s="83"/>
       <c r="G46" s="103"/>
       <c r="H46" s="103"/>
@@ -4784,10 +4780,10 @@
       <c r="K46" s="103"/>
       <c r="L46" s="104"/>
       <c r="M46" s="58"/>
-      <c r="N46" s="182"/>
-      <c r="O46" s="182"/>
-      <c r="P46" s="182"/>
-      <c r="Q46" s="182"/>
+      <c r="N46" s="185"/>
+      <c r="O46" s="185"/>
+      <c r="P46" s="185"/>
+      <c r="Q46" s="185"/>
       <c r="R46" s="98"/>
       <c r="S46" s="98"/>
       <c r="T46" s="98"/>
@@ -4810,14 +4806,11 @@
       <c r="AH46" s="67"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="136"/>
-      <c r="B47" s="137"/>
-      <c r="C47" s="138"/>
-      <c r="D47" s="138"/>
-      <c r="E47" s="139">
-        <f>E45+E46</f>
-        <v>26195.16</v>
-      </c>
+      <c r="A47" s="186"/>
+      <c r="B47" s="178"/>
+      <c r="C47" s="178"/>
+      <c r="D47" s="178"/>
+      <c r="E47" s="187"/>
       <c r="F47" s="83"/>
       <c r="G47" s="103"/>
       <c r="H47" s="103"/>
@@ -4826,10 +4819,10 @@
       <c r="K47" s="103"/>
       <c r="L47" s="104"/>
       <c r="M47" s="58"/>
-      <c r="N47" s="177"/>
-      <c r="O47" s="177"/>
-      <c r="P47" s="177"/>
-      <c r="Q47" s="177"/>
+      <c r="N47" s="180"/>
+      <c r="O47" s="180"/>
+      <c r="P47" s="180"/>
+      <c r="Q47" s="180"/>
       <c r="R47" s="90"/>
       <c r="S47" s="90"/>
       <c r="T47" s="90"/>
@@ -4837,7 +4830,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V47" s="178"/>
+      <c r="V47" s="181"/>
       <c r="W47" s="66"/>
       <c r="X47" s="67"/>
       <c r="Y47" s="67"/>
@@ -4852,11 +4845,11 @@
       <c r="AH47" s="67"/>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="183"/>
-      <c r="B48" s="184"/>
-      <c r="C48" s="185"/>
-      <c r="D48" s="185"/>
-      <c r="E48" s="185"/>
+      <c r="A48" s="186"/>
+      <c r="B48" s="178"/>
+      <c r="C48" s="178"/>
+      <c r="D48" s="178"/>
+      <c r="E48" s="188"/>
       <c r="F48" s="83"/>
       <c r="G48" s="103"/>
       <c r="H48" s="103"/>
@@ -4865,10 +4858,10 @@
       <c r="K48" s="103"/>
       <c r="L48" s="104"/>
       <c r="M48" s="58"/>
-      <c r="N48" s="182"/>
-      <c r="O48" s="182"/>
-      <c r="P48" s="182"/>
-      <c r="Q48" s="182"/>
+      <c r="N48" s="185"/>
+      <c r="O48" s="185"/>
+      <c r="P48" s="185"/>
+      <c r="Q48" s="185"/>
       <c r="R48" s="98"/>
       <c r="S48" s="98"/>
       <c r="T48" s="98"/>
@@ -4877,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="163"/>
-      <c r="W48" s="186"/>
+      <c r="W48" s="189"/>
       <c r="X48" s="67"/>
       <c r="Y48" s="67"/>
       <c r="Z48" s="67"/>
@@ -4891,29 +4884,29 @@
       <c r="AH48" s="67"/>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="187"/>
-      <c r="B49" s="180"/>
-      <c r="C49" s="180"/>
-      <c r="D49" s="180"/>
+      <c r="A49" s="186"/>
+      <c r="B49" s="178"/>
+      <c r="C49" s="178"/>
+      <c r="D49" s="178"/>
       <c r="E49" s="188"/>
-      <c r="F49" s="189"/>
+      <c r="F49" s="190"/>
       <c r="G49" s="67"/>
       <c r="H49" s="67"/>
       <c r="I49" s="67"/>
       <c r="J49" s="67"/>
-      <c r="K49" s="190"/>
-      <c r="L49" s="191"/>
+      <c r="K49" s="191"/>
+      <c r="L49" s="192"/>
       <c r="M49" s="58"/>
-      <c r="N49" s="177"/>
-      <c r="O49" s="177"/>
-      <c r="P49" s="177"/>
-      <c r="Q49" s="177"/>
+      <c r="N49" s="180"/>
+      <c r="O49" s="180"/>
+      <c r="P49" s="180"/>
+      <c r="Q49" s="180"/>
       <c r="R49" s="90"/>
       <c r="S49" s="90"/>
       <c r="T49" s="90"/>
       <c r="U49" s="90"/>
-      <c r="V49" s="178"/>
-      <c r="W49" s="192"/>
+      <c r="V49" s="181"/>
+      <c r="W49" s="193"/>
       <c r="X49" s="67"/>
       <c r="Y49" s="67"/>
       <c r="Z49" s="67"/>
@@ -4927,29 +4920,29 @@
       <c r="AH49" s="67"/>
     </row>
     <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="187"/>
-      <c r="B50" s="180"/>
-      <c r="C50" s="180"/>
-      <c r="D50" s="180"/>
-      <c r="E50" s="193"/>
+      <c r="A50" s="186"/>
+      <c r="B50" s="178"/>
+      <c r="C50" s="178"/>
+      <c r="D50" s="178"/>
+      <c r="E50" s="188"/>
       <c r="F50" s="83"/>
       <c r="G50" s="67"/>
       <c r="H50" s="67"/>
       <c r="I50" s="67"/>
       <c r="J50" s="67"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="191"/>
+      <c r="K50" s="191"/>
+      <c r="L50" s="192"/>
       <c r="M50" s="58"/>
-      <c r="N50" s="182"/>
-      <c r="O50" s="182"/>
-      <c r="P50" s="182"/>
-      <c r="Q50" s="182"/>
+      <c r="N50" s="185"/>
+      <c r="O50" s="185"/>
+      <c r="P50" s="185"/>
+      <c r="Q50" s="185"/>
       <c r="R50" s="98"/>
       <c r="S50" s="98"/>
       <c r="T50" s="98"/>
       <c r="U50" s="98"/>
       <c r="V50" s="163"/>
-      <c r="W50" s="186"/>
+      <c r="W50" s="189"/>
       <c r="X50" s="67"/>
       <c r="Y50" s="67"/>
       <c r="Z50" s="67"/>
@@ -4963,29 +4956,29 @@
       <c r="AH50" s="67"/>
     </row>
     <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="187"/>
-      <c r="B51" s="180"/>
-      <c r="C51" s="180"/>
-      <c r="D51" s="180"/>
-      <c r="E51" s="193"/>
+      <c r="A51" s="186"/>
+      <c r="B51" s="178"/>
+      <c r="C51" s="178"/>
+      <c r="D51" s="178"/>
+      <c r="E51" s="188"/>
       <c r="F51" s="83"/>
       <c r="G51" s="67"/>
       <c r="H51" s="67"/>
       <c r="I51" s="67"/>
       <c r="J51" s="67"/>
-      <c r="K51" s="190"/>
-      <c r="L51" s="191"/>
+      <c r="K51" s="191"/>
+      <c r="L51" s="192"/>
       <c r="M51" s="58"/>
-      <c r="N51" s="177"/>
-      <c r="O51" s="177"/>
-      <c r="P51" s="177"/>
-      <c r="Q51" s="177"/>
+      <c r="N51" s="180"/>
+      <c r="O51" s="180"/>
+      <c r="P51" s="180"/>
+      <c r="Q51" s="180"/>
       <c r="R51" s="90"/>
       <c r="S51" s="90"/>
       <c r="T51" s="90"/>
       <c r="U51" s="90"/>
-      <c r="V51" s="178"/>
-      <c r="W51" s="192"/>
+      <c r="V51" s="181"/>
+      <c r="W51" s="193"/>
       <c r="X51" s="67"/>
       <c r="Y51" s="67"/>
       <c r="Z51" s="67"/>
@@ -4999,29 +4992,29 @@
       <c r="AH51" s="67"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="187"/>
-      <c r="B52" s="180"/>
-      <c r="C52" s="180"/>
-      <c r="D52" s="180"/>
-      <c r="E52" s="193"/>
+      <c r="A52" s="194"/>
+      <c r="B52" s="195"/>
+      <c r="C52" s="195"/>
+      <c r="D52" s="195"/>
+      <c r="E52" s="196"/>
       <c r="F52" s="83"/>
       <c r="G52" s="67"/>
       <c r="H52" s="67"/>
       <c r="I52" s="67"/>
       <c r="J52" s="67"/>
-      <c r="K52" s="190"/>
-      <c r="L52" s="191"/>
+      <c r="K52" s="191"/>
+      <c r="L52" s="192"/>
       <c r="M52" s="58"/>
-      <c r="N52" s="182"/>
-      <c r="O52" s="182"/>
-      <c r="P52" s="182"/>
-      <c r="Q52" s="182"/>
+      <c r="N52" s="185"/>
+      <c r="O52" s="185"/>
+      <c r="P52" s="185"/>
+      <c r="Q52" s="185"/>
       <c r="R52" s="98"/>
       <c r="S52" s="98"/>
       <c r="T52" s="98"/>
       <c r="U52" s="98"/>
       <c r="V52" s="163"/>
-      <c r="W52" s="186"/>
+      <c r="W52" s="189"/>
       <c r="X52" s="67"/>
       <c r="Y52" s="67"/>
       <c r="Z52" s="67"/>
@@ -5035,29 +5028,29 @@
       <c r="AH52" s="67"/>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="187"/>
-      <c r="B53" s="180"/>
-      <c r="C53" s="180"/>
-      <c r="D53" s="180"/>
-      <c r="E53" s="193"/>
+      <c r="A53" s="197"/>
+      <c r="B53" s="197"/>
+      <c r="C53" s="197"/>
+      <c r="D53" s="197"/>
+      <c r="E53" s="198"/>
       <c r="F53" s="83"/>
       <c r="G53" s="67"/>
       <c r="H53" s="67"/>
       <c r="I53" s="67"/>
       <c r="J53" s="67"/>
-      <c r="K53" s="190"/>
-      <c r="L53" s="191"/>
+      <c r="K53" s="191"/>
+      <c r="L53" s="192"/>
       <c r="M53" s="58"/>
-      <c r="N53" s="177"/>
-      <c r="O53" s="177"/>
-      <c r="P53" s="177"/>
-      <c r="Q53" s="177"/>
+      <c r="N53" s="180"/>
+      <c r="O53" s="180"/>
+      <c r="P53" s="180"/>
+      <c r="Q53" s="180"/>
       <c r="R53" s="90"/>
       <c r="S53" s="90"/>
       <c r="T53" s="90"/>
       <c r="U53" s="90"/>
-      <c r="V53" s="178"/>
-      <c r="W53" s="192"/>
+      <c r="V53" s="181"/>
+      <c r="W53" s="193"/>
       <c r="X53" s="67"/>
       <c r="Y53" s="67"/>
       <c r="Z53" s="67"/>
@@ -5071,29 +5064,29 @@
       <c r="AH53" s="67"/>
     </row>
     <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="194"/>
-      <c r="B54" s="195"/>
-      <c r="C54" s="195"/>
-      <c r="D54" s="195"/>
-      <c r="E54" s="196"/>
+      <c r="A54" s="197"/>
+      <c r="B54" s="197"/>
+      <c r="C54" s="197"/>
+      <c r="D54" s="197"/>
+      <c r="E54" s="198"/>
       <c r="F54" s="83"/>
       <c r="G54" s="67"/>
       <c r="H54" s="67"/>
       <c r="I54" s="67"/>
       <c r="J54" s="67"/>
-      <c r="K54" s="190"/>
-      <c r="L54" s="191"/>
+      <c r="K54" s="191"/>
+      <c r="L54" s="192"/>
       <c r="M54" s="58"/>
-      <c r="N54" s="182"/>
-      <c r="O54" s="182"/>
-      <c r="P54" s="182"/>
-      <c r="Q54" s="182"/>
+      <c r="N54" s="185"/>
+      <c r="O54" s="185"/>
+      <c r="P54" s="185"/>
+      <c r="Q54" s="185"/>
       <c r="R54" s="98"/>
       <c r="S54" s="98"/>
       <c r="T54" s="98"/>
       <c r="U54" s="98"/>
       <c r="V54" s="163"/>
-      <c r="W54" s="186"/>
+      <c r="W54" s="189"/>
       <c r="X54" s="67"/>
       <c r="Y54" s="67"/>
       <c r="Z54" s="67"/>
@@ -5117,19 +5110,19 @@
       <c r="H55" s="67"/>
       <c r="I55" s="67"/>
       <c r="J55" s="67"/>
-      <c r="K55" s="190"/>
-      <c r="L55" s="191"/>
+      <c r="K55" s="191"/>
+      <c r="L55" s="192"/>
       <c r="M55" s="58"/>
-      <c r="N55" s="177"/>
-      <c r="O55" s="177"/>
-      <c r="P55" s="177"/>
-      <c r="Q55" s="177"/>
+      <c r="N55" s="180"/>
+      <c r="O55" s="180"/>
+      <c r="P55" s="180"/>
+      <c r="Q55" s="180"/>
       <c r="R55" s="90"/>
       <c r="S55" s="90"/>
       <c r="T55" s="90"/>
       <c r="U55" s="90"/>
-      <c r="V55" s="178"/>
-      <c r="W55" s="192"/>
+      <c r="V55" s="181"/>
+      <c r="W55" s="193"/>
       <c r="X55" s="67"/>
       <c r="Y55" s="67"/>
       <c r="Z55" s="67"/>
@@ -5153,19 +5146,19 @@
       <c r="H56" s="67"/>
       <c r="I56" s="67"/>
       <c r="J56" s="67"/>
-      <c r="K56" s="190"/>
-      <c r="L56" s="191"/>
+      <c r="K56" s="191"/>
+      <c r="L56" s="192"/>
       <c r="M56" s="58"/>
-      <c r="N56" s="182"/>
-      <c r="O56" s="182"/>
-      <c r="P56" s="182"/>
-      <c r="Q56" s="182"/>
+      <c r="N56" s="185"/>
+      <c r="O56" s="185"/>
+      <c r="P56" s="185"/>
+      <c r="Q56" s="185"/>
       <c r="R56" s="98"/>
       <c r="S56" s="98"/>
       <c r="T56" s="98"/>
       <c r="U56" s="98"/>
       <c r="V56" s="163"/>
-      <c r="W56" s="186"/>
+      <c r="W56" s="189"/>
       <c r="X56" s="67"/>
       <c r="Y56" s="67"/>
       <c r="Z56" s="67"/>
@@ -5189,19 +5182,19 @@
       <c r="H57" s="67"/>
       <c r="I57" s="67"/>
       <c r="J57" s="67"/>
-      <c r="K57" s="190"/>
-      <c r="L57" s="191"/>
+      <c r="K57" s="191"/>
+      <c r="L57" s="192"/>
       <c r="M57" s="58"/>
-      <c r="N57" s="177"/>
-      <c r="O57" s="177"/>
-      <c r="P57" s="177"/>
-      <c r="Q57" s="177"/>
+      <c r="N57" s="180"/>
+      <c r="O57" s="180"/>
+      <c r="P57" s="180"/>
+      <c r="Q57" s="180"/>
       <c r="R57" s="90"/>
       <c r="S57" s="90"/>
       <c r="T57" s="90"/>
       <c r="U57" s="90"/>
-      <c r="V57" s="178"/>
-      <c r="W57" s="192"/>
+      <c r="V57" s="181"/>
+      <c r="W57" s="193"/>
       <c r="X57" s="67"/>
       <c r="Y57" s="67"/>
       <c r="Z57" s="67"/>
@@ -5225,19 +5218,19 @@
       <c r="H58" s="67"/>
       <c r="I58" s="67"/>
       <c r="J58" s="67"/>
-      <c r="K58" s="190"/>
-      <c r="L58" s="191"/>
+      <c r="K58" s="191"/>
+      <c r="L58" s="192"/>
       <c r="M58" s="58"/>
-      <c r="N58" s="182"/>
-      <c r="O58" s="182"/>
-      <c r="P58" s="182"/>
-      <c r="Q58" s="182"/>
+      <c r="N58" s="185"/>
+      <c r="O58" s="185"/>
+      <c r="P58" s="185"/>
+      <c r="Q58" s="185"/>
       <c r="R58" s="98"/>
       <c r="S58" s="98"/>
       <c r="T58" s="98"/>
       <c r="U58" s="98"/>
       <c r="V58" s="163"/>
-      <c r="W58" s="186"/>
+      <c r="W58" s="189"/>
       <c r="X58" s="67"/>
       <c r="Y58" s="67"/>
       <c r="Z58" s="67"/>
@@ -5261,19 +5254,19 @@
       <c r="H59" s="67"/>
       <c r="I59" s="67"/>
       <c r="J59" s="67"/>
-      <c r="K59" s="190"/>
-      <c r="L59" s="191"/>
+      <c r="K59" s="191"/>
+      <c r="L59" s="192"/>
       <c r="M59" s="58"/>
-      <c r="N59" s="177"/>
-      <c r="O59" s="177"/>
-      <c r="P59" s="177"/>
-      <c r="Q59" s="177"/>
+      <c r="N59" s="180"/>
+      <c r="O59" s="180"/>
+      <c r="P59" s="180"/>
+      <c r="Q59" s="180"/>
       <c r="R59" s="90"/>
       <c r="S59" s="90"/>
       <c r="T59" s="90"/>
       <c r="U59" s="90"/>
-      <c r="V59" s="178"/>
-      <c r="W59" s="192"/>
+      <c r="V59" s="181"/>
+      <c r="W59" s="193"/>
       <c r="X59" s="67"/>
       <c r="Y59" s="67"/>
       <c r="Z59" s="67"/>
@@ -5297,13 +5290,13 @@
       <c r="H60" s="67"/>
       <c r="I60" s="67"/>
       <c r="J60" s="67"/>
-      <c r="K60" s="190"/>
-      <c r="L60" s="191"/>
+      <c r="K60" s="191"/>
+      <c r="L60" s="192"/>
       <c r="M60" s="58"/>
-      <c r="N60" s="182"/>
-      <c r="O60" s="182"/>
-      <c r="P60" s="182"/>
-      <c r="Q60" s="182"/>
+      <c r="N60" s="185"/>
+      <c r="O60" s="185"/>
+      <c r="P60" s="185"/>
+      <c r="Q60" s="185"/>
       <c r="R60" s="98"/>
       <c r="S60" s="98"/>
       <c r="T60" s="98"/>
@@ -5333,18 +5326,18 @@
       <c r="H61" s="67"/>
       <c r="I61" s="67"/>
       <c r="J61" s="67"/>
-      <c r="K61" s="190"/>
-      <c r="L61" s="191"/>
+      <c r="K61" s="191"/>
+      <c r="L61" s="192"/>
       <c r="M61" s="58"/>
-      <c r="N61" s="177"/>
-      <c r="O61" s="177"/>
-      <c r="P61" s="177"/>
-      <c r="Q61" s="177"/>
+      <c r="N61" s="180"/>
+      <c r="O61" s="180"/>
+      <c r="P61" s="180"/>
+      <c r="Q61" s="180"/>
       <c r="R61" s="90"/>
       <c r="S61" s="90"/>
       <c r="T61" s="90"/>
       <c r="U61" s="90"/>
-      <c r="V61" s="178"/>
+      <c r="V61" s="181"/>
       <c r="W61" s="200"/>
       <c r="X61" s="67"/>
       <c r="Y61" s="67"/>
@@ -5369,13 +5362,13 @@
       <c r="H62" s="67"/>
       <c r="I62" s="67"/>
       <c r="J62" s="67"/>
-      <c r="K62" s="190"/>
-      <c r="L62" s="191"/>
+      <c r="K62" s="191"/>
+      <c r="L62" s="192"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="182"/>
-      <c r="O62" s="182"/>
-      <c r="P62" s="182"/>
-      <c r="Q62" s="182"/>
+      <c r="N62" s="185"/>
+      <c r="O62" s="185"/>
+      <c r="P62" s="185"/>
+      <c r="Q62" s="185"/>
       <c r="R62" s="98"/>
       <c r="S62" s="98"/>
       <c r="T62" s="98"/>
@@ -5405,18 +5398,18 @@
       <c r="H63" s="67"/>
       <c r="I63" s="67"/>
       <c r="J63" s="67"/>
-      <c r="K63" s="190"/>
-      <c r="L63" s="191"/>
+      <c r="K63" s="191"/>
+      <c r="L63" s="192"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="177"/>
-      <c r="O63" s="177"/>
-      <c r="P63" s="177"/>
-      <c r="Q63" s="177"/>
+      <c r="N63" s="180"/>
+      <c r="O63" s="180"/>
+      <c r="P63" s="180"/>
+      <c r="Q63" s="180"/>
       <c r="R63" s="90"/>
       <c r="S63" s="90"/>
       <c r="T63" s="90"/>
       <c r="U63" s="90"/>
-      <c r="V63" s="178"/>
+      <c r="V63" s="181"/>
       <c r="W63" s="200"/>
       <c r="X63" s="67"/>
       <c r="Y63" s="67"/>
@@ -5441,13 +5434,13 @@
       <c r="H64" s="67"/>
       <c r="I64" s="67"/>
       <c r="J64" s="67"/>
-      <c r="K64" s="190"/>
-      <c r="L64" s="191"/>
+      <c r="K64" s="191"/>
+      <c r="L64" s="192"/>
       <c r="M64" s="58"/>
-      <c r="N64" s="182"/>
-      <c r="O64" s="182"/>
-      <c r="P64" s="182"/>
-      <c r="Q64" s="182"/>
+      <c r="N64" s="185"/>
+      <c r="O64" s="185"/>
+      <c r="P64" s="185"/>
+      <c r="Q64" s="185"/>
       <c r="R64" s="98"/>
       <c r="S64" s="98"/>
       <c r="T64" s="98"/>
@@ -5477,18 +5470,18 @@
       <c r="H65" s="67"/>
       <c r="I65" s="67"/>
       <c r="J65" s="67"/>
-      <c r="K65" s="190"/>
-      <c r="L65" s="191"/>
+      <c r="K65" s="191"/>
+      <c r="L65" s="192"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="177"/>
-      <c r="O65" s="177"/>
-      <c r="P65" s="177"/>
-      <c r="Q65" s="177"/>
+      <c r="N65" s="180"/>
+      <c r="O65" s="180"/>
+      <c r="P65" s="180"/>
+      <c r="Q65" s="180"/>
       <c r="R65" s="90"/>
       <c r="S65" s="90"/>
       <c r="T65" s="90"/>
       <c r="U65" s="90"/>
-      <c r="V65" s="178"/>
+      <c r="V65" s="181"/>
       <c r="W65" s="200"/>
       <c r="X65" s="67"/>
       <c r="Y65" s="67"/>
@@ -5513,13 +5506,13 @@
       <c r="H66" s="67"/>
       <c r="I66" s="67"/>
       <c r="J66" s="67"/>
-      <c r="K66" s="190"/>
-      <c r="L66" s="191"/>
+      <c r="K66" s="191"/>
+      <c r="L66" s="192"/>
       <c r="M66" s="58"/>
-      <c r="N66" s="182"/>
-      <c r="O66" s="182"/>
-      <c r="P66" s="182"/>
-      <c r="Q66" s="182"/>
+      <c r="N66" s="185"/>
+      <c r="O66" s="185"/>
+      <c r="P66" s="185"/>
+      <c r="Q66" s="185"/>
       <c r="R66" s="98"/>
       <c r="S66" s="98"/>
       <c r="T66" s="98"/>
@@ -5549,18 +5542,18 @@
       <c r="H67" s="67"/>
       <c r="I67" s="67"/>
       <c r="J67" s="67"/>
-      <c r="K67" s="190"/>
-      <c r="L67" s="191"/>
+      <c r="K67" s="191"/>
+      <c r="L67" s="192"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="177"/>
-      <c r="O67" s="177"/>
-      <c r="P67" s="177"/>
-      <c r="Q67" s="177"/>
+      <c r="N67" s="180"/>
+      <c r="O67" s="180"/>
+      <c r="P67" s="180"/>
+      <c r="Q67" s="180"/>
       <c r="R67" s="90"/>
       <c r="S67" s="90"/>
       <c r="T67" s="90"/>
       <c r="U67" s="90"/>
-      <c r="V67" s="178"/>
+      <c r="V67" s="181"/>
       <c r="W67" s="200"/>
       <c r="X67" s="67"/>
       <c r="Y67" s="67"/>
@@ -5585,13 +5578,13 @@
       <c r="H68" s="67"/>
       <c r="I68" s="67"/>
       <c r="J68" s="67"/>
-      <c r="K68" s="190"/>
-      <c r="L68" s="191"/>
+      <c r="K68" s="191"/>
+      <c r="L68" s="192"/>
       <c r="M68" s="58"/>
-      <c r="N68" s="182"/>
-      <c r="O68" s="182"/>
-      <c r="P68" s="182"/>
-      <c r="Q68" s="182"/>
+      <c r="N68" s="185"/>
+      <c r="O68" s="185"/>
+      <c r="P68" s="185"/>
+      <c r="Q68" s="185"/>
       <c r="R68" s="98"/>
       <c r="S68" s="98"/>
       <c r="T68" s="98"/>
@@ -5621,18 +5614,18 @@
       <c r="H69" s="67"/>
       <c r="I69" s="67"/>
       <c r="J69" s="67"/>
-      <c r="K69" s="190"/>
-      <c r="L69" s="191"/>
+      <c r="K69" s="191"/>
+      <c r="L69" s="192"/>
       <c r="M69" s="58"/>
-      <c r="N69" s="177"/>
-      <c r="O69" s="177"/>
-      <c r="P69" s="177"/>
-      <c r="Q69" s="177"/>
+      <c r="N69" s="180"/>
+      <c r="O69" s="180"/>
+      <c r="P69" s="180"/>
+      <c r="Q69" s="180"/>
       <c r="R69" s="90"/>
       <c r="S69" s="90"/>
       <c r="T69" s="90"/>
       <c r="U69" s="90"/>
-      <c r="V69" s="178"/>
+      <c r="V69" s="181"/>
       <c r="W69" s="200"/>
       <c r="X69" s="67"/>
       <c r="Y69" s="67"/>
@@ -5657,13 +5650,13 @@
       <c r="H70" s="67"/>
       <c r="I70" s="67"/>
       <c r="J70" s="67"/>
-      <c r="K70" s="190"/>
-      <c r="L70" s="191"/>
+      <c r="K70" s="191"/>
+      <c r="L70" s="192"/>
       <c r="M70" s="58"/>
-      <c r="N70" s="182"/>
-      <c r="O70" s="182"/>
-      <c r="P70" s="182"/>
-      <c r="Q70" s="182"/>
+      <c r="N70" s="185"/>
+      <c r="O70" s="185"/>
+      <c r="P70" s="185"/>
+      <c r="Q70" s="185"/>
       <c r="R70" s="98"/>
       <c r="S70" s="98"/>
       <c r="T70" s="98"/>
@@ -5693,18 +5686,18 @@
       <c r="H71" s="67"/>
       <c r="I71" s="67"/>
       <c r="J71" s="67"/>
-      <c r="K71" s="190"/>
-      <c r="L71" s="191"/>
+      <c r="K71" s="191"/>
+      <c r="L71" s="192"/>
       <c r="M71" s="58"/>
-      <c r="N71" s="177"/>
-      <c r="O71" s="177"/>
-      <c r="P71" s="177"/>
-      <c r="Q71" s="177"/>
+      <c r="N71" s="180"/>
+      <c r="O71" s="180"/>
+      <c r="P71" s="180"/>
+      <c r="Q71" s="180"/>
       <c r="R71" s="90"/>
       <c r="S71" s="90"/>
       <c r="T71" s="90"/>
       <c r="U71" s="90"/>
-      <c r="V71" s="178"/>
+      <c r="V71" s="181"/>
       <c r="W71" s="200"/>
       <c r="X71" s="67"/>
       <c r="Y71" s="67"/>
@@ -5729,13 +5722,13 @@
       <c r="H72" s="67"/>
       <c r="I72" s="67"/>
       <c r="J72" s="67"/>
-      <c r="K72" s="190"/>
-      <c r="L72" s="191"/>
+      <c r="K72" s="191"/>
+      <c r="L72" s="192"/>
       <c r="M72" s="58"/>
-      <c r="N72" s="182"/>
-      <c r="O72" s="182"/>
-      <c r="P72" s="182"/>
-      <c r="Q72" s="182"/>
+      <c r="N72" s="185"/>
+      <c r="O72" s="185"/>
+      <c r="P72" s="185"/>
+      <c r="Q72" s="185"/>
       <c r="R72" s="98"/>
       <c r="S72" s="98"/>
       <c r="T72" s="98"/>
@@ -5755,28 +5748,28 @@
       <c r="AH72" s="67"/>
     </row>
     <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" s="197"/>
-      <c r="B73" s="197"/>
-      <c r="C73" s="197"/>
-      <c r="D73" s="197"/>
-      <c r="E73" s="198"/>
+      <c r="A73" s="201"/>
+      <c r="B73" s="201"/>
+      <c r="C73" s="201"/>
+      <c r="D73" s="201"/>
+      <c r="E73" s="202"/>
       <c r="F73" s="83"/>
       <c r="G73" s="67"/>
       <c r="H73" s="67"/>
       <c r="I73" s="67"/>
       <c r="J73" s="67"/>
-      <c r="K73" s="190"/>
-      <c r="L73" s="191"/>
+      <c r="K73" s="191"/>
+      <c r="L73" s="192"/>
       <c r="M73" s="58"/>
-      <c r="N73" s="177"/>
-      <c r="O73" s="177"/>
-      <c r="P73" s="177"/>
-      <c r="Q73" s="177"/>
+      <c r="N73" s="180"/>
+      <c r="O73" s="180"/>
+      <c r="P73" s="180"/>
+      <c r="Q73" s="180"/>
       <c r="R73" s="90"/>
       <c r="S73" s="90"/>
       <c r="T73" s="90"/>
       <c r="U73" s="90"/>
-      <c r="V73" s="178"/>
+      <c r="V73" s="181"/>
       <c r="W73" s="200"/>
       <c r="X73" s="67"/>
       <c r="Y73" s="67"/>
@@ -5791,23 +5784,23 @@
       <c r="AH73" s="67"/>
     </row>
     <row r="74" ht="22.5" customHeight="1">
-      <c r="A74" s="197"/>
-      <c r="B74" s="197"/>
-      <c r="C74" s="197"/>
-      <c r="D74" s="197"/>
-      <c r="E74" s="198"/>
+      <c r="A74" s="201"/>
+      <c r="B74" s="201"/>
+      <c r="C74" s="201"/>
+      <c r="D74" s="201"/>
+      <c r="E74" s="202"/>
       <c r="F74" s="83"/>
       <c r="G74" s="67"/>
       <c r="H74" s="67"/>
       <c r="I74" s="67"/>
       <c r="J74" s="67"/>
-      <c r="K74" s="190"/>
-      <c r="L74" s="191"/>
+      <c r="K74" s="191"/>
+      <c r="L74" s="192"/>
       <c r="M74" s="58"/>
-      <c r="N74" s="182"/>
-      <c r="O74" s="182"/>
-      <c r="P74" s="182"/>
-      <c r="Q74" s="182"/>
+      <c r="N74" s="185"/>
+      <c r="O74" s="185"/>
+      <c r="P74" s="185"/>
+      <c r="Q74" s="185"/>
       <c r="R74" s="98"/>
       <c r="S74" s="98"/>
       <c r="T74" s="98"/>
@@ -5837,8 +5830,8 @@
       <c r="H75" s="67"/>
       <c r="I75" s="67"/>
       <c r="J75" s="67"/>
-      <c r="K75" s="190"/>
-      <c r="L75" s="191"/>
+      <c r="K75" s="191"/>
+      <c r="L75" s="192"/>
       <c r="M75" s="58"/>
       <c r="N75" s="203"/>
       <c r="O75" s="203"/>
@@ -5873,8 +5866,8 @@
       <c r="H76" s="67"/>
       <c r="I76" s="67"/>
       <c r="J76" s="67"/>
-      <c r="K76" s="190"/>
-      <c r="L76" s="191"/>
+      <c r="K76" s="191"/>
+      <c r="L76" s="192"/>
       <c r="M76" s="58"/>
       <c r="N76" s="203"/>
       <c r="O76" s="203"/>
@@ -5909,8 +5902,8 @@
       <c r="H77" s="67"/>
       <c r="I77" s="67"/>
       <c r="J77" s="67"/>
-      <c r="K77" s="190"/>
-      <c r="L77" s="191"/>
+      <c r="K77" s="191"/>
+      <c r="L77" s="192"/>
       <c r="M77" s="58"/>
       <c r="N77" s="203"/>
       <c r="O77" s="203"/>
@@ -5945,8 +5938,8 @@
       <c r="H78" s="67"/>
       <c r="I78" s="67"/>
       <c r="J78" s="67"/>
-      <c r="K78" s="190"/>
-      <c r="L78" s="191"/>
+      <c r="K78" s="191"/>
+      <c r="L78" s="192"/>
       <c r="M78" s="58"/>
       <c r="N78" s="203"/>
       <c r="O78" s="203"/>
@@ -5981,8 +5974,8 @@
       <c r="H79" s="67"/>
       <c r="I79" s="67"/>
       <c r="J79" s="67"/>
-      <c r="K79" s="190"/>
-      <c r="L79" s="191"/>
+      <c r="K79" s="191"/>
+      <c r="L79" s="192"/>
       <c r="M79" s="58"/>
       <c r="N79" s="203"/>
       <c r="O79" s="203"/>
@@ -6017,8 +6010,8 @@
       <c r="H80" s="67"/>
       <c r="I80" s="67"/>
       <c r="J80" s="67"/>
-      <c r="K80" s="190"/>
-      <c r="L80" s="191"/>
+      <c r="K80" s="191"/>
+      <c r="L80" s="192"/>
       <c r="M80" s="58"/>
       <c r="N80" s="203"/>
       <c r="O80" s="203"/>
@@ -6053,8 +6046,8 @@
       <c r="H81" s="67"/>
       <c r="I81" s="67"/>
       <c r="J81" s="67"/>
-      <c r="K81" s="190"/>
-      <c r="L81" s="191"/>
+      <c r="K81" s="191"/>
+      <c r="L81" s="192"/>
       <c r="M81" s="58"/>
       <c r="N81" s="203"/>
       <c r="O81" s="203"/>
@@ -6089,8 +6082,8 @@
       <c r="H82" s="67"/>
       <c r="I82" s="67"/>
       <c r="J82" s="67"/>
-      <c r="K82" s="190"/>
-      <c r="L82" s="191"/>
+      <c r="K82" s="191"/>
+      <c r="L82" s="192"/>
       <c r="M82" s="58"/>
       <c r="N82" s="203"/>
       <c r="O82" s="203"/>
@@ -6125,8 +6118,8 @@
       <c r="H83" s="67"/>
       <c r="I83" s="67"/>
       <c r="J83" s="67"/>
-      <c r="K83" s="190"/>
-      <c r="L83" s="191"/>
+      <c r="K83" s="191"/>
+      <c r="L83" s="192"/>
       <c r="M83" s="58"/>
       <c r="N83" s="203"/>
       <c r="O83" s="203"/>
@@ -6161,8 +6154,8 @@
       <c r="H84" s="67"/>
       <c r="I84" s="67"/>
       <c r="J84" s="67"/>
-      <c r="K84" s="190"/>
-      <c r="L84" s="191"/>
+      <c r="K84" s="191"/>
+      <c r="L84" s="192"/>
       <c r="M84" s="58"/>
       <c r="N84" s="203"/>
       <c r="O84" s="203"/>
@@ -6197,8 +6190,8 @@
       <c r="H85" s="67"/>
       <c r="I85" s="67"/>
       <c r="J85" s="67"/>
-      <c r="K85" s="190"/>
-      <c r="L85" s="191"/>
+      <c r="K85" s="191"/>
+      <c r="L85" s="192"/>
       <c r="M85" s="58"/>
       <c r="N85" s="203"/>
       <c r="O85" s="203"/>
@@ -6233,8 +6226,8 @@
       <c r="H86" s="67"/>
       <c r="I86" s="67"/>
       <c r="J86" s="67"/>
-      <c r="K86" s="190"/>
-      <c r="L86" s="191"/>
+      <c r="K86" s="191"/>
+      <c r="L86" s="192"/>
       <c r="M86" s="58"/>
       <c r="N86" s="203"/>
       <c r="O86" s="203"/>
@@ -6269,8 +6262,8 @@
       <c r="H87" s="67"/>
       <c r="I87" s="67"/>
       <c r="J87" s="67"/>
-      <c r="K87" s="190"/>
-      <c r="L87" s="191"/>
+      <c r="K87" s="191"/>
+      <c r="L87" s="192"/>
       <c r="M87" s="58"/>
       <c r="N87" s="203"/>
       <c r="O87" s="203"/>
@@ -6305,8 +6298,8 @@
       <c r="H88" s="67"/>
       <c r="I88" s="67"/>
       <c r="J88" s="67"/>
-      <c r="K88" s="190"/>
-      <c r="L88" s="191"/>
+      <c r="K88" s="191"/>
+      <c r="L88" s="192"/>
       <c r="M88" s="58"/>
       <c r="N88" s="203"/>
       <c r="O88" s="203"/>
@@ -6341,8 +6334,8 @@
       <c r="H89" s="67"/>
       <c r="I89" s="67"/>
       <c r="J89" s="67"/>
-      <c r="K89" s="190"/>
-      <c r="L89" s="191"/>
+      <c r="K89" s="191"/>
+      <c r="L89" s="192"/>
       <c r="M89" s="58"/>
       <c r="N89" s="203"/>
       <c r="O89" s="203"/>
@@ -6377,8 +6370,8 @@
       <c r="H90" s="67"/>
       <c r="I90" s="67"/>
       <c r="J90" s="67"/>
-      <c r="K90" s="190"/>
-      <c r="L90" s="191"/>
+      <c r="K90" s="191"/>
+      <c r="L90" s="192"/>
       <c r="M90" s="58"/>
       <c r="N90" s="203"/>
       <c r="O90" s="203"/>
@@ -6413,8 +6406,8 @@
       <c r="H91" s="67"/>
       <c r="I91" s="67"/>
       <c r="J91" s="67"/>
-      <c r="K91" s="190"/>
-      <c r="L91" s="191"/>
+      <c r="K91" s="191"/>
+      <c r="L91" s="192"/>
       <c r="M91" s="58"/>
       <c r="N91" s="203"/>
       <c r="O91" s="203"/>
@@ -6449,8 +6442,8 @@
       <c r="H92" s="67"/>
       <c r="I92" s="67"/>
       <c r="J92" s="67"/>
-      <c r="K92" s="190"/>
-      <c r="L92" s="191"/>
+      <c r="K92" s="191"/>
+      <c r="L92" s="192"/>
       <c r="M92" s="58"/>
       <c r="N92" s="203"/>
       <c r="O92" s="203"/>
@@ -6485,8 +6478,8 @@
       <c r="H93" s="67"/>
       <c r="I93" s="67"/>
       <c r="J93" s="67"/>
-      <c r="K93" s="190"/>
-      <c r="L93" s="191"/>
+      <c r="K93" s="191"/>
+      <c r="L93" s="192"/>
       <c r="M93" s="58"/>
       <c r="N93" s="203"/>
       <c r="O93" s="203"/>
@@ -6521,8 +6514,8 @@
       <c r="H94" s="67"/>
       <c r="I94" s="67"/>
       <c r="J94" s="67"/>
-      <c r="K94" s="190"/>
-      <c r="L94" s="191"/>
+      <c r="K94" s="191"/>
+      <c r="L94" s="192"/>
       <c r="M94" s="58"/>
       <c r="N94" s="203"/>
       <c r="O94" s="203"/>
@@ -6557,8 +6550,8 @@
       <c r="H95" s="67"/>
       <c r="I95" s="67"/>
       <c r="J95" s="67"/>
-      <c r="K95" s="190"/>
-      <c r="L95" s="191"/>
+      <c r="K95" s="191"/>
+      <c r="L95" s="192"/>
       <c r="M95" s="58"/>
       <c r="N95" s="203"/>
       <c r="O95" s="203"/>
@@ -6593,8 +6586,8 @@
       <c r="H96" s="67"/>
       <c r="I96" s="67"/>
       <c r="J96" s="67"/>
-      <c r="K96" s="190"/>
-      <c r="L96" s="191"/>
+      <c r="K96" s="191"/>
+      <c r="L96" s="192"/>
       <c r="M96" s="58"/>
       <c r="N96" s="203"/>
       <c r="O96" s="203"/>
@@ -6629,8 +6622,8 @@
       <c r="H97" s="67"/>
       <c r="I97" s="67"/>
       <c r="J97" s="67"/>
-      <c r="K97" s="190"/>
-      <c r="L97" s="191"/>
+      <c r="K97" s="191"/>
+      <c r="L97" s="192"/>
       <c r="M97" s="58"/>
       <c r="N97" s="203"/>
       <c r="O97" s="203"/>
@@ -6665,8 +6658,8 @@
       <c r="H98" s="67"/>
       <c r="I98" s="67"/>
       <c r="J98" s="67"/>
-      <c r="K98" s="190"/>
-      <c r="L98" s="191"/>
+      <c r="K98" s="191"/>
+      <c r="L98" s="192"/>
       <c r="M98" s="58"/>
       <c r="N98" s="203"/>
       <c r="O98" s="203"/>
@@ -6701,8 +6694,8 @@
       <c r="H99" s="67"/>
       <c r="I99" s="67"/>
       <c r="J99" s="67"/>
-      <c r="K99" s="190"/>
-      <c r="L99" s="191"/>
+      <c r="K99" s="191"/>
+      <c r="L99" s="192"/>
       <c r="M99" s="58"/>
       <c r="N99" s="203"/>
       <c r="O99" s="203"/>
@@ -6737,8 +6730,8 @@
       <c r="H100" s="67"/>
       <c r="I100" s="67"/>
       <c r="J100" s="67"/>
-      <c r="K100" s="190"/>
-      <c r="L100" s="191"/>
+      <c r="K100" s="191"/>
+      <c r="L100" s="192"/>
       <c r="M100" s="58"/>
       <c r="N100" s="203"/>
       <c r="O100" s="203"/>
@@ -6773,8 +6766,8 @@
       <c r="H101" s="67"/>
       <c r="I101" s="67"/>
       <c r="J101" s="67"/>
-      <c r="K101" s="190"/>
-      <c r="L101" s="191"/>
+      <c r="K101" s="191"/>
+      <c r="L101" s="192"/>
       <c r="M101" s="58"/>
       <c r="N101" s="203"/>
       <c r="O101" s="203"/>
@@ -6809,8 +6802,8 @@
       <c r="H102" s="67"/>
       <c r="I102" s="67"/>
       <c r="J102" s="67"/>
-      <c r="K102" s="190"/>
-      <c r="L102" s="191"/>
+      <c r="K102" s="191"/>
+      <c r="L102" s="192"/>
       <c r="M102" s="58"/>
       <c r="N102" s="203"/>
       <c r="O102" s="203"/>
@@ -6845,8 +6838,8 @@
       <c r="H103" s="67"/>
       <c r="I103" s="67"/>
       <c r="J103" s="67"/>
-      <c r="K103" s="190"/>
-      <c r="L103" s="191"/>
+      <c r="K103" s="191"/>
+      <c r="L103" s="192"/>
       <c r="M103" s="58"/>
       <c r="N103" s="203"/>
       <c r="O103" s="203"/>
@@ -6881,8 +6874,8 @@
       <c r="H104" s="67"/>
       <c r="I104" s="67"/>
       <c r="J104" s="67"/>
-      <c r="K104" s="190"/>
-      <c r="L104" s="191"/>
+      <c r="K104" s="191"/>
+      <c r="L104" s="192"/>
       <c r="M104" s="58"/>
       <c r="N104" s="203"/>
       <c r="O104" s="203"/>
@@ -6917,8 +6910,8 @@
       <c r="H105" s="67"/>
       <c r="I105" s="67"/>
       <c r="J105" s="67"/>
-      <c r="K105" s="190"/>
-      <c r="L105" s="191"/>
+      <c r="K105" s="191"/>
+      <c r="L105" s="192"/>
       <c r="M105" s="58"/>
       <c r="N105" s="203"/>
       <c r="O105" s="203"/>
@@ -6953,8 +6946,8 @@
       <c r="H106" s="67"/>
       <c r="I106" s="67"/>
       <c r="J106" s="67"/>
-      <c r="K106" s="190"/>
-      <c r="L106" s="191"/>
+      <c r="K106" s="191"/>
+      <c r="L106" s="192"/>
       <c r="M106" s="58"/>
       <c r="N106" s="203"/>
       <c r="O106" s="203"/>
@@ -6989,8 +6982,8 @@
       <c r="H107" s="67"/>
       <c r="I107" s="67"/>
       <c r="J107" s="67"/>
-      <c r="K107" s="190"/>
-      <c r="L107" s="191"/>
+      <c r="K107" s="191"/>
+      <c r="L107" s="192"/>
       <c r="M107" s="58"/>
       <c r="N107" s="203"/>
       <c r="O107" s="203"/>
@@ -7025,8 +7018,8 @@
       <c r="H108" s="67"/>
       <c r="I108" s="67"/>
       <c r="J108" s="67"/>
-      <c r="K108" s="190"/>
-      <c r="L108" s="191"/>
+      <c r="K108" s="191"/>
+      <c r="L108" s="192"/>
       <c r="M108" s="58"/>
       <c r="N108" s="203"/>
       <c r="O108" s="203"/>
@@ -7061,8 +7054,8 @@
       <c r="H109" s="67"/>
       <c r="I109" s="67"/>
       <c r="J109" s="67"/>
-      <c r="K109" s="190"/>
-      <c r="L109" s="191"/>
+      <c r="K109" s="191"/>
+      <c r="L109" s="192"/>
       <c r="M109" s="58"/>
       <c r="N109" s="203"/>
       <c r="O109" s="203"/>
@@ -7097,8 +7090,8 @@
       <c r="H110" s="67"/>
       <c r="I110" s="67"/>
       <c r="J110" s="67"/>
-      <c r="K110" s="190"/>
-      <c r="L110" s="191"/>
+      <c r="K110" s="191"/>
+      <c r="L110" s="192"/>
       <c r="M110" s="58"/>
       <c r="N110" s="203"/>
       <c r="O110" s="203"/>
@@ -7133,8 +7126,8 @@
       <c r="H111" s="67"/>
       <c r="I111" s="67"/>
       <c r="J111" s="67"/>
-      <c r="K111" s="190"/>
-      <c r="L111" s="191"/>
+      <c r="K111" s="191"/>
+      <c r="L111" s="192"/>
       <c r="M111" s="58"/>
       <c r="N111" s="203"/>
       <c r="O111" s="203"/>
@@ -7169,8 +7162,8 @@
       <c r="H112" s="67"/>
       <c r="I112" s="67"/>
       <c r="J112" s="67"/>
-      <c r="K112" s="190"/>
-      <c r="L112" s="191"/>
+      <c r="K112" s="191"/>
+      <c r="L112" s="192"/>
       <c r="M112" s="58"/>
       <c r="N112" s="67"/>
       <c r="O112" s="67"/>
@@ -7205,8 +7198,8 @@
       <c r="H113" s="67"/>
       <c r="I113" s="67"/>
       <c r="J113" s="67"/>
-      <c r="K113" s="190"/>
-      <c r="L113" s="191"/>
+      <c r="K113" s="191"/>
+      <c r="L113" s="192"/>
       <c r="M113" s="58"/>
       <c r="N113" s="67"/>
       <c r="O113" s="67"/>
@@ -7241,8 +7234,8 @@
       <c r="H114" s="67"/>
       <c r="I114" s="67"/>
       <c r="J114" s="67"/>
-      <c r="K114" s="190"/>
-      <c r="L114" s="191"/>
+      <c r="K114" s="191"/>
+      <c r="L114" s="192"/>
       <c r="M114" s="58"/>
       <c r="N114" s="67"/>
       <c r="O114" s="67"/>
@@ -7277,8 +7270,8 @@
       <c r="H115" s="67"/>
       <c r="I115" s="67"/>
       <c r="J115" s="67"/>
-      <c r="K115" s="190"/>
-      <c r="L115" s="191"/>
+      <c r="K115" s="191"/>
+      <c r="L115" s="192"/>
       <c r="M115" s="58"/>
       <c r="N115" s="67"/>
       <c r="O115" s="67"/>
@@ -7313,8 +7306,8 @@
       <c r="H116" s="67"/>
       <c r="I116" s="67"/>
       <c r="J116" s="67"/>
-      <c r="K116" s="190"/>
-      <c r="L116" s="191"/>
+      <c r="K116" s="191"/>
+      <c r="L116" s="192"/>
       <c r="M116" s="58"/>
       <c r="N116" s="67"/>
       <c r="O116" s="67"/>
@@ -7349,8 +7342,8 @@
       <c r="H117" s="67"/>
       <c r="I117" s="67"/>
       <c r="J117" s="67"/>
-      <c r="K117" s="190"/>
-      <c r="L117" s="191"/>
+      <c r="K117" s="191"/>
+      <c r="L117" s="192"/>
       <c r="M117" s="58"/>
       <c r="N117" s="67"/>
       <c r="O117" s="67"/>
@@ -7385,8 +7378,8 @@
       <c r="H118" s="67"/>
       <c r="I118" s="67"/>
       <c r="J118" s="67"/>
-      <c r="K118" s="190"/>
-      <c r="L118" s="191"/>
+      <c r="K118" s="191"/>
+      <c r="L118" s="192"/>
       <c r="M118" s="58"/>
       <c r="N118" s="67"/>
       <c r="O118" s="67"/>
@@ -7421,8 +7414,8 @@
       <c r="H119" s="67"/>
       <c r="I119" s="67"/>
       <c r="J119" s="67"/>
-      <c r="K119" s="190"/>
-      <c r="L119" s="191"/>
+      <c r="K119" s="191"/>
+      <c r="L119" s="192"/>
       <c r="M119" s="58"/>
       <c r="N119" s="67"/>
       <c r="O119" s="67"/>
@@ -7457,8 +7450,8 @@
       <c r="H120" s="67"/>
       <c r="I120" s="67"/>
       <c r="J120" s="67"/>
-      <c r="K120" s="190"/>
-      <c r="L120" s="191"/>
+      <c r="K120" s="191"/>
+      <c r="L120" s="192"/>
       <c r="M120" s="58"/>
       <c r="N120" s="67"/>
       <c r="O120" s="67"/>
@@ -7493,8 +7486,8 @@
       <c r="H121" s="67"/>
       <c r="I121" s="67"/>
       <c r="J121" s="67"/>
-      <c r="K121" s="190"/>
-      <c r="L121" s="191"/>
+      <c r="K121" s="191"/>
+      <c r="L121" s="192"/>
       <c r="M121" s="58"/>
       <c r="N121" s="67"/>
       <c r="O121" s="67"/>
@@ -7529,8 +7522,8 @@
       <c r="H122" s="67"/>
       <c r="I122" s="67"/>
       <c r="J122" s="67"/>
-      <c r="K122" s="190"/>
-      <c r="L122" s="191"/>
+      <c r="K122" s="191"/>
+      <c r="L122" s="192"/>
       <c r="M122" s="58"/>
       <c r="N122" s="67"/>
       <c r="O122" s="67"/>
@@ -7565,8 +7558,8 @@
       <c r="H123" s="67"/>
       <c r="I123" s="67"/>
       <c r="J123" s="67"/>
-      <c r="K123" s="190"/>
-      <c r="L123" s="191"/>
+      <c r="K123" s="191"/>
+      <c r="L123" s="192"/>
       <c r="M123" s="58"/>
       <c r="N123" s="67"/>
       <c r="O123" s="67"/>
@@ -7601,8 +7594,8 @@
       <c r="H124" s="67"/>
       <c r="I124" s="67"/>
       <c r="J124" s="67"/>
-      <c r="K124" s="190"/>
-      <c r="L124" s="191"/>
+      <c r="K124" s="191"/>
+      <c r="L124" s="192"/>
       <c r="M124" s="58"/>
       <c r="N124" s="67"/>
       <c r="O124" s="67"/>
@@ -7637,8 +7630,8 @@
       <c r="H125" s="67"/>
       <c r="I125" s="67"/>
       <c r="J125" s="67"/>
-      <c r="K125" s="190"/>
-      <c r="L125" s="191"/>
+      <c r="K125" s="191"/>
+      <c r="L125" s="192"/>
       <c r="M125" s="58"/>
       <c r="N125" s="67"/>
       <c r="O125" s="67"/>
@@ -7673,8 +7666,8 @@
       <c r="H126" s="67"/>
       <c r="I126" s="67"/>
       <c r="J126" s="67"/>
-      <c r="K126" s="190"/>
-      <c r="L126" s="191"/>
+      <c r="K126" s="191"/>
+      <c r="L126" s="192"/>
       <c r="M126" s="58"/>
       <c r="N126" s="67"/>
       <c r="O126" s="67"/>
@@ -7709,8 +7702,8 @@
       <c r="H127" s="67"/>
       <c r="I127" s="67"/>
       <c r="J127" s="67"/>
-      <c r="K127" s="190"/>
-      <c r="L127" s="191"/>
+      <c r="K127" s="191"/>
+      <c r="L127" s="192"/>
       <c r="M127" s="58"/>
       <c r="N127" s="67"/>
       <c r="O127" s="67"/>
@@ -7745,8 +7738,8 @@
       <c r="H128" s="67"/>
       <c r="I128" s="67"/>
       <c r="J128" s="67"/>
-      <c r="K128" s="190"/>
-      <c r="L128" s="191"/>
+      <c r="K128" s="191"/>
+      <c r="L128" s="192"/>
       <c r="M128" s="58"/>
       <c r="N128" s="67"/>
       <c r="O128" s="67"/>
@@ -7781,8 +7774,8 @@
       <c r="H129" s="67"/>
       <c r="I129" s="67"/>
       <c r="J129" s="67"/>
-      <c r="K129" s="190"/>
-      <c r="L129" s="191"/>
+      <c r="K129" s="191"/>
+      <c r="L129" s="192"/>
       <c r="M129" s="58"/>
       <c r="N129" s="67"/>
       <c r="O129" s="67"/>
@@ -7817,8 +7810,8 @@
       <c r="H130" s="67"/>
       <c r="I130" s="67"/>
       <c r="J130" s="67"/>
-      <c r="K130" s="190"/>
-      <c r="L130" s="191"/>
+      <c r="K130" s="191"/>
+      <c r="L130" s="192"/>
       <c r="M130" s="58"/>
       <c r="N130" s="67"/>
       <c r="O130" s="67"/>
@@ -7853,8 +7846,8 @@
       <c r="H131" s="67"/>
       <c r="I131" s="67"/>
       <c r="J131" s="67"/>
-      <c r="K131" s="190"/>
-      <c r="L131" s="191"/>
+      <c r="K131" s="191"/>
+      <c r="L131" s="192"/>
       <c r="M131" s="58"/>
       <c r="N131" s="67"/>
       <c r="O131" s="67"/>
@@ -7889,8 +7882,8 @@
       <c r="H132" s="67"/>
       <c r="I132" s="67"/>
       <c r="J132" s="67"/>
-      <c r="K132" s="190"/>
-      <c r="L132" s="191"/>
+      <c r="K132" s="191"/>
+      <c r="L132" s="192"/>
       <c r="M132" s="58"/>
       <c r="N132" s="67"/>
       <c r="O132" s="67"/>
@@ -7925,8 +7918,8 @@
       <c r="H133" s="67"/>
       <c r="I133" s="67"/>
       <c r="J133" s="67"/>
-      <c r="K133" s="190"/>
-      <c r="L133" s="191"/>
+      <c r="K133" s="191"/>
+      <c r="L133" s="192"/>
       <c r="M133" s="58"/>
       <c r="N133" s="67"/>
       <c r="O133" s="67"/>
@@ -7961,8 +7954,8 @@
       <c r="H134" s="67"/>
       <c r="I134" s="67"/>
       <c r="J134" s="67"/>
-      <c r="K134" s="190"/>
-      <c r="L134" s="191"/>
+      <c r="K134" s="191"/>
+      <c r="L134" s="192"/>
       <c r="M134" s="58"/>
       <c r="N134" s="67"/>
       <c r="O134" s="67"/>
@@ -7997,8 +7990,8 @@
       <c r="H135" s="67"/>
       <c r="I135" s="67"/>
       <c r="J135" s="67"/>
-      <c r="K135" s="190"/>
-      <c r="L135" s="191"/>
+      <c r="K135" s="191"/>
+      <c r="L135" s="192"/>
       <c r="M135" s="58"/>
       <c r="N135" s="67"/>
       <c r="O135" s="67"/>
@@ -8033,8 +8026,8 @@
       <c r="H136" s="67"/>
       <c r="I136" s="67"/>
       <c r="J136" s="67"/>
-      <c r="K136" s="190"/>
-      <c r="L136" s="191"/>
+      <c r="K136" s="191"/>
+      <c r="L136" s="192"/>
       <c r="M136" s="58"/>
       <c r="N136" s="67"/>
       <c r="O136" s="67"/>
@@ -8069,8 +8062,8 @@
       <c r="H137" s="67"/>
       <c r="I137" s="67"/>
       <c r="J137" s="67"/>
-      <c r="K137" s="190"/>
-      <c r="L137" s="191"/>
+      <c r="K137" s="191"/>
+      <c r="L137" s="192"/>
       <c r="M137" s="58"/>
       <c r="N137" s="67"/>
       <c r="O137" s="67"/>
@@ -8105,8 +8098,8 @@
       <c r="H138" s="67"/>
       <c r="I138" s="67"/>
       <c r="J138" s="67"/>
-      <c r="K138" s="190"/>
-      <c r="L138" s="191"/>
+      <c r="K138" s="191"/>
+      <c r="L138" s="192"/>
       <c r="M138" s="58"/>
       <c r="N138" s="67"/>
       <c r="O138" s="67"/>
@@ -8141,8 +8134,8 @@
       <c r="H139" s="67"/>
       <c r="I139" s="67"/>
       <c r="J139" s="67"/>
-      <c r="K139" s="190"/>
-      <c r="L139" s="191"/>
+      <c r="K139" s="191"/>
+      <c r="L139" s="192"/>
       <c r="M139" s="58"/>
       <c r="N139" s="67"/>
       <c r="O139" s="67"/>
@@ -8177,8 +8170,8 @@
       <c r="H140" s="67"/>
       <c r="I140" s="67"/>
       <c r="J140" s="67"/>
-      <c r="K140" s="190"/>
-      <c r="L140" s="191"/>
+      <c r="K140" s="191"/>
+      <c r="L140" s="192"/>
       <c r="M140" s="58"/>
       <c r="N140" s="67"/>
       <c r="O140" s="67"/>
@@ -8213,8 +8206,8 @@
       <c r="H141" s="67"/>
       <c r="I141" s="67"/>
       <c r="J141" s="67"/>
-      <c r="K141" s="190"/>
-      <c r="L141" s="191"/>
+      <c r="K141" s="191"/>
+      <c r="L141" s="192"/>
       <c r="M141" s="58"/>
       <c r="N141" s="67"/>
       <c r="O141" s="67"/>
@@ -8249,8 +8242,8 @@
       <c r="H142" s="67"/>
       <c r="I142" s="67"/>
       <c r="J142" s="67"/>
-      <c r="K142" s="190"/>
-      <c r="L142" s="191"/>
+      <c r="K142" s="191"/>
+      <c r="L142" s="192"/>
       <c r="M142" s="58"/>
       <c r="N142" s="67"/>
       <c r="O142" s="67"/>
@@ -8285,8 +8278,8 @@
       <c r="H143" s="67"/>
       <c r="I143" s="67"/>
       <c r="J143" s="67"/>
-      <c r="K143" s="190"/>
-      <c r="L143" s="191"/>
+      <c r="K143" s="191"/>
+      <c r="L143" s="192"/>
       <c r="M143" s="58"/>
       <c r="N143" s="67"/>
       <c r="O143" s="67"/>
@@ -8321,8 +8314,8 @@
       <c r="H144" s="67"/>
       <c r="I144" s="67"/>
       <c r="J144" s="67"/>
-      <c r="K144" s="190"/>
-      <c r="L144" s="191"/>
+      <c r="K144" s="191"/>
+      <c r="L144" s="192"/>
       <c r="M144" s="58"/>
       <c r="N144" s="67"/>
       <c r="O144" s="67"/>
@@ -8357,8 +8350,8 @@
       <c r="H145" s="67"/>
       <c r="I145" s="67"/>
       <c r="J145" s="67"/>
-      <c r="K145" s="190"/>
-      <c r="L145" s="191"/>
+      <c r="K145" s="191"/>
+      <c r="L145" s="192"/>
       <c r="M145" s="58"/>
       <c r="N145" s="67"/>
       <c r="O145" s="67"/>
@@ -8393,8 +8386,8 @@
       <c r="H146" s="67"/>
       <c r="I146" s="67"/>
       <c r="J146" s="67"/>
-      <c r="K146" s="190"/>
-      <c r="L146" s="191"/>
+      <c r="K146" s="191"/>
+      <c r="L146" s="192"/>
       <c r="M146" s="58"/>
       <c r="N146" s="67"/>
       <c r="O146" s="67"/>
@@ -8429,8 +8422,8 @@
       <c r="H147" s="67"/>
       <c r="I147" s="67"/>
       <c r="J147" s="67"/>
-      <c r="K147" s="190"/>
-      <c r="L147" s="191"/>
+      <c r="K147" s="191"/>
+      <c r="L147" s="192"/>
       <c r="M147" s="58"/>
       <c r="N147" s="67"/>
       <c r="O147" s="67"/>
@@ -8465,8 +8458,8 @@
       <c r="H148" s="67"/>
       <c r="I148" s="67"/>
       <c r="J148" s="67"/>
-      <c r="K148" s="190"/>
-      <c r="L148" s="191"/>
+      <c r="K148" s="191"/>
+      <c r="L148" s="192"/>
       <c r="M148" s="58"/>
       <c r="N148" s="67"/>
       <c r="O148" s="67"/>
@@ -8501,8 +8494,8 @@
       <c r="H149" s="67"/>
       <c r="I149" s="67"/>
       <c r="J149" s="67"/>
-      <c r="K149" s="190"/>
-      <c r="L149" s="191"/>
+      <c r="K149" s="191"/>
+      <c r="L149" s="192"/>
       <c r="M149" s="58"/>
       <c r="N149" s="67"/>
       <c r="O149" s="67"/>
@@ -8537,8 +8530,8 @@
       <c r="H150" s="67"/>
       <c r="I150" s="67"/>
       <c r="J150" s="67"/>
-      <c r="K150" s="190"/>
-      <c r="L150" s="191"/>
+      <c r="K150" s="191"/>
+      <c r="L150" s="192"/>
       <c r="M150" s="58"/>
       <c r="N150" s="67"/>
       <c r="O150" s="67"/>
@@ -8573,8 +8566,8 @@
       <c r="H151" s="67"/>
       <c r="I151" s="67"/>
       <c r="J151" s="67"/>
-      <c r="K151" s="190"/>
-      <c r="L151" s="191"/>
+      <c r="K151" s="191"/>
+      <c r="L151" s="192"/>
       <c r="M151" s="58"/>
       <c r="N151" s="67"/>
       <c r="O151" s="67"/>
@@ -8609,8 +8602,8 @@
       <c r="H152" s="67"/>
       <c r="I152" s="67"/>
       <c r="J152" s="67"/>
-      <c r="K152" s="190"/>
-      <c r="L152" s="191"/>
+      <c r="K152" s="191"/>
+      <c r="L152" s="192"/>
       <c r="M152" s="58"/>
       <c r="N152" s="67"/>
       <c r="O152" s="67"/>
@@ -8645,8 +8638,8 @@
       <c r="H153" s="67"/>
       <c r="I153" s="67"/>
       <c r="J153" s="67"/>
-      <c r="K153" s="190"/>
-      <c r="L153" s="191"/>
+      <c r="K153" s="191"/>
+      <c r="L153" s="192"/>
       <c r="M153" s="58"/>
       <c r="N153" s="67"/>
       <c r="O153" s="67"/>
@@ -8681,8 +8674,8 @@
       <c r="H154" s="67"/>
       <c r="I154" s="67"/>
       <c r="J154" s="67"/>
-      <c r="K154" s="190"/>
-      <c r="L154" s="191"/>
+      <c r="K154" s="191"/>
+      <c r="L154" s="192"/>
       <c r="M154" s="58"/>
       <c r="N154" s="67"/>
       <c r="O154" s="67"/>
@@ -8717,8 +8710,8 @@
       <c r="H155" s="67"/>
       <c r="I155" s="67"/>
       <c r="J155" s="67"/>
-      <c r="K155" s="190"/>
-      <c r="L155" s="191"/>
+      <c r="K155" s="191"/>
+      <c r="L155" s="192"/>
       <c r="M155" s="58"/>
       <c r="N155" s="67"/>
       <c r="O155" s="67"/>
@@ -8753,8 +8746,8 @@
       <c r="H156" s="67"/>
       <c r="I156" s="67"/>
       <c r="J156" s="67"/>
-      <c r="K156" s="190"/>
-      <c r="L156" s="191"/>
+      <c r="K156" s="191"/>
+      <c r="L156" s="192"/>
       <c r="M156" s="58"/>
       <c r="N156" s="67"/>
       <c r="O156" s="67"/>
@@ -8789,8 +8782,8 @@
       <c r="H157" s="67"/>
       <c r="I157" s="67"/>
       <c r="J157" s="67"/>
-      <c r="K157" s="190"/>
-      <c r="L157" s="191"/>
+      <c r="K157" s="191"/>
+      <c r="L157" s="192"/>
       <c r="M157" s="58"/>
       <c r="N157" s="67"/>
       <c r="O157" s="67"/>
@@ -8825,8 +8818,8 @@
       <c r="H158" s="67"/>
       <c r="I158" s="67"/>
       <c r="J158" s="67"/>
-      <c r="K158" s="190"/>
-      <c r="L158" s="191"/>
+      <c r="K158" s="191"/>
+      <c r="L158" s="192"/>
       <c r="M158" s="58"/>
       <c r="N158" s="67"/>
       <c r="O158" s="67"/>
@@ -8861,8 +8854,8 @@
       <c r="H159" s="67"/>
       <c r="I159" s="67"/>
       <c r="J159" s="67"/>
-      <c r="K159" s="190"/>
-      <c r="L159" s="191"/>
+      <c r="K159" s="191"/>
+      <c r="L159" s="192"/>
       <c r="M159" s="58"/>
       <c r="N159" s="67"/>
       <c r="O159" s="67"/>
@@ -8897,8 +8890,8 @@
       <c r="H160" s="67"/>
       <c r="I160" s="67"/>
       <c r="J160" s="67"/>
-      <c r="K160" s="190"/>
-      <c r="L160" s="191"/>
+      <c r="K160" s="191"/>
+      <c r="L160" s="192"/>
       <c r="M160" s="58"/>
       <c r="N160" s="67"/>
       <c r="O160" s="67"/>
@@ -8933,8 +8926,8 @@
       <c r="H161" s="67"/>
       <c r="I161" s="67"/>
       <c r="J161" s="67"/>
-      <c r="K161" s="190"/>
-      <c r="L161" s="191"/>
+      <c r="K161" s="191"/>
+      <c r="L161" s="192"/>
       <c r="M161" s="58"/>
       <c r="N161" s="67"/>
       <c r="O161" s="67"/>
@@ -8969,8 +8962,8 @@
       <c r="H162" s="67"/>
       <c r="I162" s="67"/>
       <c r="J162" s="67"/>
-      <c r="K162" s="190"/>
-      <c r="L162" s="191"/>
+      <c r="K162" s="191"/>
+      <c r="L162" s="192"/>
       <c r="M162" s="58"/>
       <c r="N162" s="67"/>
       <c r="O162" s="67"/>
@@ -9005,8 +8998,8 @@
       <c r="H163" s="67"/>
       <c r="I163" s="67"/>
       <c r="J163" s="67"/>
-      <c r="K163" s="190"/>
-      <c r="L163" s="191"/>
+      <c r="K163" s="191"/>
+      <c r="L163" s="192"/>
       <c r="M163" s="58"/>
       <c r="N163" s="67"/>
       <c r="O163" s="67"/>
@@ -9041,8 +9034,8 @@
       <c r="H164" s="67"/>
       <c r="I164" s="67"/>
       <c r="J164" s="67"/>
-      <c r="K164" s="190"/>
-      <c r="L164" s="191"/>
+      <c r="K164" s="191"/>
+      <c r="L164" s="192"/>
       <c r="M164" s="58"/>
       <c r="N164" s="67"/>
       <c r="O164" s="67"/>
@@ -9077,8 +9070,8 @@
       <c r="H165" s="67"/>
       <c r="I165" s="67"/>
       <c r="J165" s="67"/>
-      <c r="K165" s="190"/>
-      <c r="L165" s="191"/>
+      <c r="K165" s="191"/>
+      <c r="L165" s="192"/>
       <c r="M165" s="58"/>
       <c r="N165" s="67"/>
       <c r="O165" s="67"/>
@@ -9113,8 +9106,8 @@
       <c r="H166" s="67"/>
       <c r="I166" s="67"/>
       <c r="J166" s="67"/>
-      <c r="K166" s="190"/>
-      <c r="L166" s="191"/>
+      <c r="K166" s="191"/>
+      <c r="L166" s="192"/>
       <c r="M166" s="58"/>
       <c r="N166" s="67"/>
       <c r="O166" s="67"/>
@@ -9149,8 +9142,8 @@
       <c r="H167" s="67"/>
       <c r="I167" s="67"/>
       <c r="J167" s="67"/>
-      <c r="K167" s="190"/>
-      <c r="L167" s="191"/>
+      <c r="K167" s="191"/>
+      <c r="L167" s="192"/>
       <c r="M167" s="58"/>
       <c r="N167" s="67"/>
       <c r="O167" s="67"/>
@@ -9185,8 +9178,8 @@
       <c r="H168" s="67"/>
       <c r="I168" s="67"/>
       <c r="J168" s="67"/>
-      <c r="K168" s="190"/>
-      <c r="L168" s="191"/>
+      <c r="K168" s="191"/>
+      <c r="L168" s="192"/>
       <c r="M168" s="58"/>
       <c r="N168" s="67"/>
       <c r="O168" s="67"/>
@@ -9221,8 +9214,8 @@
       <c r="H169" s="67"/>
       <c r="I169" s="67"/>
       <c r="J169" s="67"/>
-      <c r="K169" s="190"/>
-      <c r="L169" s="191"/>
+      <c r="K169" s="191"/>
+      <c r="L169" s="192"/>
       <c r="M169" s="58"/>
       <c r="N169" s="67"/>
       <c r="O169" s="67"/>
@@ -9257,8 +9250,8 @@
       <c r="H170" s="67"/>
       <c r="I170" s="67"/>
       <c r="J170" s="67"/>
-      <c r="K170" s="190"/>
-      <c r="L170" s="191"/>
+      <c r="K170" s="191"/>
+      <c r="L170" s="192"/>
       <c r="M170" s="58"/>
       <c r="N170" s="67"/>
       <c r="O170" s="67"/>
@@ -9293,8 +9286,8 @@
       <c r="H171" s="67"/>
       <c r="I171" s="67"/>
       <c r="J171" s="67"/>
-      <c r="K171" s="190"/>
-      <c r="L171" s="191"/>
+      <c r="K171" s="191"/>
+      <c r="L171" s="192"/>
       <c r="M171" s="58"/>
       <c r="N171" s="67"/>
       <c r="O171" s="67"/>
@@ -9329,8 +9322,8 @@
       <c r="H172" s="67"/>
       <c r="I172" s="67"/>
       <c r="J172" s="67"/>
-      <c r="K172" s="190"/>
-      <c r="L172" s="191"/>
+      <c r="K172" s="191"/>
+      <c r="L172" s="192"/>
       <c r="M172" s="58"/>
       <c r="N172" s="67"/>
       <c r="O172" s="67"/>
@@ -9365,8 +9358,8 @@
       <c r="H173" s="67"/>
       <c r="I173" s="67"/>
       <c r="J173" s="67"/>
-      <c r="K173" s="190"/>
-      <c r="L173" s="191"/>
+      <c r="K173" s="191"/>
+      <c r="L173" s="192"/>
       <c r="M173" s="58"/>
       <c r="N173" s="67"/>
       <c r="O173" s="67"/>
@@ -9401,8 +9394,8 @@
       <c r="H174" s="67"/>
       <c r="I174" s="67"/>
       <c r="J174" s="67"/>
-      <c r="K174" s="190"/>
-      <c r="L174" s="191"/>
+      <c r="K174" s="191"/>
+      <c r="L174" s="192"/>
       <c r="M174" s="58"/>
       <c r="N174" s="67"/>
       <c r="O174" s="67"/>
@@ -9437,8 +9430,8 @@
       <c r="H175" s="67"/>
       <c r="I175" s="67"/>
       <c r="J175" s="67"/>
-      <c r="K175" s="190"/>
-      <c r="L175" s="191"/>
+      <c r="K175" s="191"/>
+      <c r="L175" s="192"/>
       <c r="M175" s="58"/>
       <c r="N175" s="67"/>
       <c r="O175" s="67"/>
@@ -9473,8 +9466,8 @@
       <c r="H176" s="67"/>
       <c r="I176" s="67"/>
       <c r="J176" s="67"/>
-      <c r="K176" s="190"/>
-      <c r="L176" s="191"/>
+      <c r="K176" s="191"/>
+      <c r="L176" s="192"/>
       <c r="M176" s="58"/>
       <c r="N176" s="67"/>
       <c r="O176" s="67"/>
@@ -9509,8 +9502,8 @@
       <c r="H177" s="67"/>
       <c r="I177" s="67"/>
       <c r="J177" s="67"/>
-      <c r="K177" s="190"/>
-      <c r="L177" s="191"/>
+      <c r="K177" s="191"/>
+      <c r="L177" s="192"/>
       <c r="M177" s="58"/>
       <c r="N177" s="67"/>
       <c r="O177" s="67"/>
@@ -9545,8 +9538,8 @@
       <c r="H178" s="67"/>
       <c r="I178" s="67"/>
       <c r="J178" s="67"/>
-      <c r="K178" s="190"/>
-      <c r="L178" s="191"/>
+      <c r="K178" s="191"/>
+      <c r="L178" s="192"/>
       <c r="M178" s="58"/>
       <c r="N178" s="67"/>
       <c r="O178" s="67"/>
@@ -9581,8 +9574,8 @@
       <c r="H179" s="67"/>
       <c r="I179" s="67"/>
       <c r="J179" s="67"/>
-      <c r="K179" s="190"/>
-      <c r="L179" s="191"/>
+      <c r="K179" s="191"/>
+      <c r="L179" s="192"/>
       <c r="M179" s="58"/>
       <c r="N179" s="67"/>
       <c r="O179" s="67"/>
@@ -9617,8 +9610,8 @@
       <c r="H180" s="67"/>
       <c r="I180" s="67"/>
       <c r="J180" s="67"/>
-      <c r="K180" s="190"/>
-      <c r="L180" s="191"/>
+      <c r="K180" s="191"/>
+      <c r="L180" s="192"/>
       <c r="M180" s="58"/>
       <c r="N180" s="67"/>
       <c r="O180" s="67"/>
@@ -9653,8 +9646,8 @@
       <c r="H181" s="67"/>
       <c r="I181" s="67"/>
       <c r="J181" s="67"/>
-      <c r="K181" s="190"/>
-      <c r="L181" s="191"/>
+      <c r="K181" s="191"/>
+      <c r="L181" s="192"/>
       <c r="M181" s="58"/>
       <c r="N181" s="67"/>
       <c r="O181" s="67"/>
@@ -9689,8 +9682,8 @@
       <c r="H182" s="67"/>
       <c r="I182" s="67"/>
       <c r="J182" s="67"/>
-      <c r="K182" s="190"/>
-      <c r="L182" s="191"/>
+      <c r="K182" s="191"/>
+      <c r="L182" s="192"/>
       <c r="M182" s="58"/>
       <c r="N182" s="67"/>
       <c r="O182" s="67"/>
@@ -9725,8 +9718,8 @@
       <c r="H183" s="67"/>
       <c r="I183" s="67"/>
       <c r="J183" s="67"/>
-      <c r="K183" s="190"/>
-      <c r="L183" s="191"/>
+      <c r="K183" s="191"/>
+      <c r="L183" s="192"/>
       <c r="M183" s="58"/>
       <c r="N183" s="67"/>
       <c r="O183" s="67"/>
@@ -9761,8 +9754,8 @@
       <c r="H184" s="67"/>
       <c r="I184" s="67"/>
       <c r="J184" s="67"/>
-      <c r="K184" s="190"/>
-      <c r="L184" s="191"/>
+      <c r="K184" s="191"/>
+      <c r="L184" s="192"/>
       <c r="M184" s="58"/>
       <c r="N184" s="67"/>
       <c r="O184" s="67"/>
@@ -9797,8 +9790,8 @@
       <c r="H185" s="67"/>
       <c r="I185" s="67"/>
       <c r="J185" s="67"/>
-      <c r="K185" s="190"/>
-      <c r="L185" s="191"/>
+      <c r="K185" s="191"/>
+      <c r="L185" s="192"/>
       <c r="M185" s="58"/>
       <c r="N185" s="67"/>
       <c r="O185" s="67"/>
@@ -9833,8 +9826,8 @@
       <c r="H186" s="67"/>
       <c r="I186" s="67"/>
       <c r="J186" s="67"/>
-      <c r="K186" s="190"/>
-      <c r="L186" s="191"/>
+      <c r="K186" s="191"/>
+      <c r="L186" s="192"/>
       <c r="M186" s="58"/>
       <c r="N186" s="67"/>
       <c r="O186" s="67"/>
@@ -9869,8 +9862,8 @@
       <c r="H187" s="67"/>
       <c r="I187" s="67"/>
       <c r="J187" s="67"/>
-      <c r="K187" s="190"/>
-      <c r="L187" s="191"/>
+      <c r="K187" s="191"/>
+      <c r="L187" s="192"/>
       <c r="M187" s="58"/>
       <c r="N187" s="67"/>
       <c r="O187" s="67"/>
@@ -9905,8 +9898,8 @@
       <c r="H188" s="67"/>
       <c r="I188" s="67"/>
       <c r="J188" s="67"/>
-      <c r="K188" s="190"/>
-      <c r="L188" s="191"/>
+      <c r="K188" s="191"/>
+      <c r="L188" s="192"/>
       <c r="M188" s="58"/>
       <c r="N188" s="67"/>
       <c r="O188" s="67"/>
@@ -9941,8 +9934,8 @@
       <c r="H189" s="67"/>
       <c r="I189" s="67"/>
       <c r="J189" s="67"/>
-      <c r="K189" s="190"/>
-      <c r="L189" s="191"/>
+      <c r="K189" s="191"/>
+      <c r="L189" s="192"/>
       <c r="M189" s="58"/>
       <c r="N189" s="67"/>
       <c r="O189" s="67"/>
@@ -9977,8 +9970,8 @@
       <c r="H190" s="67"/>
       <c r="I190" s="67"/>
       <c r="J190" s="67"/>
-      <c r="K190" s="190"/>
-      <c r="L190" s="191"/>
+      <c r="K190" s="191"/>
+      <c r="L190" s="192"/>
       <c r="M190" s="58"/>
       <c r="N190" s="67"/>
       <c r="O190" s="67"/>
@@ -10013,8 +10006,8 @@
       <c r="H191" s="67"/>
       <c r="I191" s="67"/>
       <c r="J191" s="67"/>
-      <c r="K191" s="190"/>
-      <c r="L191" s="191"/>
+      <c r="K191" s="191"/>
+      <c r="L191" s="192"/>
       <c r="M191" s="58"/>
       <c r="N191" s="67"/>
       <c r="O191" s="67"/>
@@ -10049,8 +10042,8 @@
       <c r="H192" s="67"/>
       <c r="I192" s="67"/>
       <c r="J192" s="67"/>
-      <c r="K192" s="190"/>
-      <c r="L192" s="191"/>
+      <c r="K192" s="191"/>
+      <c r="L192" s="192"/>
       <c r="M192" s="58"/>
       <c r="N192" s="67"/>
       <c r="O192" s="67"/>
@@ -10085,8 +10078,8 @@
       <c r="H193" s="67"/>
       <c r="I193" s="67"/>
       <c r="J193" s="67"/>
-      <c r="K193" s="190"/>
-      <c r="L193" s="191"/>
+      <c r="K193" s="191"/>
+      <c r="L193" s="192"/>
       <c r="M193" s="58"/>
       <c r="N193" s="67"/>
       <c r="O193" s="67"/>
@@ -10121,8 +10114,8 @@
       <c r="H194" s="67"/>
       <c r="I194" s="67"/>
       <c r="J194" s="67"/>
-      <c r="K194" s="190"/>
-      <c r="L194" s="191"/>
+      <c r="K194" s="191"/>
+      <c r="L194" s="192"/>
       <c r="M194" s="58"/>
       <c r="N194" s="67"/>
       <c r="O194" s="67"/>
@@ -10157,8 +10150,8 @@
       <c r="H195" s="67"/>
       <c r="I195" s="67"/>
       <c r="J195" s="67"/>
-      <c r="K195" s="190"/>
-      <c r="L195" s="191"/>
+      <c r="K195" s="191"/>
+      <c r="L195" s="192"/>
       <c r="M195" s="58"/>
       <c r="N195" s="67"/>
       <c r="O195" s="67"/>
@@ -10193,8 +10186,8 @@
       <c r="H196" s="67"/>
       <c r="I196" s="67"/>
       <c r="J196" s="67"/>
-      <c r="K196" s="190"/>
-      <c r="L196" s="191"/>
+      <c r="K196" s="191"/>
+      <c r="L196" s="192"/>
       <c r="M196" s="58"/>
       <c r="N196" s="67"/>
       <c r="O196" s="67"/>
@@ -10229,8 +10222,8 @@
       <c r="H197" s="67"/>
       <c r="I197" s="67"/>
       <c r="J197" s="67"/>
-      <c r="K197" s="190"/>
-      <c r="L197" s="191"/>
+      <c r="K197" s="191"/>
+      <c r="L197" s="192"/>
       <c r="M197" s="58"/>
       <c r="N197" s="67"/>
       <c r="O197" s="67"/>
@@ -10265,8 +10258,8 @@
       <c r="H198" s="67"/>
       <c r="I198" s="67"/>
       <c r="J198" s="67"/>
-      <c r="K198" s="190"/>
-      <c r="L198" s="191"/>
+      <c r="K198" s="191"/>
+      <c r="L198" s="192"/>
       <c r="M198" s="58"/>
       <c r="N198" s="67"/>
       <c r="O198" s="67"/>
@@ -10301,8 +10294,8 @@
       <c r="H199" s="67"/>
       <c r="I199" s="67"/>
       <c r="J199" s="67"/>
-      <c r="K199" s="190"/>
-      <c r="L199" s="191"/>
+      <c r="K199" s="191"/>
+      <c r="L199" s="192"/>
       <c r="M199" s="58"/>
       <c r="N199" s="67"/>
       <c r="O199" s="67"/>
@@ -10337,8 +10330,8 @@
       <c r="H200" s="67"/>
       <c r="I200" s="67"/>
       <c r="J200" s="67"/>
-      <c r="K200" s="190"/>
-      <c r="L200" s="191"/>
+      <c r="K200" s="191"/>
+      <c r="L200" s="192"/>
       <c r="M200" s="58"/>
       <c r="N200" s="67"/>
       <c r="O200" s="67"/>
@@ -10373,8 +10366,8 @@
       <c r="H201" s="67"/>
       <c r="I201" s="67"/>
       <c r="J201" s="67"/>
-      <c r="K201" s="190"/>
-      <c r="L201" s="191"/>
+      <c r="K201" s="191"/>
+      <c r="L201" s="192"/>
       <c r="M201" s="58"/>
       <c r="N201" s="67"/>
       <c r="O201" s="67"/>
@@ -10409,8 +10402,8 @@
       <c r="H202" s="67"/>
       <c r="I202" s="67"/>
       <c r="J202" s="67"/>
-      <c r="K202" s="190"/>
-      <c r="L202" s="191"/>
+      <c r="K202" s="191"/>
+      <c r="L202" s="192"/>
       <c r="M202" s="58"/>
       <c r="N202" s="67"/>
       <c r="O202" s="67"/>
@@ -10445,8 +10438,8 @@
       <c r="H203" s="67"/>
       <c r="I203" s="67"/>
       <c r="J203" s="67"/>
-      <c r="K203" s="190"/>
-      <c r="L203" s="191"/>
+      <c r="K203" s="191"/>
+      <c r="L203" s="192"/>
       <c r="M203" s="58"/>
       <c r="N203" s="67"/>
       <c r="O203" s="67"/>
@@ -10481,8 +10474,8 @@
       <c r="H204" s="67"/>
       <c r="I204" s="67"/>
       <c r="J204" s="67"/>
-      <c r="K204" s="190"/>
-      <c r="L204" s="191"/>
+      <c r="K204" s="191"/>
+      <c r="L204" s="192"/>
       <c r="M204" s="58"/>
       <c r="N204" s="67"/>
       <c r="O204" s="67"/>
@@ -10517,8 +10510,8 @@
       <c r="H205" s="67"/>
       <c r="I205" s="67"/>
       <c r="J205" s="67"/>
-      <c r="K205" s="190"/>
-      <c r="L205" s="191"/>
+      <c r="K205" s="191"/>
+      <c r="L205" s="192"/>
       <c r="M205" s="58"/>
       <c r="N205" s="67"/>
       <c r="O205" s="67"/>
@@ -10553,8 +10546,8 @@
       <c r="H206" s="67"/>
       <c r="I206" s="67"/>
       <c r="J206" s="67"/>
-      <c r="K206" s="190"/>
-      <c r="L206" s="191"/>
+      <c r="K206" s="191"/>
+      <c r="L206" s="192"/>
       <c r="M206" s="58"/>
       <c r="N206" s="67"/>
       <c r="O206" s="67"/>
@@ -10589,8 +10582,8 @@
       <c r="H207" s="67"/>
       <c r="I207" s="67"/>
       <c r="J207" s="67"/>
-      <c r="K207" s="190"/>
-      <c r="L207" s="191"/>
+      <c r="K207" s="191"/>
+      <c r="L207" s="192"/>
       <c r="M207" s="58"/>
       <c r="N207" s="67"/>
       <c r="O207" s="67"/>
@@ -10625,8 +10618,8 @@
       <c r="H208" s="67"/>
       <c r="I208" s="67"/>
       <c r="J208" s="67"/>
-      <c r="K208" s="190"/>
-      <c r="L208" s="191"/>
+      <c r="K208" s="191"/>
+      <c r="L208" s="192"/>
       <c r="M208" s="58"/>
       <c r="N208" s="67"/>
       <c r="O208" s="67"/>
@@ -10661,8 +10654,8 @@
       <c r="H209" s="67"/>
       <c r="I209" s="67"/>
       <c r="J209" s="67"/>
-      <c r="K209" s="190"/>
-      <c r="L209" s="191"/>
+      <c r="K209" s="191"/>
+      <c r="L209" s="192"/>
       <c r="M209" s="58"/>
       <c r="N209" s="67"/>
       <c r="O209" s="67"/>
@@ -10697,8 +10690,8 @@
       <c r="H210" s="67"/>
       <c r="I210" s="67"/>
       <c r="J210" s="67"/>
-      <c r="K210" s="190"/>
-      <c r="L210" s="191"/>
+      <c r="K210" s="191"/>
+      <c r="L210" s="192"/>
       <c r="M210" s="58"/>
       <c r="N210" s="67"/>
       <c r="O210" s="67"/>
@@ -10733,8 +10726,8 @@
       <c r="H211" s="67"/>
       <c r="I211" s="67"/>
       <c r="J211" s="67"/>
-      <c r="K211" s="190"/>
-      <c r="L211" s="191"/>
+      <c r="K211" s="191"/>
+      <c r="L211" s="192"/>
       <c r="M211" s="58"/>
       <c r="N211" s="67"/>
       <c r="O211" s="67"/>
@@ -10769,8 +10762,8 @@
       <c r="H212" s="67"/>
       <c r="I212" s="67"/>
       <c r="J212" s="67"/>
-      <c r="K212" s="190"/>
-      <c r="L212" s="191"/>
+      <c r="K212" s="191"/>
+      <c r="L212" s="192"/>
       <c r="M212" s="58"/>
       <c r="N212" s="67"/>
       <c r="O212" s="67"/>
@@ -10805,8 +10798,8 @@
       <c r="H213" s="67"/>
       <c r="I213" s="67"/>
       <c r="J213" s="67"/>
-      <c r="K213" s="190"/>
-      <c r="L213" s="191"/>
+      <c r="K213" s="191"/>
+      <c r="L213" s="192"/>
       <c r="M213" s="58"/>
       <c r="N213" s="67"/>
       <c r="O213" s="67"/>
@@ -10841,8 +10834,8 @@
       <c r="H214" s="67"/>
       <c r="I214" s="67"/>
       <c r="J214" s="67"/>
-      <c r="K214" s="190"/>
-      <c r="L214" s="191"/>
+      <c r="K214" s="191"/>
+      <c r="L214" s="192"/>
       <c r="M214" s="58"/>
       <c r="N214" s="67"/>
       <c r="O214" s="67"/>
@@ -10877,8 +10870,8 @@
       <c r="H215" s="67"/>
       <c r="I215" s="67"/>
       <c r="J215" s="67"/>
-      <c r="K215" s="190"/>
-      <c r="L215" s="191"/>
+      <c r="K215" s="191"/>
+      <c r="L215" s="192"/>
       <c r="M215" s="58"/>
       <c r="N215" s="67"/>
       <c r="O215" s="67"/>
@@ -10913,8 +10906,8 @@
       <c r="H216" s="67"/>
       <c r="I216" s="67"/>
       <c r="J216" s="67"/>
-      <c r="K216" s="190"/>
-      <c r="L216" s="191"/>
+      <c r="K216" s="191"/>
+      <c r="L216" s="192"/>
       <c r="M216" s="58"/>
       <c r="N216" s="67"/>
       <c r="O216" s="67"/>
@@ -10949,8 +10942,8 @@
       <c r="H217" s="67"/>
       <c r="I217" s="67"/>
       <c r="J217" s="67"/>
-      <c r="K217" s="190"/>
-      <c r="L217" s="191"/>
+      <c r="K217" s="191"/>
+      <c r="L217" s="192"/>
       <c r="M217" s="58"/>
       <c r="N217" s="67"/>
       <c r="O217" s="67"/>
@@ -10985,8 +10978,8 @@
       <c r="H218" s="67"/>
       <c r="I218" s="67"/>
       <c r="J218" s="67"/>
-      <c r="K218" s="190"/>
-      <c r="L218" s="191"/>
+      <c r="K218" s="191"/>
+      <c r="L218" s="192"/>
       <c r="M218" s="58"/>
       <c r="N218" s="67"/>
       <c r="O218" s="67"/>
@@ -11021,8 +11014,8 @@
       <c r="H219" s="67"/>
       <c r="I219" s="67"/>
       <c r="J219" s="67"/>
-      <c r="K219" s="190"/>
-      <c r="L219" s="191"/>
+      <c r="K219" s="191"/>
+      <c r="L219" s="192"/>
       <c r="M219" s="58"/>
       <c r="N219" s="67"/>
       <c r="O219" s="67"/>
@@ -11057,8 +11050,8 @@
       <c r="H220" s="67"/>
       <c r="I220" s="67"/>
       <c r="J220" s="67"/>
-      <c r="K220" s="190"/>
-      <c r="L220" s="191"/>
+      <c r="K220" s="191"/>
+      <c r="L220" s="192"/>
       <c r="M220" s="58"/>
       <c r="N220" s="67"/>
       <c r="O220" s="67"/>
@@ -11093,8 +11086,8 @@
       <c r="H221" s="67"/>
       <c r="I221" s="67"/>
       <c r="J221" s="67"/>
-      <c r="K221" s="190"/>
-      <c r="L221" s="191"/>
+      <c r="K221" s="191"/>
+      <c r="L221" s="192"/>
       <c r="M221" s="58"/>
       <c r="N221" s="67"/>
       <c r="O221" s="67"/>
@@ -11129,8 +11122,8 @@
       <c r="H222" s="67"/>
       <c r="I222" s="67"/>
       <c r="J222" s="67"/>
-      <c r="K222" s="190"/>
-      <c r="L222" s="191"/>
+      <c r="K222" s="191"/>
+      <c r="L222" s="192"/>
       <c r="M222" s="58"/>
       <c r="N222" s="67"/>
       <c r="O222" s="67"/>
@@ -11165,8 +11158,8 @@
       <c r="H223" s="67"/>
       <c r="I223" s="67"/>
       <c r="J223" s="67"/>
-      <c r="K223" s="190"/>
-      <c r="L223" s="191"/>
+      <c r="K223" s="191"/>
+      <c r="L223" s="192"/>
       <c r="M223" s="58"/>
       <c r="N223" s="67"/>
       <c r="O223" s="67"/>
@@ -11201,8 +11194,8 @@
       <c r="H224" s="67"/>
       <c r="I224" s="67"/>
       <c r="J224" s="67"/>
-      <c r="K224" s="190"/>
-      <c r="L224" s="191"/>
+      <c r="K224" s="191"/>
+      <c r="L224" s="192"/>
       <c r="M224" s="58"/>
       <c r="N224" s="67"/>
       <c r="O224" s="67"/>
@@ -11237,8 +11230,8 @@
       <c r="H225" s="67"/>
       <c r="I225" s="67"/>
       <c r="J225" s="67"/>
-      <c r="K225" s="190"/>
-      <c r="L225" s="191"/>
+      <c r="K225" s="191"/>
+      <c r="L225" s="192"/>
       <c r="M225" s="58"/>
       <c r="N225" s="67"/>
       <c r="O225" s="67"/>
@@ -11273,8 +11266,8 @@
       <c r="H226" s="67"/>
       <c r="I226" s="67"/>
       <c r="J226" s="67"/>
-      <c r="K226" s="190"/>
-      <c r="L226" s="191"/>
+      <c r="K226" s="191"/>
+      <c r="L226" s="192"/>
       <c r="M226" s="58"/>
       <c r="N226" s="67"/>
       <c r="O226" s="67"/>
@@ -11309,8 +11302,8 @@
       <c r="H227" s="67"/>
       <c r="I227" s="67"/>
       <c r="J227" s="67"/>
-      <c r="K227" s="190"/>
-      <c r="L227" s="191"/>
+      <c r="K227" s="191"/>
+      <c r="L227" s="192"/>
       <c r="M227" s="58"/>
       <c r="N227" s="67"/>
       <c r="O227" s="67"/>
@@ -11345,8 +11338,8 @@
       <c r="H228" s="67"/>
       <c r="I228" s="67"/>
       <c r="J228" s="67"/>
-      <c r="K228" s="190"/>
-      <c r="L228" s="191"/>
+      <c r="K228" s="191"/>
+      <c r="L228" s="192"/>
       <c r="M228" s="58"/>
       <c r="N228" s="67"/>
       <c r="O228" s="67"/>
@@ -11381,8 +11374,8 @@
       <c r="H229" s="67"/>
       <c r="I229" s="67"/>
       <c r="J229" s="67"/>
-      <c r="K229" s="190"/>
-      <c r="L229" s="191"/>
+      <c r="K229" s="191"/>
+      <c r="L229" s="192"/>
       <c r="M229" s="58"/>
       <c r="N229" s="67"/>
       <c r="O229" s="67"/>
@@ -11417,8 +11410,8 @@
       <c r="H230" s="67"/>
       <c r="I230" s="67"/>
       <c r="J230" s="67"/>
-      <c r="K230" s="190"/>
-      <c r="L230" s="191"/>
+      <c r="K230" s="191"/>
+      <c r="L230" s="192"/>
       <c r="M230" s="58"/>
       <c r="N230" s="67"/>
       <c r="O230" s="67"/>
@@ -11453,8 +11446,8 @@
       <c r="H231" s="67"/>
       <c r="I231" s="67"/>
       <c r="J231" s="67"/>
-      <c r="K231" s="190"/>
-      <c r="L231" s="191"/>
+      <c r="K231" s="191"/>
+      <c r="L231" s="192"/>
       <c r="M231" s="58"/>
       <c r="N231" s="67"/>
       <c r="O231" s="67"/>
@@ -11489,8 +11482,8 @@
       <c r="H232" s="67"/>
       <c r="I232" s="67"/>
       <c r="J232" s="67"/>
-      <c r="K232" s="190"/>
-      <c r="L232" s="191"/>
+      <c r="K232" s="191"/>
+      <c r="L232" s="192"/>
       <c r="M232" s="58"/>
       <c r="N232" s="67"/>
       <c r="O232" s="67"/>
@@ -11525,8 +11518,8 @@
       <c r="H233" s="67"/>
       <c r="I233" s="67"/>
       <c r="J233" s="67"/>
-      <c r="K233" s="190"/>
-      <c r="L233" s="191"/>
+      <c r="K233" s="191"/>
+      <c r="L233" s="192"/>
       <c r="M233" s="58"/>
       <c r="N233" s="67"/>
       <c r="O233" s="67"/>
@@ -11561,8 +11554,8 @@
       <c r="H234" s="67"/>
       <c r="I234" s="67"/>
       <c r="J234" s="67"/>
-      <c r="K234" s="190"/>
-      <c r="L234" s="191"/>
+      <c r="K234" s="191"/>
+      <c r="L234" s="192"/>
       <c r="M234" s="58"/>
       <c r="N234" s="67"/>
       <c r="O234" s="67"/>
@@ -11597,8 +11590,8 @@
       <c r="H235" s="67"/>
       <c r="I235" s="67"/>
       <c r="J235" s="67"/>
-      <c r="K235" s="190"/>
-      <c r="L235" s="191"/>
+      <c r="K235" s="191"/>
+      <c r="L235" s="192"/>
       <c r="M235" s="58"/>
       <c r="N235" s="67"/>
       <c r="O235" s="67"/>
@@ -11633,8 +11626,8 @@
       <c r="H236" s="67"/>
       <c r="I236" s="67"/>
       <c r="J236" s="67"/>
-      <c r="K236" s="190"/>
-      <c r="L236" s="191"/>
+      <c r="K236" s="191"/>
+      <c r="L236" s="192"/>
       <c r="M236" s="58"/>
       <c r="N236" s="67"/>
       <c r="O236" s="67"/>
@@ -11669,8 +11662,8 @@
       <c r="H237" s="67"/>
       <c r="I237" s="67"/>
       <c r="J237" s="67"/>
-      <c r="K237" s="190"/>
-      <c r="L237" s="191"/>
+      <c r="K237" s="191"/>
+      <c r="L237" s="192"/>
       <c r="M237" s="58"/>
       <c r="N237" s="67"/>
       <c r="O237" s="67"/>
@@ -11705,8 +11698,8 @@
       <c r="H238" s="67"/>
       <c r="I238" s="67"/>
       <c r="J238" s="67"/>
-      <c r="K238" s="190"/>
-      <c r="L238" s="191"/>
+      <c r="K238" s="191"/>
+      <c r="L238" s="192"/>
       <c r="M238" s="58"/>
       <c r="N238" s="67"/>
       <c r="O238" s="67"/>
@@ -11741,8 +11734,8 @@
       <c r="H239" s="67"/>
       <c r="I239" s="67"/>
       <c r="J239" s="67"/>
-      <c r="K239" s="190"/>
-      <c r="L239" s="191"/>
+      <c r="K239" s="191"/>
+      <c r="L239" s="192"/>
       <c r="M239" s="58"/>
       <c r="N239" s="67"/>
       <c r="O239" s="67"/>
@@ -11777,8 +11770,8 @@
       <c r="H240" s="67"/>
       <c r="I240" s="67"/>
       <c r="J240" s="67"/>
-      <c r="K240" s="190"/>
-      <c r="L240" s="191"/>
+      <c r="K240" s="191"/>
+      <c r="L240" s="192"/>
       <c r="M240" s="58"/>
       <c r="N240" s="67"/>
       <c r="O240" s="67"/>
@@ -11813,8 +11806,8 @@
       <c r="H241" s="67"/>
       <c r="I241" s="67"/>
       <c r="J241" s="67"/>
-      <c r="K241" s="190"/>
-      <c r="L241" s="191"/>
+      <c r="K241" s="191"/>
+      <c r="L241" s="192"/>
       <c r="M241" s="58"/>
       <c r="N241" s="67"/>
       <c r="O241" s="67"/>
@@ -11849,8 +11842,8 @@
       <c r="H242" s="67"/>
       <c r="I242" s="67"/>
       <c r="J242" s="67"/>
-      <c r="K242" s="190"/>
-      <c r="L242" s="191"/>
+      <c r="K242" s="191"/>
+      <c r="L242" s="192"/>
       <c r="M242" s="58"/>
       <c r="N242" s="67"/>
       <c r="O242" s="67"/>
@@ -11885,8 +11878,8 @@
       <c r="H243" s="67"/>
       <c r="I243" s="67"/>
       <c r="J243" s="67"/>
-      <c r="K243" s="190"/>
-      <c r="L243" s="191"/>
+      <c r="K243" s="191"/>
+      <c r="L243" s="192"/>
       <c r="M243" s="58"/>
       <c r="N243" s="67"/>
       <c r="O243" s="67"/>
@@ -11921,8 +11914,8 @@
       <c r="H244" s="67"/>
       <c r="I244" s="67"/>
       <c r="J244" s="67"/>
-      <c r="K244" s="190"/>
-      <c r="L244" s="191"/>
+      <c r="K244" s="191"/>
+      <c r="L244" s="192"/>
       <c r="M244" s="58"/>
       <c r="N244" s="67"/>
       <c r="O244" s="67"/>
@@ -11957,8 +11950,8 @@
       <c r="H245" s="67"/>
       <c r="I245" s="67"/>
       <c r="J245" s="67"/>
-      <c r="K245" s="190"/>
-      <c r="L245" s="191"/>
+      <c r="K245" s="191"/>
+      <c r="L245" s="192"/>
       <c r="M245" s="58"/>
       <c r="N245" s="67"/>
       <c r="O245" s="67"/>
@@ -11993,8 +11986,8 @@
       <c r="H246" s="67"/>
       <c r="I246" s="67"/>
       <c r="J246" s="67"/>
-      <c r="K246" s="190"/>
-      <c r="L246" s="191"/>
+      <c r="K246" s="191"/>
+      <c r="L246" s="192"/>
       <c r="M246" s="58"/>
       <c r="N246" s="67"/>
       <c r="O246" s="67"/>
@@ -12029,8 +12022,8 @@
       <c r="H247" s="67"/>
       <c r="I247" s="67"/>
       <c r="J247" s="67"/>
-      <c r="K247" s="190"/>
-      <c r="L247" s="191"/>
+      <c r="K247" s="191"/>
+      <c r="L247" s="192"/>
       <c r="M247" s="58"/>
       <c r="N247" s="67"/>
       <c r="O247" s="67"/>
@@ -12065,8 +12058,8 @@
       <c r="H248" s="67"/>
       <c r="I248" s="67"/>
       <c r="J248" s="67"/>
-      <c r="K248" s="190"/>
-      <c r="L248" s="191"/>
+      <c r="K248" s="191"/>
+      <c r="L248" s="192"/>
       <c r="M248" s="58"/>
       <c r="N248" s="67"/>
       <c r="O248" s="67"/>
@@ -12101,8 +12094,8 @@
       <c r="H249" s="67"/>
       <c r="I249" s="67"/>
       <c r="J249" s="67"/>
-      <c r="K249" s="190"/>
-      <c r="L249" s="191"/>
+      <c r="K249" s="191"/>
+      <c r="L249" s="192"/>
       <c r="M249" s="58"/>
       <c r="N249" s="67"/>
       <c r="O249" s="67"/>
@@ -12137,8 +12130,8 @@
       <c r="H250" s="67"/>
       <c r="I250" s="67"/>
       <c r="J250" s="67"/>
-      <c r="K250" s="190"/>
-      <c r="L250" s="191"/>
+      <c r="K250" s="191"/>
+      <c r="L250" s="192"/>
       <c r="M250" s="58"/>
       <c r="N250" s="67"/>
       <c r="O250" s="67"/>
@@ -12173,8 +12166,8 @@
       <c r="H251" s="67"/>
       <c r="I251" s="67"/>
       <c r="J251" s="67"/>
-      <c r="K251" s="190"/>
-      <c r="L251" s="191"/>
+      <c r="K251" s="191"/>
+      <c r="L251" s="192"/>
       <c r="M251" s="58"/>
       <c r="N251" s="67"/>
       <c r="O251" s="67"/>
@@ -12209,8 +12202,8 @@
       <c r="H252" s="67"/>
       <c r="I252" s="67"/>
       <c r="J252" s="67"/>
-      <c r="K252" s="190"/>
-      <c r="L252" s="191"/>
+      <c r="K252" s="191"/>
+      <c r="L252" s="192"/>
       <c r="M252" s="58"/>
       <c r="N252" s="67"/>
       <c r="O252" s="67"/>
@@ -12245,8 +12238,8 @@
       <c r="H253" s="67"/>
       <c r="I253" s="67"/>
       <c r="J253" s="67"/>
-      <c r="K253" s="190"/>
-      <c r="L253" s="191"/>
+      <c r="K253" s="191"/>
+      <c r="L253" s="192"/>
       <c r="M253" s="58"/>
       <c r="N253" s="67"/>
       <c r="O253" s="67"/>
@@ -12281,8 +12274,8 @@
       <c r="H254" s="67"/>
       <c r="I254" s="67"/>
       <c r="J254" s="67"/>
-      <c r="K254" s="190"/>
-      <c r="L254" s="191"/>
+      <c r="K254" s="191"/>
+      <c r="L254" s="192"/>
       <c r="M254" s="58"/>
       <c r="N254" s="67"/>
       <c r="O254" s="67"/>
@@ -12317,8 +12310,8 @@
       <c r="H255" s="67"/>
       <c r="I255" s="67"/>
       <c r="J255" s="67"/>
-      <c r="K255" s="190"/>
-      <c r="L255" s="191"/>
+      <c r="K255" s="191"/>
+      <c r="L255" s="192"/>
       <c r="M255" s="58"/>
       <c r="N255" s="67"/>
       <c r="O255" s="67"/>
@@ -12353,8 +12346,8 @@
       <c r="H256" s="67"/>
       <c r="I256" s="67"/>
       <c r="J256" s="67"/>
-      <c r="K256" s="190"/>
-      <c r="L256" s="191"/>
+      <c r="K256" s="191"/>
+      <c r="L256" s="192"/>
       <c r="M256" s="58"/>
       <c r="N256" s="67"/>
       <c r="O256" s="67"/>
@@ -12389,8 +12382,8 @@
       <c r="H257" s="67"/>
       <c r="I257" s="67"/>
       <c r="J257" s="67"/>
-      <c r="K257" s="190"/>
-      <c r="L257" s="191"/>
+      <c r="K257" s="191"/>
+      <c r="L257" s="192"/>
       <c r="M257" s="58"/>
       <c r="N257" s="67"/>
       <c r="O257" s="67"/>
@@ -12425,8 +12418,8 @@
       <c r="H258" s="67"/>
       <c r="I258" s="67"/>
       <c r="J258" s="67"/>
-      <c r="K258" s="190"/>
-      <c r="L258" s="191"/>
+      <c r="K258" s="191"/>
+      <c r="L258" s="192"/>
       <c r="M258" s="58"/>
       <c r="N258" s="67"/>
       <c r="O258" s="67"/>
@@ -12461,8 +12454,8 @@
       <c r="H259" s="67"/>
       <c r="I259" s="67"/>
       <c r="J259" s="67"/>
-      <c r="K259" s="190"/>
-      <c r="L259" s="191"/>
+      <c r="K259" s="191"/>
+      <c r="L259" s="192"/>
       <c r="M259" s="58"/>
       <c r="N259" s="67"/>
       <c r="O259" s="67"/>
@@ -12497,8 +12490,8 @@
       <c r="H260" s="67"/>
       <c r="I260" s="67"/>
       <c r="J260" s="67"/>
-      <c r="K260" s="190"/>
-      <c r="L260" s="191"/>
+      <c r="K260" s="191"/>
+      <c r="L260" s="192"/>
       <c r="M260" s="58"/>
       <c r="N260" s="67"/>
       <c r="O260" s="67"/>
@@ -12533,8 +12526,8 @@
       <c r="H261" s="67"/>
       <c r="I261" s="67"/>
       <c r="J261" s="67"/>
-      <c r="K261" s="190"/>
-      <c r="L261" s="191"/>
+      <c r="K261" s="191"/>
+      <c r="L261" s="192"/>
       <c r="M261" s="58"/>
       <c r="N261" s="67"/>
       <c r="O261" s="67"/>
@@ -12569,8 +12562,8 @@
       <c r="H262" s="67"/>
       <c r="I262" s="67"/>
       <c r="J262" s="67"/>
-      <c r="K262" s="190"/>
-      <c r="L262" s="191"/>
+      <c r="K262" s="191"/>
+      <c r="L262" s="192"/>
       <c r="M262" s="58"/>
       <c r="N262" s="67"/>
       <c r="O262" s="67"/>
@@ -12605,8 +12598,8 @@
       <c r="H263" s="67"/>
       <c r="I263" s="67"/>
       <c r="J263" s="67"/>
-      <c r="K263" s="190"/>
-      <c r="L263" s="191"/>
+      <c r="K263" s="191"/>
+      <c r="L263" s="192"/>
       <c r="M263" s="58"/>
       <c r="N263" s="67"/>
       <c r="O263" s="67"/>
@@ -12641,8 +12634,8 @@
       <c r="H264" s="67"/>
       <c r="I264" s="67"/>
       <c r="J264" s="67"/>
-      <c r="K264" s="190"/>
-      <c r="L264" s="191"/>
+      <c r="K264" s="191"/>
+      <c r="L264" s="192"/>
       <c r="M264" s="58"/>
       <c r="N264" s="67"/>
       <c r="O264" s="67"/>
@@ -12677,8 +12670,8 @@
       <c r="H265" s="67"/>
       <c r="I265" s="67"/>
       <c r="J265" s="67"/>
-      <c r="K265" s="190"/>
-      <c r="L265" s="191"/>
+      <c r="K265" s="191"/>
+      <c r="L265" s="192"/>
       <c r="M265" s="58"/>
       <c r="N265" s="67"/>
       <c r="O265" s="67"/>
@@ -12713,8 +12706,8 @@
       <c r="H266" s="67"/>
       <c r="I266" s="67"/>
       <c r="J266" s="67"/>
-      <c r="K266" s="190"/>
-      <c r="L266" s="191"/>
+      <c r="K266" s="191"/>
+      <c r="L266" s="192"/>
       <c r="M266" s="58"/>
       <c r="N266" s="67"/>
       <c r="O266" s="67"/>
@@ -12749,8 +12742,8 @@
       <c r="H267" s="67"/>
       <c r="I267" s="67"/>
       <c r="J267" s="67"/>
-      <c r="K267" s="190"/>
-      <c r="L267" s="191"/>
+      <c r="K267" s="191"/>
+      <c r="L267" s="192"/>
       <c r="M267" s="58"/>
       <c r="N267" s="67"/>
       <c r="O267" s="67"/>
@@ -12785,8 +12778,8 @@
       <c r="H268" s="67"/>
       <c r="I268" s="67"/>
       <c r="J268" s="67"/>
-      <c r="K268" s="190"/>
-      <c r="L268" s="191"/>
+      <c r="K268" s="191"/>
+      <c r="L268" s="192"/>
       <c r="M268" s="58"/>
       <c r="N268" s="67"/>
       <c r="O268" s="67"/>
@@ -12821,8 +12814,8 @@
       <c r="H269" s="67"/>
       <c r="I269" s="67"/>
       <c r="J269" s="67"/>
-      <c r="K269" s="190"/>
-      <c r="L269" s="191"/>
+      <c r="K269" s="191"/>
+      <c r="L269" s="192"/>
       <c r="M269" s="58"/>
       <c r="N269" s="67"/>
       <c r="O269" s="67"/>
@@ -12857,8 +12850,8 @@
       <c r="H270" s="67"/>
       <c r="I270" s="67"/>
       <c r="J270" s="67"/>
-      <c r="K270" s="190"/>
-      <c r="L270" s="191"/>
+      <c r="K270" s="191"/>
+      <c r="L270" s="192"/>
       <c r="M270" s="58"/>
       <c r="N270" s="67"/>
       <c r="O270" s="67"/>
@@ -12893,8 +12886,8 @@
       <c r="H271" s="67"/>
       <c r="I271" s="67"/>
       <c r="J271" s="67"/>
-      <c r="K271" s="190"/>
-      <c r="L271" s="191"/>
+      <c r="K271" s="191"/>
+      <c r="L271" s="192"/>
       <c r="M271" s="58"/>
       <c r="N271" s="67"/>
       <c r="O271" s="67"/>
@@ -12929,8 +12922,8 @@
       <c r="H272" s="67"/>
       <c r="I272" s="67"/>
       <c r="J272" s="67"/>
-      <c r="K272" s="190"/>
-      <c r="L272" s="191"/>
+      <c r="K272" s="191"/>
+      <c r="L272" s="192"/>
       <c r="M272" s="58"/>
       <c r="N272" s="67"/>
       <c r="O272" s="67"/>
@@ -12965,8 +12958,8 @@
       <c r="H273" s="67"/>
       <c r="I273" s="67"/>
       <c r="J273" s="67"/>
-      <c r="K273" s="190"/>
-      <c r="L273" s="191"/>
+      <c r="K273" s="191"/>
+      <c r="L273" s="192"/>
       <c r="M273" s="58"/>
       <c r="N273" s="67"/>
       <c r="O273" s="67"/>
@@ -13001,8 +12994,8 @@
       <c r="H274" s="67"/>
       <c r="I274" s="67"/>
       <c r="J274" s="67"/>
-      <c r="K274" s="190"/>
-      <c r="L274" s="191"/>
+      <c r="K274" s="191"/>
+      <c r="L274" s="192"/>
       <c r="M274" s="58"/>
       <c r="N274" s="67"/>
       <c r="O274" s="67"/>
@@ -13037,8 +13030,8 @@
       <c r="H275" s="67"/>
       <c r="I275" s="67"/>
       <c r="J275" s="67"/>
-      <c r="K275" s="190"/>
-      <c r="L275" s="191"/>
+      <c r="K275" s="191"/>
+      <c r="L275" s="192"/>
       <c r="M275" s="58"/>
       <c r="N275" s="67"/>
       <c r="O275" s="67"/>
@@ -13073,8 +13066,8 @@
       <c r="H276" s="67"/>
       <c r="I276" s="67"/>
       <c r="J276" s="67"/>
-      <c r="K276" s="190"/>
-      <c r="L276" s="191"/>
+      <c r="K276" s="191"/>
+      <c r="L276" s="192"/>
       <c r="M276" s="58"/>
       <c r="N276" s="67"/>
       <c r="O276" s="67"/>
@@ -13109,8 +13102,8 @@
       <c r="H277" s="67"/>
       <c r="I277" s="67"/>
       <c r="J277" s="67"/>
-      <c r="K277" s="190"/>
-      <c r="L277" s="191"/>
+      <c r="K277" s="191"/>
+      <c r="L277" s="192"/>
       <c r="M277" s="58"/>
       <c r="N277" s="67"/>
       <c r="O277" s="67"/>
@@ -13145,8 +13138,8 @@
       <c r="H278" s="67"/>
       <c r="I278" s="67"/>
       <c r="J278" s="67"/>
-      <c r="K278" s="190"/>
-      <c r="L278" s="191"/>
+      <c r="K278" s="191"/>
+      <c r="L278" s="192"/>
       <c r="M278" s="58"/>
       <c r="N278" s="67"/>
       <c r="O278" s="67"/>
@@ -13181,8 +13174,8 @@
       <c r="H279" s="67"/>
       <c r="I279" s="67"/>
       <c r="J279" s="67"/>
-      <c r="K279" s="190"/>
-      <c r="L279" s="191"/>
+      <c r="K279" s="191"/>
+      <c r="L279" s="192"/>
       <c r="M279" s="58"/>
       <c r="N279" s="67"/>
       <c r="O279" s="67"/>
@@ -13217,8 +13210,8 @@
       <c r="H280" s="67"/>
       <c r="I280" s="67"/>
       <c r="J280" s="67"/>
-      <c r="K280" s="190"/>
-      <c r="L280" s="191"/>
+      <c r="K280" s="191"/>
+      <c r="L280" s="192"/>
       <c r="M280" s="58"/>
       <c r="N280" s="67"/>
       <c r="O280" s="67"/>
@@ -13253,8 +13246,8 @@
       <c r="H281" s="67"/>
       <c r="I281" s="67"/>
       <c r="J281" s="67"/>
-      <c r="K281" s="190"/>
-      <c r="L281" s="191"/>
+      <c r="K281" s="191"/>
+      <c r="L281" s="192"/>
       <c r="M281" s="58"/>
       <c r="N281" s="67"/>
       <c r="O281" s="67"/>
@@ -13289,8 +13282,8 @@
       <c r="H282" s="67"/>
       <c r="I282" s="67"/>
       <c r="J282" s="67"/>
-      <c r="K282" s="190"/>
-      <c r="L282" s="191"/>
+      <c r="K282" s="191"/>
+      <c r="L282" s="192"/>
       <c r="M282" s="58"/>
       <c r="N282" s="67"/>
       <c r="O282" s="67"/>
@@ -13325,8 +13318,8 @@
       <c r="H283" s="67"/>
       <c r="I283" s="67"/>
       <c r="J283" s="67"/>
-      <c r="K283" s="190"/>
-      <c r="L283" s="191"/>
+      <c r="K283" s="191"/>
+      <c r="L283" s="192"/>
       <c r="M283" s="58"/>
       <c r="N283" s="67"/>
       <c r="O283" s="67"/>
@@ -13361,8 +13354,8 @@
       <c r="H284" s="67"/>
       <c r="I284" s="67"/>
       <c r="J284" s="67"/>
-      <c r="K284" s="190"/>
-      <c r="L284" s="191"/>
+      <c r="K284" s="191"/>
+      <c r="L284" s="192"/>
       <c r="M284" s="58"/>
       <c r="N284" s="67"/>
       <c r="O284" s="67"/>
@@ -13397,8 +13390,8 @@
       <c r="H285" s="67"/>
       <c r="I285" s="67"/>
       <c r="J285" s="67"/>
-      <c r="K285" s="190"/>
-      <c r="L285" s="191"/>
+      <c r="K285" s="191"/>
+      <c r="L285" s="192"/>
       <c r="M285" s="58"/>
       <c r="N285" s="67"/>
       <c r="O285" s="67"/>
@@ -13433,8 +13426,8 @@
       <c r="H286" s="67"/>
       <c r="I286" s="67"/>
       <c r="J286" s="67"/>
-      <c r="K286" s="190"/>
-      <c r="L286" s="191"/>
+      <c r="K286" s="191"/>
+      <c r="L286" s="192"/>
       <c r="M286" s="58"/>
       <c r="N286" s="67"/>
       <c r="O286" s="67"/>
@@ -13469,8 +13462,8 @@
       <c r="H287" s="67"/>
       <c r="I287" s="67"/>
       <c r="J287" s="67"/>
-      <c r="K287" s="190"/>
-      <c r="L287" s="191"/>
+      <c r="K287" s="191"/>
+      <c r="L287" s="192"/>
       <c r="M287" s="58"/>
       <c r="N287" s="67"/>
       <c r="O287" s="67"/>
@@ -13505,8 +13498,8 @@
       <c r="H288" s="67"/>
       <c r="I288" s="67"/>
       <c r="J288" s="67"/>
-      <c r="K288" s="190"/>
-      <c r="L288" s="191"/>
+      <c r="K288" s="191"/>
+      <c r="L288" s="192"/>
       <c r="M288" s="58"/>
       <c r="N288" s="67"/>
       <c r="O288" s="67"/>
@@ -13541,8 +13534,8 @@
       <c r="H289" s="67"/>
       <c r="I289" s="67"/>
       <c r="J289" s="67"/>
-      <c r="K289" s="190"/>
-      <c r="L289" s="191"/>
+      <c r="K289" s="191"/>
+      <c r="L289" s="192"/>
       <c r="M289" s="58"/>
       <c r="N289" s="67"/>
       <c r="O289" s="67"/>
@@ -13577,8 +13570,8 @@
       <c r="H290" s="67"/>
       <c r="I290" s="67"/>
       <c r="J290" s="67"/>
-      <c r="K290" s="190"/>
-      <c r="L290" s="191"/>
+      <c r="K290" s="191"/>
+      <c r="L290" s="192"/>
       <c r="M290" s="58"/>
       <c r="N290" s="67"/>
       <c r="O290" s="67"/>
@@ -13613,8 +13606,8 @@
       <c r="H291" s="67"/>
       <c r="I291" s="67"/>
       <c r="J291" s="67"/>
-      <c r="K291" s="190"/>
-      <c r="L291" s="191"/>
+      <c r="K291" s="191"/>
+      <c r="L291" s="192"/>
       <c r="M291" s="58"/>
       <c r="N291" s="67"/>
       <c r="O291" s="67"/>
@@ -13649,8 +13642,8 @@
       <c r="H292" s="67"/>
       <c r="I292" s="67"/>
       <c r="J292" s="67"/>
-      <c r="K292" s="190"/>
-      <c r="L292" s="191"/>
+      <c r="K292" s="191"/>
+      <c r="L292" s="192"/>
       <c r="M292" s="58"/>
       <c r="N292" s="67"/>
       <c r="O292" s="67"/>
@@ -13685,8 +13678,8 @@
       <c r="H293" s="67"/>
       <c r="I293" s="67"/>
       <c r="J293" s="67"/>
-      <c r="K293" s="190"/>
-      <c r="L293" s="191"/>
+      <c r="K293" s="191"/>
+      <c r="L293" s="192"/>
       <c r="M293" s="58"/>
       <c r="N293" s="67"/>
       <c r="O293" s="67"/>
@@ -13721,8 +13714,8 @@
       <c r="H294" s="67"/>
       <c r="I294" s="67"/>
       <c r="J294" s="67"/>
-      <c r="K294" s="190"/>
-      <c r="L294" s="191"/>
+      <c r="K294" s="191"/>
+      <c r="L294" s="192"/>
       <c r="M294" s="58"/>
       <c r="N294" s="67"/>
       <c r="O294" s="67"/>
@@ -13757,8 +13750,8 @@
       <c r="H295" s="67"/>
       <c r="I295" s="67"/>
       <c r="J295" s="67"/>
-      <c r="K295" s="190"/>
-      <c r="L295" s="191"/>
+      <c r="K295" s="191"/>
+      <c r="L295" s="192"/>
       <c r="M295" s="58"/>
       <c r="N295" s="67"/>
       <c r="O295" s="67"/>
@@ -13793,8 +13786,8 @@
       <c r="H296" s="67"/>
       <c r="I296" s="67"/>
       <c r="J296" s="67"/>
-      <c r="K296" s="190"/>
-      <c r="L296" s="191"/>
+      <c r="K296" s="191"/>
+      <c r="L296" s="192"/>
       <c r="M296" s="58"/>
       <c r="N296" s="67"/>
       <c r="O296" s="67"/>
@@ -13829,8 +13822,8 @@
       <c r="H297" s="67"/>
       <c r="I297" s="67"/>
       <c r="J297" s="67"/>
-      <c r="K297" s="190"/>
-      <c r="L297" s="191"/>
+      <c r="K297" s="191"/>
+      <c r="L297" s="192"/>
       <c r="M297" s="58"/>
       <c r="N297" s="67"/>
       <c r="O297" s="67"/>
@@ -13865,8 +13858,8 @@
       <c r="H298" s="67"/>
       <c r="I298" s="67"/>
       <c r="J298" s="67"/>
-      <c r="K298" s="190"/>
-      <c r="L298" s="191"/>
+      <c r="K298" s="191"/>
+      <c r="L298" s="192"/>
       <c r="M298" s="58"/>
       <c r="N298" s="67"/>
       <c r="O298" s="67"/>
@@ -13901,8 +13894,8 @@
       <c r="H299" s="67"/>
       <c r="I299" s="67"/>
       <c r="J299" s="67"/>
-      <c r="K299" s="190"/>
-      <c r="L299" s="191"/>
+      <c r="K299" s="191"/>
+      <c r="L299" s="192"/>
       <c r="M299" s="58"/>
       <c r="N299" s="67"/>
       <c r="O299" s="67"/>
@@ -13937,8 +13930,8 @@
       <c r="H300" s="67"/>
       <c r="I300" s="67"/>
       <c r="J300" s="67"/>
-      <c r="K300" s="190"/>
-      <c r="L300" s="191"/>
+      <c r="K300" s="191"/>
+      <c r="L300" s="192"/>
       <c r="M300" s="58"/>
       <c r="N300" s="67"/>
       <c r="O300" s="67"/>
@@ -13973,8 +13966,8 @@
       <c r="H301" s="67"/>
       <c r="I301" s="67"/>
       <c r="J301" s="67"/>
-      <c r="K301" s="190"/>
-      <c r="L301" s="191"/>
+      <c r="K301" s="191"/>
+      <c r="L301" s="192"/>
       <c r="M301" s="58"/>
       <c r="N301" s="67"/>
       <c r="O301" s="67"/>
@@ -14009,8 +14002,8 @@
       <c r="H302" s="67"/>
       <c r="I302" s="67"/>
       <c r="J302" s="67"/>
-      <c r="K302" s="190"/>
-      <c r="L302" s="191"/>
+      <c r="K302" s="191"/>
+      <c r="L302" s="192"/>
       <c r="M302" s="58"/>
       <c r="N302" s="67"/>
       <c r="O302" s="67"/>
@@ -14045,8 +14038,8 @@
       <c r="H303" s="67"/>
       <c r="I303" s="67"/>
       <c r="J303" s="67"/>
-      <c r="K303" s="190"/>
-      <c r="L303" s="191"/>
+      <c r="K303" s="191"/>
+      <c r="L303" s="192"/>
       <c r="M303" s="58"/>
       <c r="N303" s="67"/>
       <c r="O303" s="67"/>
@@ -14081,8 +14074,8 @@
       <c r="H304" s="67"/>
       <c r="I304" s="67"/>
       <c r="J304" s="67"/>
-      <c r="K304" s="190"/>
-      <c r="L304" s="191"/>
+      <c r="K304" s="191"/>
+      <c r="L304" s="192"/>
       <c r="M304" s="58"/>
       <c r="N304" s="67"/>
       <c r="O304" s="67"/>
@@ -14117,8 +14110,8 @@
       <c r="H305" s="67"/>
       <c r="I305" s="67"/>
       <c r="J305" s="67"/>
-      <c r="K305" s="190"/>
-      <c r="L305" s="191"/>
+      <c r="K305" s="191"/>
+      <c r="L305" s="192"/>
       <c r="M305" s="58"/>
       <c r="N305" s="67"/>
       <c r="O305" s="67"/>
@@ -14153,8 +14146,8 @@
       <c r="H306" s="67"/>
       <c r="I306" s="67"/>
       <c r="J306" s="67"/>
-      <c r="K306" s="190"/>
-      <c r="L306" s="191"/>
+      <c r="K306" s="191"/>
+      <c r="L306" s="192"/>
       <c r="M306" s="58"/>
       <c r="N306" s="67"/>
       <c r="O306" s="67"/>
@@ -14189,8 +14182,8 @@
       <c r="H307" s="67"/>
       <c r="I307" s="67"/>
       <c r="J307" s="67"/>
-      <c r="K307" s="190"/>
-      <c r="L307" s="191"/>
+      <c r="K307" s="191"/>
+      <c r="L307" s="192"/>
       <c r="M307" s="58"/>
       <c r="N307" s="67"/>
       <c r="O307" s="67"/>
@@ -14225,8 +14218,8 @@
       <c r="H308" s="67"/>
       <c r="I308" s="67"/>
       <c r="J308" s="67"/>
-      <c r="K308" s="190"/>
-      <c r="L308" s="191"/>
+      <c r="K308" s="191"/>
+      <c r="L308" s="192"/>
       <c r="M308" s="58"/>
       <c r="N308" s="67"/>
       <c r="O308" s="67"/>
@@ -14261,8 +14254,8 @@
       <c r="H309" s="67"/>
       <c r="I309" s="67"/>
       <c r="J309" s="67"/>
-      <c r="K309" s="190"/>
-      <c r="L309" s="191"/>
+      <c r="K309" s="191"/>
+      <c r="L309" s="192"/>
       <c r="M309" s="58"/>
       <c r="N309" s="67"/>
       <c r="O309" s="67"/>
@@ -14297,8 +14290,8 @@
       <c r="H310" s="67"/>
       <c r="I310" s="67"/>
       <c r="J310" s="67"/>
-      <c r="K310" s="190"/>
-      <c r="L310" s="191"/>
+      <c r="K310" s="191"/>
+      <c r="L310" s="192"/>
       <c r="M310" s="58"/>
       <c r="N310" s="67"/>
       <c r="O310" s="67"/>
@@ -14333,8 +14326,8 @@
       <c r="H311" s="67"/>
       <c r="I311" s="67"/>
       <c r="J311" s="67"/>
-      <c r="K311" s="190"/>
-      <c r="L311" s="191"/>
+      <c r="K311" s="191"/>
+      <c r="L311" s="192"/>
       <c r="M311" s="58"/>
       <c r="N311" s="67"/>
       <c r="O311" s="67"/>
@@ -14369,8 +14362,8 @@
       <c r="H312" s="67"/>
       <c r="I312" s="67"/>
       <c r="J312" s="67"/>
-      <c r="K312" s="190"/>
-      <c r="L312" s="191"/>
+      <c r="K312" s="191"/>
+      <c r="L312" s="192"/>
       <c r="M312" s="58"/>
       <c r="N312" s="67"/>
       <c r="O312" s="67"/>
@@ -14405,8 +14398,8 @@
       <c r="H313" s="67"/>
       <c r="I313" s="67"/>
       <c r="J313" s="67"/>
-      <c r="K313" s="190"/>
-      <c r="L313" s="191"/>
+      <c r="K313" s="191"/>
+      <c r="L313" s="192"/>
       <c r="M313" s="58"/>
       <c r="N313" s="67"/>
       <c r="O313" s="67"/>
@@ -14441,8 +14434,8 @@
       <c r="H314" s="67"/>
       <c r="I314" s="67"/>
       <c r="J314" s="67"/>
-      <c r="K314" s="190"/>
-      <c r="L314" s="191"/>
+      <c r="K314" s="191"/>
+      <c r="L314" s="192"/>
       <c r="M314" s="58"/>
       <c r="N314" s="67"/>
       <c r="O314" s="67"/>
@@ -14477,8 +14470,8 @@
       <c r="H315" s="67"/>
       <c r="I315" s="67"/>
       <c r="J315" s="67"/>
-      <c r="K315" s="190"/>
-      <c r="L315" s="191"/>
+      <c r="K315" s="191"/>
+      <c r="L315" s="192"/>
       <c r="M315" s="58"/>
       <c r="N315" s="67"/>
       <c r="O315" s="67"/>
@@ -14513,8 +14506,8 @@
       <c r="H316" s="67"/>
       <c r="I316" s="67"/>
       <c r="J316" s="67"/>
-      <c r="K316" s="190"/>
-      <c r="L316" s="191"/>
+      <c r="K316" s="191"/>
+      <c r="L316" s="192"/>
       <c r="M316" s="58"/>
       <c r="N316" s="67"/>
       <c r="O316" s="67"/>
@@ -14549,8 +14542,8 @@
       <c r="H317" s="67"/>
       <c r="I317" s="67"/>
       <c r="J317" s="67"/>
-      <c r="K317" s="190"/>
-      <c r="L317" s="191"/>
+      <c r="K317" s="191"/>
+      <c r="L317" s="192"/>
       <c r="M317" s="58"/>
       <c r="N317" s="67"/>
       <c r="O317" s="67"/>
@@ -14585,8 +14578,8 @@
       <c r="H318" s="67"/>
       <c r="I318" s="67"/>
       <c r="J318" s="67"/>
-      <c r="K318" s="190"/>
-      <c r="L318" s="191"/>
+      <c r="K318" s="191"/>
+      <c r="L318" s="192"/>
       <c r="M318" s="58"/>
       <c r="N318" s="67"/>
       <c r="O318" s="67"/>
@@ -14621,8 +14614,8 @@
       <c r="H319" s="67"/>
       <c r="I319" s="67"/>
       <c r="J319" s="67"/>
-      <c r="K319" s="190"/>
-      <c r="L319" s="191"/>
+      <c r="K319" s="191"/>
+      <c r="L319" s="192"/>
       <c r="M319" s="58"/>
       <c r="N319" s="67"/>
       <c r="O319" s="67"/>
@@ -14657,8 +14650,8 @@
       <c r="H320" s="67"/>
       <c r="I320" s="67"/>
       <c r="J320" s="67"/>
-      <c r="K320" s="190"/>
-      <c r="L320" s="191"/>
+      <c r="K320" s="191"/>
+      <c r="L320" s="192"/>
       <c r="M320" s="58"/>
       <c r="N320" s="67"/>
       <c r="O320" s="67"/>
@@ -14693,8 +14686,8 @@
       <c r="H321" s="67"/>
       <c r="I321" s="67"/>
       <c r="J321" s="67"/>
-      <c r="K321" s="190"/>
-      <c r="L321" s="191"/>
+      <c r="K321" s="191"/>
+      <c r="L321" s="192"/>
       <c r="M321" s="58"/>
       <c r="N321" s="67"/>
       <c r="O321" s="67"/>
@@ -14729,8 +14722,8 @@
       <c r="H322" s="67"/>
       <c r="I322" s="67"/>
       <c r="J322" s="67"/>
-      <c r="K322" s="190"/>
-      <c r="L322" s="191"/>
+      <c r="K322" s="191"/>
+      <c r="L322" s="192"/>
       <c r="M322" s="58"/>
       <c r="N322" s="67"/>
       <c r="O322" s="67"/>
@@ -14765,8 +14758,8 @@
       <c r="H323" s="67"/>
       <c r="I323" s="67"/>
       <c r="J323" s="67"/>
-      <c r="K323" s="190"/>
-      <c r="L323" s="191"/>
+      <c r="K323" s="191"/>
+      <c r="L323" s="192"/>
       <c r="M323" s="58"/>
       <c r="N323" s="67"/>
       <c r="O323" s="67"/>
@@ -14801,8 +14794,8 @@
       <c r="H324" s="67"/>
       <c r="I324" s="67"/>
       <c r="J324" s="67"/>
-      <c r="K324" s="190"/>
-      <c r="L324" s="191"/>
+      <c r="K324" s="191"/>
+      <c r="L324" s="192"/>
       <c r="M324" s="58"/>
       <c r="N324" s="67"/>
       <c r="O324" s="67"/>
@@ -14837,8 +14830,8 @@
       <c r="H325" s="67"/>
       <c r="I325" s="67"/>
       <c r="J325" s="67"/>
-      <c r="K325" s="190"/>
-      <c r="L325" s="191"/>
+      <c r="K325" s="191"/>
+      <c r="L325" s="192"/>
       <c r="M325" s="58"/>
       <c r="N325" s="67"/>
       <c r="O325" s="67"/>
@@ -14873,8 +14866,8 @@
       <c r="H326" s="67"/>
       <c r="I326" s="67"/>
       <c r="J326" s="67"/>
-      <c r="K326" s="190"/>
-      <c r="L326" s="191"/>
+      <c r="K326" s="191"/>
+      <c r="L326" s="192"/>
       <c r="M326" s="58"/>
       <c r="N326" s="67"/>
       <c r="O326" s="67"/>
@@ -14909,8 +14902,8 @@
       <c r="H327" s="67"/>
       <c r="I327" s="67"/>
       <c r="J327" s="67"/>
-      <c r="K327" s="190"/>
-      <c r="L327" s="191"/>
+      <c r="K327" s="191"/>
+      <c r="L327" s="192"/>
       <c r="M327" s="58"/>
       <c r="N327" s="67"/>
       <c r="O327" s="67"/>
@@ -14945,8 +14938,8 @@
       <c r="H328" s="67"/>
       <c r="I328" s="67"/>
       <c r="J328" s="67"/>
-      <c r="K328" s="190"/>
-      <c r="L328" s="191"/>
+      <c r="K328" s="191"/>
+      <c r="L328" s="192"/>
       <c r="M328" s="58"/>
       <c r="N328" s="67"/>
       <c r="O328" s="67"/>
@@ -14981,8 +14974,8 @@
       <c r="H329" s="67"/>
       <c r="I329" s="67"/>
       <c r="J329" s="67"/>
-      <c r="K329" s="190"/>
-      <c r="L329" s="191"/>
+      <c r="K329" s="191"/>
+      <c r="L329" s="192"/>
       <c r="M329" s="58"/>
       <c r="N329" s="67"/>
       <c r="O329" s="67"/>
@@ -15017,8 +15010,8 @@
       <c r="H330" s="67"/>
       <c r="I330" s="67"/>
       <c r="J330" s="67"/>
-      <c r="K330" s="190"/>
-      <c r="L330" s="191"/>
+      <c r="K330" s="191"/>
+      <c r="L330" s="192"/>
       <c r="M330" s="58"/>
       <c r="N330" s="67"/>
       <c r="O330" s="67"/>
@@ -15053,8 +15046,8 @@
       <c r="H331" s="67"/>
       <c r="I331" s="67"/>
       <c r="J331" s="67"/>
-      <c r="K331" s="190"/>
-      <c r="L331" s="191"/>
+      <c r="K331" s="191"/>
+      <c r="L331" s="192"/>
       <c r="M331" s="58"/>
       <c r="N331" s="67"/>
       <c r="O331" s="67"/>
@@ -15089,8 +15082,8 @@
       <c r="H332" s="67"/>
       <c r="I332" s="67"/>
       <c r="J332" s="67"/>
-      <c r="K332" s="190"/>
-      <c r="L332" s="191"/>
+      <c r="K332" s="191"/>
+      <c r="L332" s="192"/>
       <c r="M332" s="58"/>
       <c r="N332" s="67"/>
       <c r="O332" s="67"/>
@@ -15125,8 +15118,8 @@
       <c r="H333" s="67"/>
       <c r="I333" s="67"/>
       <c r="J333" s="67"/>
-      <c r="K333" s="190"/>
-      <c r="L333" s="191"/>
+      <c r="K333" s="191"/>
+      <c r="L333" s="192"/>
       <c r="M333" s="58"/>
       <c r="N333" s="67"/>
       <c r="O333" s="67"/>
@@ -15161,8 +15154,8 @@
       <c r="H334" s="67"/>
       <c r="I334" s="67"/>
       <c r="J334" s="67"/>
-      <c r="K334" s="190"/>
-      <c r="L334" s="191"/>
+      <c r="K334" s="191"/>
+      <c r="L334" s="192"/>
       <c r="M334" s="58"/>
       <c r="N334" s="67"/>
       <c r="O334" s="67"/>
@@ -15197,8 +15190,8 @@
       <c r="H335" s="67"/>
       <c r="I335" s="67"/>
       <c r="J335" s="67"/>
-      <c r="K335" s="190"/>
-      <c r="L335" s="191"/>
+      <c r="K335" s="191"/>
+      <c r="L335" s="192"/>
       <c r="M335" s="58"/>
       <c r="N335" s="67"/>
       <c r="O335" s="67"/>
@@ -15233,8 +15226,8 @@
       <c r="H336" s="67"/>
       <c r="I336" s="67"/>
       <c r="J336" s="67"/>
-      <c r="K336" s="190"/>
-      <c r="L336" s="191"/>
+      <c r="K336" s="191"/>
+      <c r="L336" s="192"/>
       <c r="M336" s="58"/>
       <c r="N336" s="67"/>
       <c r="O336" s="67"/>
@@ -15269,8 +15262,8 @@
       <c r="H337" s="67"/>
       <c r="I337" s="67"/>
       <c r="J337" s="67"/>
-      <c r="K337" s="190"/>
-      <c r="L337" s="191"/>
+      <c r="K337" s="191"/>
+      <c r="L337" s="192"/>
       <c r="M337" s="58"/>
       <c r="N337" s="67"/>
       <c r="O337" s="67"/>
@@ -15305,8 +15298,8 @@
       <c r="H338" s="67"/>
       <c r="I338" s="67"/>
       <c r="J338" s="67"/>
-      <c r="K338" s="190"/>
-      <c r="L338" s="191"/>
+      <c r="K338" s="191"/>
+      <c r="L338" s="192"/>
       <c r="M338" s="58"/>
       <c r="N338" s="67"/>
       <c r="O338" s="67"/>
@@ -15341,8 +15334,8 @@
       <c r="H339" s="67"/>
       <c r="I339" s="67"/>
       <c r="J339" s="67"/>
-      <c r="K339" s="190"/>
-      <c r="L339" s="191"/>
+      <c r="K339" s="191"/>
+      <c r="L339" s="192"/>
       <c r="M339" s="58"/>
       <c r="N339" s="67"/>
       <c r="O339" s="67"/>
@@ -15377,8 +15370,8 @@
       <c r="H340" s="67"/>
       <c r="I340" s="67"/>
       <c r="J340" s="67"/>
-      <c r="K340" s="190"/>
-      <c r="L340" s="191"/>
+      <c r="K340" s="191"/>
+      <c r="L340" s="192"/>
       <c r="M340" s="58"/>
       <c r="N340" s="67"/>
       <c r="O340" s="67"/>
@@ -15413,8 +15406,8 @@
       <c r="H341" s="67"/>
       <c r="I341" s="67"/>
       <c r="J341" s="67"/>
-      <c r="K341" s="190"/>
-      <c r="L341" s="191"/>
+      <c r="K341" s="191"/>
+      <c r="L341" s="192"/>
       <c r="M341" s="58"/>
       <c r="N341" s="67"/>
       <c r="O341" s="67"/>
@@ -15449,8 +15442,8 @@
       <c r="H342" s="67"/>
       <c r="I342" s="67"/>
       <c r="J342" s="67"/>
-      <c r="K342" s="190"/>
-      <c r="L342" s="191"/>
+      <c r="K342" s="191"/>
+      <c r="L342" s="192"/>
       <c r="M342" s="58"/>
       <c r="N342" s="67"/>
       <c r="O342" s="67"/>
@@ -15485,8 +15478,8 @@
       <c r="H343" s="67"/>
       <c r="I343" s="67"/>
       <c r="J343" s="67"/>
-      <c r="K343" s="190"/>
-      <c r="L343" s="191"/>
+      <c r="K343" s="191"/>
+      <c r="L343" s="192"/>
       <c r="M343" s="58"/>
       <c r="N343" s="67"/>
       <c r="O343" s="67"/>
@@ -15521,8 +15514,8 @@
       <c r="H344" s="67"/>
       <c r="I344" s="67"/>
       <c r="J344" s="67"/>
-      <c r="K344" s="190"/>
-      <c r="L344" s="191"/>
+      <c r="K344" s="191"/>
+      <c r="L344" s="192"/>
       <c r="M344" s="58"/>
       <c r="N344" s="67"/>
       <c r="O344" s="67"/>
@@ -15557,8 +15550,8 @@
       <c r="H345" s="67"/>
       <c r="I345" s="67"/>
       <c r="J345" s="67"/>
-      <c r="K345" s="190"/>
-      <c r="L345" s="191"/>
+      <c r="K345" s="191"/>
+      <c r="L345" s="192"/>
       <c r="M345" s="58"/>
       <c r="N345" s="67"/>
       <c r="O345" s="67"/>
@@ -15593,8 +15586,8 @@
       <c r="H346" s="67"/>
       <c r="I346" s="67"/>
       <c r="J346" s="67"/>
-      <c r="K346" s="190"/>
-      <c r="L346" s="191"/>
+      <c r="K346" s="191"/>
+      <c r="L346" s="192"/>
       <c r="M346" s="58"/>
       <c r="N346" s="67"/>
       <c r="O346" s="67"/>
@@ -15629,8 +15622,8 @@
       <c r="H347" s="67"/>
       <c r="I347" s="67"/>
       <c r="J347" s="67"/>
-      <c r="K347" s="190"/>
-      <c r="L347" s="191"/>
+      <c r="K347" s="191"/>
+      <c r="L347" s="192"/>
       <c r="M347" s="58"/>
       <c r="N347" s="67"/>
       <c r="O347" s="67"/>
@@ -15665,8 +15658,8 @@
       <c r="H348" s="67"/>
       <c r="I348" s="67"/>
       <c r="J348" s="67"/>
-      <c r="K348" s="190"/>
-      <c r="L348" s="191"/>
+      <c r="K348" s="191"/>
+      <c r="L348" s="192"/>
       <c r="M348" s="58"/>
       <c r="N348" s="67"/>
       <c r="O348" s="67"/>
@@ -15701,8 +15694,8 @@
       <c r="H349" s="67"/>
       <c r="I349" s="67"/>
       <c r="J349" s="67"/>
-      <c r="K349" s="190"/>
-      <c r="L349" s="191"/>
+      <c r="K349" s="191"/>
+      <c r="L349" s="192"/>
       <c r="M349" s="58"/>
       <c r="N349" s="67"/>
       <c r="O349" s="67"/>
@@ -15737,8 +15730,8 @@
       <c r="H350" s="67"/>
       <c r="I350" s="67"/>
       <c r="J350" s="67"/>
-      <c r="K350" s="190"/>
-      <c r="L350" s="191"/>
+      <c r="K350" s="191"/>
+      <c r="L350" s="192"/>
       <c r="M350" s="58"/>
       <c r="N350" s="67"/>
       <c r="O350" s="67"/>
@@ -15773,8 +15766,8 @@
       <c r="H351" s="67"/>
       <c r="I351" s="67"/>
       <c r="J351" s="67"/>
-      <c r="K351" s="190"/>
-      <c r="L351" s="191"/>
+      <c r="K351" s="191"/>
+      <c r="L351" s="192"/>
       <c r="M351" s="58"/>
       <c r="N351" s="67"/>
       <c r="O351" s="67"/>
@@ -15809,8 +15802,8 @@
       <c r="H352" s="67"/>
       <c r="I352" s="67"/>
       <c r="J352" s="67"/>
-      <c r="K352" s="190"/>
-      <c r="L352" s="191"/>
+      <c r="K352" s="191"/>
+      <c r="L352" s="192"/>
       <c r="M352" s="58"/>
       <c r="N352" s="67"/>
       <c r="O352" s="67"/>
@@ -15845,8 +15838,8 @@
       <c r="H353" s="67"/>
       <c r="I353" s="67"/>
       <c r="J353" s="67"/>
-      <c r="K353" s="190"/>
-      <c r="L353" s="191"/>
+      <c r="K353" s="191"/>
+      <c r="L353" s="192"/>
       <c r="M353" s="58"/>
       <c r="N353" s="67"/>
       <c r="O353" s="67"/>
@@ -15881,8 +15874,8 @@
       <c r="H354" s="67"/>
       <c r="I354" s="67"/>
       <c r="J354" s="67"/>
-      <c r="K354" s="190"/>
-      <c r="L354" s="191"/>
+      <c r="K354" s="191"/>
+      <c r="L354" s="192"/>
       <c r="M354" s="58"/>
       <c r="N354" s="67"/>
       <c r="O354" s="67"/>
@@ -15917,8 +15910,8 @@
       <c r="H355" s="67"/>
       <c r="I355" s="67"/>
       <c r="J355" s="67"/>
-      <c r="K355" s="190"/>
-      <c r="L355" s="191"/>
+      <c r="K355" s="191"/>
+      <c r="L355" s="192"/>
       <c r="M355" s="58"/>
       <c r="N355" s="67"/>
       <c r="O355" s="67"/>
@@ -15953,8 +15946,8 @@
       <c r="H356" s="67"/>
       <c r="I356" s="67"/>
       <c r="J356" s="67"/>
-      <c r="K356" s="190"/>
-      <c r="L356" s="191"/>
+      <c r="K356" s="191"/>
+      <c r="L356" s="192"/>
       <c r="M356" s="58"/>
       <c r="N356" s="67"/>
       <c r="O356" s="67"/>
@@ -15989,8 +15982,8 @@
       <c r="H357" s="67"/>
       <c r="I357" s="67"/>
       <c r="J357" s="67"/>
-      <c r="K357" s="190"/>
-      <c r="L357" s="191"/>
+      <c r="K357" s="191"/>
+      <c r="L357" s="192"/>
       <c r="M357" s="58"/>
       <c r="N357" s="67"/>
       <c r="O357" s="67"/>
@@ -16025,8 +16018,8 @@
       <c r="H358" s="67"/>
       <c r="I358" s="67"/>
       <c r="J358" s="67"/>
-      <c r="K358" s="190"/>
-      <c r="L358" s="191"/>
+      <c r="K358" s="191"/>
+      <c r="L358" s="192"/>
       <c r="M358" s="58"/>
       <c r="N358" s="67"/>
       <c r="O358" s="67"/>
@@ -16061,8 +16054,8 @@
       <c r="H359" s="67"/>
       <c r="I359" s="67"/>
       <c r="J359" s="67"/>
-      <c r="K359" s="190"/>
-      <c r="L359" s="191"/>
+      <c r="K359" s="191"/>
+      <c r="L359" s="192"/>
       <c r="M359" s="58"/>
       <c r="N359" s="67"/>
       <c r="O359" s="67"/>
@@ -16097,8 +16090,8 @@
       <c r="H360" s="67"/>
       <c r="I360" s="67"/>
       <c r="J360" s="67"/>
-      <c r="K360" s="190"/>
-      <c r="L360" s="191"/>
+      <c r="K360" s="191"/>
+      <c r="L360" s="192"/>
       <c r="M360" s="58"/>
       <c r="N360" s="67"/>
       <c r="O360" s="67"/>
@@ -16133,8 +16126,8 @@
       <c r="H361" s="67"/>
       <c r="I361" s="67"/>
       <c r="J361" s="67"/>
-      <c r="K361" s="190"/>
-      <c r="L361" s="191"/>
+      <c r="K361" s="191"/>
+      <c r="L361" s="192"/>
       <c r="M361" s="58"/>
       <c r="N361" s="67"/>
       <c r="O361" s="67"/>
@@ -16169,8 +16162,8 @@
       <c r="H362" s="67"/>
       <c r="I362" s="67"/>
       <c r="J362" s="67"/>
-      <c r="K362" s="190"/>
-      <c r="L362" s="191"/>
+      <c r="K362" s="191"/>
+      <c r="L362" s="192"/>
       <c r="M362" s="58"/>
       <c r="N362" s="67"/>
       <c r="O362" s="67"/>
@@ -16205,8 +16198,8 @@
       <c r="H363" s="67"/>
       <c r="I363" s="67"/>
       <c r="J363" s="67"/>
-      <c r="K363" s="190"/>
-      <c r="L363" s="191"/>
+      <c r="K363" s="191"/>
+      <c r="L363" s="192"/>
       <c r="M363" s="58"/>
       <c r="N363" s="67"/>
       <c r="O363" s="67"/>
@@ -16241,8 +16234,8 @@
       <c r="H364" s="67"/>
       <c r="I364" s="67"/>
       <c r="J364" s="67"/>
-      <c r="K364" s="190"/>
-      <c r="L364" s="191"/>
+      <c r="K364" s="191"/>
+      <c r="L364" s="192"/>
       <c r="M364" s="58"/>
       <c r="N364" s="67"/>
       <c r="O364" s="67"/>
@@ -16277,8 +16270,8 @@
       <c r="H365" s="67"/>
       <c r="I365" s="67"/>
       <c r="J365" s="67"/>
-      <c r="K365" s="190"/>
-      <c r="L365" s="191"/>
+      <c r="K365" s="191"/>
+      <c r="L365" s="192"/>
       <c r="M365" s="58"/>
       <c r="N365" s="67"/>
       <c r="O365" s="67"/>
@@ -16313,8 +16306,8 @@
       <c r="H366" s="67"/>
       <c r="I366" s="67"/>
       <c r="J366" s="67"/>
-      <c r="K366" s="190"/>
-      <c r="L366" s="191"/>
+      <c r="K366" s="191"/>
+      <c r="L366" s="192"/>
       <c r="M366" s="58"/>
       <c r="N366" s="67"/>
       <c r="O366" s="67"/>
@@ -16349,8 +16342,8 @@
       <c r="H367" s="67"/>
       <c r="I367" s="67"/>
       <c r="J367" s="67"/>
-      <c r="K367" s="190"/>
-      <c r="L367" s="191"/>
+      <c r="K367" s="191"/>
+      <c r="L367" s="192"/>
       <c r="M367" s="58"/>
       <c r="N367" s="67"/>
       <c r="O367" s="67"/>
@@ -16385,8 +16378,8 @@
       <c r="H368" s="67"/>
       <c r="I368" s="67"/>
       <c r="J368" s="67"/>
-      <c r="K368" s="190"/>
-      <c r="L368" s="191"/>
+      <c r="K368" s="191"/>
+      <c r="L368" s="192"/>
       <c r="M368" s="58"/>
       <c r="N368" s="67"/>
       <c r="O368" s="67"/>
@@ -16421,8 +16414,8 @@
       <c r="H369" s="67"/>
       <c r="I369" s="67"/>
       <c r="J369" s="67"/>
-      <c r="K369" s="190"/>
-      <c r="L369" s="191"/>
+      <c r="K369" s="191"/>
+      <c r="L369" s="192"/>
       <c r="M369" s="58"/>
       <c r="N369" s="67"/>
       <c r="O369" s="67"/>
@@ -16457,8 +16450,8 @@
       <c r="H370" s="67"/>
       <c r="I370" s="67"/>
       <c r="J370" s="67"/>
-      <c r="K370" s="190"/>
-      <c r="L370" s="191"/>
+      <c r="K370" s="191"/>
+      <c r="L370" s="192"/>
       <c r="M370" s="58"/>
       <c r="N370" s="67"/>
       <c r="O370" s="67"/>
@@ -16493,8 +16486,8 @@
       <c r="H371" s="67"/>
       <c r="I371" s="67"/>
       <c r="J371" s="67"/>
-      <c r="K371" s="190"/>
-      <c r="L371" s="191"/>
+      <c r="K371" s="191"/>
+      <c r="L371" s="192"/>
       <c r="M371" s="58"/>
       <c r="N371" s="67"/>
       <c r="O371" s="67"/>
@@ -17383,11 +17376,11 @@
       <c r="AH395" s="67"/>
     </row>
     <row r="396">
-      <c r="A396" s="201"/>
-      <c r="B396" s="201"/>
-      <c r="C396" s="201"/>
-      <c r="D396" s="201"/>
-      <c r="E396" s="202"/>
+      <c r="A396" s="215"/>
+      <c r="B396" s="216"/>
+      <c r="C396" s="216"/>
+      <c r="D396" s="216"/>
+      <c r="E396" s="217"/>
       <c r="F396" s="140"/>
       <c r="G396" s="213"/>
       <c r="H396" s="203"/>
@@ -17419,11 +17412,11 @@
       <c r="AH396" s="67"/>
     </row>
     <row r="397">
-      <c r="A397" s="201"/>
-      <c r="B397" s="201"/>
-      <c r="C397" s="201"/>
-      <c r="D397" s="201"/>
-      <c r="E397" s="202"/>
+      <c r="A397" s="218"/>
+      <c r="B397" s="219"/>
+      <c r="C397" s="219"/>
+      <c r="D397" s="219"/>
+      <c r="E397" s="220"/>
       <c r="F397" s="140"/>
       <c r="G397" s="213"/>
       <c r="H397" s="203"/>
@@ -17455,11 +17448,11 @@
       <c r="AH397" s="67"/>
     </row>
     <row r="398">
-      <c r="A398" s="215"/>
-      <c r="B398" s="216"/>
-      <c r="C398" s="216"/>
-      <c r="D398" s="216"/>
-      <c r="E398" s="217"/>
+      <c r="A398" s="218"/>
+      <c r="B398" s="219"/>
+      <c r="C398" s="219"/>
+      <c r="D398" s="219"/>
+      <c r="E398" s="220"/>
       <c r="F398" s="140"/>
       <c r="G398" s="213"/>
       <c r="H398" s="203"/>
@@ -38561,8 +38554,8 @@
       <c r="H984" s="67"/>
       <c r="I984" s="67"/>
       <c r="J984" s="67"/>
-      <c r="K984" s="190"/>
-      <c r="L984" s="191"/>
+      <c r="K984" s="191"/>
+      <c r="L984" s="192"/>
       <c r="M984" s="58"/>
       <c r="N984" s="213"/>
       <c r="O984" s="203"/>
@@ -38597,8 +38590,8 @@
       <c r="H985" s="67"/>
       <c r="I985" s="67"/>
       <c r="J985" s="67"/>
-      <c r="K985" s="190"/>
-      <c r="L985" s="191"/>
+      <c r="K985" s="191"/>
+      <c r="L985" s="192"/>
       <c r="M985" s="58"/>
       <c r="N985" s="213"/>
       <c r="O985" s="203"/>
@@ -38633,8 +38626,8 @@
       <c r="H986" s="67"/>
       <c r="I986" s="67"/>
       <c r="J986" s="67"/>
-      <c r="K986" s="190"/>
-      <c r="L986" s="191"/>
+      <c r="K986" s="191"/>
+      <c r="L986" s="192"/>
       <c r="M986" s="58"/>
       <c r="N986" s="221"/>
       <c r="O986" s="222"/>
@@ -38669,17 +38662,17 @@
       <c r="H987" s="67"/>
       <c r="I987" s="67"/>
       <c r="J987" s="67"/>
-      <c r="K987" s="190"/>
-      <c r="L987" s="191"/>
+      <c r="K987" s="191"/>
+      <c r="L987" s="192"/>
       <c r="M987" s="58"/>
       <c r="N987" s="67"/>
       <c r="O987" s="67"/>
       <c r="P987" s="67"/>
       <c r="Q987" s="67"/>
-      <c r="R987" s="190"/>
-      <c r="S987" s="190"/>
-      <c r="T987" s="190"/>
-      <c r="U987" s="190"/>
+      <c r="R987" s="191"/>
+      <c r="S987" s="191"/>
+      <c r="T987" s="191"/>
+      <c r="U987" s="191"/>
       <c r="V987" s="208"/>
       <c r="W987" s="58"/>
       <c r="X987" s="67"/>
@@ -38705,17 +38698,17 @@
       <c r="H988" s="67"/>
       <c r="I988" s="67"/>
       <c r="J988" s="67"/>
-      <c r="K988" s="190"/>
-      <c r="L988" s="191"/>
+      <c r="K988" s="191"/>
+      <c r="L988" s="192"/>
       <c r="M988" s="58"/>
       <c r="N988" s="67"/>
       <c r="O988" s="67"/>
       <c r="P988" s="67"/>
       <c r="Q988" s="67"/>
-      <c r="R988" s="190"/>
-      <c r="S988" s="190"/>
-      <c r="T988" s="190"/>
-      <c r="U988" s="190"/>
+      <c r="R988" s="191"/>
+      <c r="S988" s="191"/>
+      <c r="T988" s="191"/>
+      <c r="U988" s="191"/>
       <c r="V988" s="208"/>
       <c r="W988" s="58"/>
       <c r="X988" s="67"/>
@@ -38742,10 +38735,10 @@
       <c r="O989" s="67"/>
       <c r="P989" s="67"/>
       <c r="Q989" s="67"/>
-      <c r="R989" s="190"/>
-      <c r="S989" s="190"/>
-      <c r="T989" s="190"/>
-      <c r="U989" s="190"/>
+      <c r="R989" s="191"/>
+      <c r="S989" s="191"/>
+      <c r="T989" s="191"/>
+      <c r="U989" s="191"/>
       <c r="V989" s="208"/>
       <c r="W989" s="58"/>
       <c r="X989" s="67"/>
@@ -38772,10 +38765,10 @@
       <c r="O990" s="67"/>
       <c r="P990" s="67"/>
       <c r="Q990" s="67"/>
-      <c r="R990" s="190"/>
-      <c r="S990" s="190"/>
-      <c r="T990" s="190"/>
-      <c r="U990" s="190"/>
+      <c r="R990" s="191"/>
+      <c r="S990" s="191"/>
+      <c r="T990" s="191"/>
+      <c r="U990" s="191"/>
       <c r="V990" s="208"/>
       <c r="W990" s="58"/>
       <c r="X990" s="67"/>
@@ -38802,10 +38795,10 @@
       <c r="O991" s="67"/>
       <c r="P991" s="67"/>
       <c r="Q991" s="67"/>
-      <c r="R991" s="190"/>
-      <c r="S991" s="190"/>
-      <c r="T991" s="190"/>
-      <c r="U991" s="190"/>
+      <c r="R991" s="191"/>
+      <c r="S991" s="191"/>
+      <c r="T991" s="191"/>
+      <c r="U991" s="191"/>
       <c r="V991" s="208"/>
       <c r="W991" s="58"/>
       <c r="X991" s="67"/>
@@ -39151,11 +39144,11 @@
       <c r="AH1006" s="67"/>
     </row>
     <row r="1007">
-      <c r="A1007" s="218"/>
-      <c r="B1007" s="219"/>
-      <c r="C1007" s="219"/>
-      <c r="D1007" s="219"/>
-      <c r="E1007" s="220"/>
+      <c r="A1007" s="99"/>
+      <c r="B1007" s="101"/>
+      <c r="C1007" s="101"/>
+      <c r="D1007" s="101"/>
+      <c r="E1007" s="227"/>
       <c r="F1007" s="140"/>
       <c r="M1007" s="58"/>
       <c r="V1007" s="226"/>
@@ -39173,11 +39166,11 @@
       <c r="AH1007" s="67"/>
     </row>
     <row r="1008">
-      <c r="A1008" s="218"/>
-      <c r="B1008" s="219"/>
-      <c r="C1008" s="219"/>
-      <c r="D1008" s="219"/>
-      <c r="E1008" s="220"/>
+      <c r="A1008" s="201"/>
+      <c r="B1008" s="201"/>
+      <c r="C1008" s="201"/>
+      <c r="D1008" s="201"/>
+      <c r="E1008" s="202"/>
       <c r="F1008" s="140"/>
       <c r="M1008" s="58"/>
       <c r="V1008" s="226"/>
@@ -39195,11 +39188,11 @@
       <c r="AH1008" s="67"/>
     </row>
     <row r="1009">
-      <c r="A1009" s="99"/>
-      <c r="B1009" s="101"/>
-      <c r="C1009" s="101"/>
-      <c r="D1009" s="101"/>
-      <c r="E1009" s="227"/>
+      <c r="A1009" s="201"/>
+      <c r="B1009" s="201"/>
+      <c r="C1009" s="201"/>
+      <c r="D1009" s="201"/>
+      <c r="E1009" s="202"/>
       <c r="F1009" s="140"/>
       <c r="M1009" s="58"/>
       <c r="V1009" s="226"/>
@@ -39474,11 +39467,6 @@
       <c r="AH1021" s="67"/>
     </row>
     <row r="1022">
-      <c r="A1022" s="201"/>
-      <c r="B1022" s="201"/>
-      <c r="C1022" s="201"/>
-      <c r="D1022" s="201"/>
-      <c r="E1022" s="202"/>
       <c r="M1022" s="58"/>
       <c r="V1022" s="226"/>
       <c r="W1022" s="58"/>
@@ -39495,11 +39483,6 @@
       <c r="AH1022" s="67"/>
     </row>
     <row r="1023">
-      <c r="A1023" s="201"/>
-      <c r="B1023" s="201"/>
-      <c r="C1023" s="201"/>
-      <c r="D1023" s="201"/>
-      <c r="E1023" s="202"/>
       <c r="M1023" s="58"/>
       <c r="V1023" s="226"/>
       <c r="W1023" s="58"/>
@@ -39865,62 +39848,61 @@
     <hyperlink r:id="rId9" ref="H12"/>
     <hyperlink r:id="rId10" ref="O12"/>
     <hyperlink r:id="rId11" ref="B13"/>
-    <hyperlink r:id="rId12" ref="O13"/>
-    <hyperlink r:id="rId13" ref="O14"/>
-    <hyperlink r:id="rId14" ref="B15"/>
-    <hyperlink r:id="rId15" ref="O15"/>
-    <hyperlink r:id="rId16" ref="B16"/>
-    <hyperlink r:id="rId17" ref="O16"/>
-    <hyperlink r:id="rId18" ref="B17"/>
-    <hyperlink r:id="rId19" ref="O17"/>
-    <hyperlink r:id="rId20" ref="B18"/>
-    <hyperlink r:id="rId21" ref="O18"/>
-    <hyperlink r:id="rId22" ref="B19"/>
-    <hyperlink r:id="rId23" ref="O19"/>
-    <hyperlink r:id="rId24" ref="B20"/>
-    <hyperlink r:id="rId25" ref="O20"/>
-    <hyperlink r:id="rId26" ref="B21"/>
-    <hyperlink r:id="rId27" ref="B22"/>
-    <hyperlink r:id="rId28" ref="O22"/>
-    <hyperlink r:id="rId29" ref="B23"/>
-    <hyperlink r:id="rId30" ref="O23"/>
-    <hyperlink r:id="rId31" ref="B24"/>
-    <hyperlink r:id="rId32" ref="O24"/>
-    <hyperlink r:id="rId33" ref="B25"/>
-    <hyperlink r:id="rId34" ref="O25"/>
-    <hyperlink r:id="rId35" ref="B26"/>
+    <hyperlink r:id="rId12" ref="H13"/>
+    <hyperlink r:id="rId13" ref="O13"/>
+    <hyperlink r:id="rId14" ref="O14"/>
+    <hyperlink r:id="rId15" ref="B15"/>
+    <hyperlink r:id="rId16" ref="O15"/>
+    <hyperlink r:id="rId17" ref="B16"/>
+    <hyperlink r:id="rId18" ref="O16"/>
+    <hyperlink r:id="rId19" ref="B17"/>
+    <hyperlink r:id="rId20" ref="O17"/>
+    <hyperlink r:id="rId21" ref="B18"/>
+    <hyperlink r:id="rId22" ref="O18"/>
+    <hyperlink r:id="rId23" ref="B19"/>
+    <hyperlink r:id="rId24" ref="O19"/>
+    <hyperlink r:id="rId25" ref="B20"/>
+    <hyperlink r:id="rId26" ref="O20"/>
+    <hyperlink r:id="rId27" ref="B21"/>
+    <hyperlink r:id="rId28" ref="B22"/>
+    <hyperlink r:id="rId29" ref="O22"/>
+    <hyperlink r:id="rId30" ref="B23"/>
+    <hyperlink r:id="rId31" ref="O23"/>
+    <hyperlink r:id="rId32" ref="B24"/>
+    <hyperlink r:id="rId33" ref="O24"/>
+    <hyperlink r:id="rId34" ref="B25"/>
+    <hyperlink r:id="rId35" ref="O25"/>
     <hyperlink r:id="rId36" ref="O26"/>
     <hyperlink r:id="rId37" ref="B27"/>
     <hyperlink r:id="rId38" ref="O27"/>
-    <hyperlink r:id="rId39" ref="O28"/>
-    <hyperlink r:id="rId40" ref="B29"/>
-    <hyperlink r:id="rId41" ref="O29"/>
-    <hyperlink r:id="rId42" ref="B30"/>
-    <hyperlink r:id="rId43" ref="O30"/>
-    <hyperlink r:id="rId44" ref="B31"/>
-    <hyperlink r:id="rId45" ref="O31"/>
-    <hyperlink r:id="rId46" ref="B32"/>
-    <hyperlink r:id="rId47" ref="O32"/>
-    <hyperlink r:id="rId48" ref="B33"/>
+    <hyperlink r:id="rId39" ref="B28"/>
+    <hyperlink r:id="rId40" ref="O28"/>
+    <hyperlink r:id="rId41" ref="B29"/>
+    <hyperlink r:id="rId42" ref="O29"/>
+    <hyperlink r:id="rId43" ref="B30"/>
+    <hyperlink r:id="rId44" ref="O30"/>
+    <hyperlink r:id="rId45" ref="B31"/>
+    <hyperlink r:id="rId46" ref="O31"/>
+    <hyperlink r:id="rId47" ref="B32"/>
+    <hyperlink r:id="rId48" ref="O32"/>
     <hyperlink r:id="rId49" ref="O33"/>
-    <hyperlink r:id="rId50" ref="B34"/>
-    <hyperlink r:id="rId51" ref="O34"/>
+    <hyperlink r:id="rId50" ref="O34"/>
+    <hyperlink r:id="rId51" ref="B35"/>
     <hyperlink r:id="rId52" ref="O35"/>
     <hyperlink r:id="rId53" ref="O36"/>
-    <hyperlink r:id="rId54" ref="B37"/>
-    <hyperlink r:id="rId55" ref="O37"/>
+    <hyperlink r:id="rId54" ref="O37"/>
+    <hyperlink r:id="rId55" ref="B38"/>
     <hyperlink r:id="rId56" ref="O38"/>
     <hyperlink r:id="rId57" ref="O39"/>
-    <hyperlink r:id="rId58" ref="B40"/>
-    <hyperlink r:id="rId59" ref="O40"/>
+    <hyperlink r:id="rId58" ref="O40"/>
+    <hyperlink r:id="rId59" ref="B41"/>
     <hyperlink r:id="rId60" ref="O41"/>
     <hyperlink r:id="rId61" ref="O42"/>
     <hyperlink r:id="rId62" ref="B43"/>
     <hyperlink r:id="rId63" ref="O43"/>
     <hyperlink r:id="rId64" ref="O44"/>
-    <hyperlink r:id="rId65" ref="B45"/>
   </hyperlinks>
-  <drawing r:id="rId66"/>
+  <drawing r:id="rId65"/>
 </worksheet>
 </file>
 
@@ -39953,44 +39935,44 @@
     </row>
     <row r="3" ht="26.25" customHeight="1">
       <c r="C3" s="230" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3" s="231">
         <v>23968.18</v>
       </c>
       <c r="F3" s="230" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G3" s="231">
         <v>6196.22</v>
       </c>
       <c r="I3" s="230" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J3" s="231">
         <v>142.52</v>
       </c>
       <c r="L3" s="229"/>
       <c r="M3" s="232" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="232" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="232" t="s">
+      <c r="O3" s="232" t="s">
         <v>126</v>
-      </c>
-      <c r="O3" s="232" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="4" ht="26.25" customHeight="1">
       <c r="C4" s="233" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4" s="232">
         <v>4090.0</v>
       </c>
       <c r="G4" s="228"/>
       <c r="L4" s="234" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M4" s="232">
         <v>-780.24</v>
@@ -40005,19 +39987,19 @@
     </row>
     <row r="5" ht="26.25" customHeight="1">
       <c r="C5" s="233" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="232">
         <v>16186.02</v>
       </c>
       <c r="F5" s="233" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G5" s="232">
         <v>5373.93</v>
       </c>
       <c r="I5" s="233" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J5" s="233">
         <v>121.72</v>
@@ -40038,25 +40020,25 @@
     </row>
     <row r="6" ht="26.25" customHeight="1">
       <c r="C6" s="233" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D6" s="232">
         <v>3692.16</v>
       </c>
       <c r="F6" s="233" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G6" s="232">
         <v>804.78</v>
       </c>
       <c r="I6" s="233" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J6" s="233">
         <v>20.8</v>
       </c>
       <c r="L6" s="234" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M6" s="232">
         <v>-121.72</v>
@@ -40072,7 +40054,7 @@
     <row r="7" ht="26.25" customHeight="1">
       <c r="D7" s="228"/>
       <c r="F7" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G7" s="232">
         <v>17.51</v>

--- a/public/Invoicing.xlsx
+++ b/public/Invoicing.xlsx
@@ -46,10 +46,10 @@
     <t>50-51</t>
   </si>
   <si>
-    <t>Scheduled for Build</t>
+    <t>non recov dep</t>
   </si>
   <si>
-    <t>non recov dep</t>
+    <t>Scheduled for Build</t>
   </si>
   <si>
     <t>Needs to be Invoiced</t>
@@ -470,15 +470,15 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18.0"/>
       <color rgb="FF4A86E8"/>
       <name val="Georgia"/>
-    </font>
-    <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="15.0"/>
@@ -1227,16 +1227,25 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1245,20 +1254,11 @@
     <xf borderId="0" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1281,8 +1281,11 @@
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1291,9 +1294,6 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1326,7 +1326,7 @@
     <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -2208,17 +2208,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="10.5" customHeight="1">
-      <c r="A1" s="3"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
       <c r="L1" s="14"/>
       <c r="M1" s="15"/>
       <c r="N1" s="16"/>
@@ -2245,21 +2245,21 @@
     </row>
     <row r="2" ht="21.0" customHeight="1">
       <c r="A2" s="21"/>
-      <c r="B2" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="23">
+      <c r="B2" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="24">
         <f>D7</f>
         <v>540749.23</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="12"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="13"/>
       <c r="H2" s="26"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
       <c r="L2" s="14"/>
       <c r="M2" s="15"/>
       <c r="N2" s="16"/>
@@ -2294,13 +2294,13 @@
         <v>54124.53</v>
       </c>
       <c r="D3" s="29"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
       <c r="L3" s="14"/>
       <c r="M3" s="15"/>
       <c r="N3" s="16"/>
@@ -2335,13 +2335,13 @@
         <v>334839.185</v>
       </c>
       <c r="D4" s="29"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="32"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
       <c r="L4" s="14"/>
       <c r="M4" s="15"/>
       <c r="N4" s="16"/>
@@ -2376,13 +2376,13 @@
         <v>929712.945</v>
       </c>
       <c r="D5" s="35"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="12"/>
       <c r="G5" s="36"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="14"/>
       <c r="M5" s="15"/>
       <c r="N5" s="16"/>
@@ -2412,13 +2412,13 @@
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
       <c r="D6" s="37"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
       <c r="L6" s="14"/>
       <c r="M6" s="15"/>
       <c r="N6" s="16"/>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="7" ht="46.5" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
@@ -2454,7 +2454,7 @@
         <v>540749.23</v>
       </c>
       <c r="E7" s="41"/>
-      <c r="F7" s="10"/>
+      <c r="F7" s="12"/>
       <c r="G7" s="42" t="s">
         <v>15</v>
       </c>
@@ -38897,50 +38897,50 @@
       <c r="O2" s="1"/>
     </row>
     <row r="3" ht="26.25" customHeight="1">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>23968.18</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>6196.22</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
         <v>142.52</v>
       </c>
       <c r="L3" s="2"/>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" ht="26.25" customHeight="1">
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="5">
         <v>4090.0</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="5">
         <v>-780.24</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="5">
         <v>-300.81</v>
       </c>
       <c r="O4" s="1">
@@ -38949,31 +38949,31 @@
       </c>
     </row>
     <row r="5" ht="26.25" customHeight="1">
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="5">
         <v>16186.02</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="5">
         <v>5373.93</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="7">
         <v>121.72</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="9">
         <v>33.0</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="5">
         <v>-44.52</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="5">
         <v>-23.12</v>
       </c>
       <c r="O5" s="1">
@@ -38982,31 +38982,31 @@
       </c>
     </row>
     <row r="6" ht="26.25" customHeight="1">
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="5">
         <v>3692.16</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="5">
         <v>804.78</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="7">
         <v>20.8</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="5">
         <v>-121.72</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="5">
         <v>-20.8</v>
       </c>
       <c r="O6" s="1">
@@ -39016,19 +39016,19 @@
     </row>
     <row r="7" ht="26.25" customHeight="1">
       <c r="D7" s="1"/>
-      <c r="F7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="5">
         <v>17.51</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="9">
         <v>52.0</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="5">
         <v>-53.78</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="5">
         <v>-17.51</v>
       </c>
       <c r="O7" s="1">
@@ -39039,13 +39039,13 @@
     <row r="8" ht="26.25" customHeight="1">
       <c r="D8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="L8" s="13">
+      <c r="L8" s="9">
         <v>53.0</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="5">
         <v>-156.55</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="5">
         <v>0.0</v>
       </c>
       <c r="O8" s="1">
@@ -39057,15 +39057,15 @@
       <c r="D9" s="1"/>
       <c r="G9" s="1"/>
       <c r="L9" s="2"/>
-      <c r="M9" s="6">
+      <c r="M9" s="4">
         <f t="shared" ref="M9:O9" si="2">M4+M5+M6+M7+M8</f>
         <v>-1156.81</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="22">
         <f t="shared" si="2"/>
         <v>-362.24</v>
       </c>
-      <c r="O9" s="25">
+      <c r="O9" s="22">
         <f t="shared" si="2"/>
         <v>-1519.05</v>
       </c>
@@ -39082,7 +39082,7 @@
       <c r="D11" s="1"/>
       <c r="G11" s="1"/>
       <c r="L11" s="2"/>
-      <c r="M11" s="9">
+      <c r="M11" s="5">
         <v>-17.51</v>
       </c>
       <c r="N11" s="1"/>
